--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53F43FE-8001-4070-BF23-9F51E5BF3429}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B319324A-4EED-4467-85CE-EF28F86113AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,7 +711,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -733,6 +733,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2032,7 +2038,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2640,6 +2646,9 @@
     <xf numFmtId="167" fontId="3" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2709,7 +2718,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3082,15 +3091,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="208"/>
-      <c r="Q1" s="209"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="209"/>
-      <c r="V1" s="209"/>
-      <c r="W1" s="209"/>
-      <c r="X1" s="210"/>
+      <c r="P1" s="209"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3115,62 +3124,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="215"/>
-      <c r="G4" s="216" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="218" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="220" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="218" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="222" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="223"/>
-      <c r="S4" s="223"/>
-      <c r="T4" s="223"/>
-      <c r="U4" s="223"/>
-      <c r="V4" s="224"/>
-      <c r="W4" s="223"/>
-      <c r="X4" s="225"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="217"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="219"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5421,7 +5430,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="203" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -5439,7 +5448,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="204"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -5455,7 +5464,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="205"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -5471,7 +5480,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="206" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -5489,7 +5498,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="206"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -5505,7 +5514,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="207"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -5898,15 +5907,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="208">
+      <c r="P1" s="209">
         <v>46058</v>
       </c>
-      <c r="Q1" s="209"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="209"/>
-      <c r="V1" s="210"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="211"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -5929,60 +5938,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="215"/>
-      <c r="G4" s="216" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="218" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="220" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="218" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="222" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="223"/>
-      <c r="S4" s="223"/>
-      <c r="T4" s="223"/>
-      <c r="U4" s="223"/>
-      <c r="V4" s="225"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="226"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="217"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="219"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8791,7 +8800,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="203" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -8809,7 +8818,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="204"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -8825,7 +8834,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="205"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -8841,7 +8850,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="206" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -8859,7 +8868,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="206"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -8875,7 +8884,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="207"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -9269,17 +9278,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="208">
+      <c r="P1" s="209">
         <v>46083</v>
       </c>
-      <c r="Q1" s="209"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="209"/>
-      <c r="V1" s="209"/>
-      <c r="W1" s="209"/>
-      <c r="X1" s="210"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9304,62 +9313,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="215"/>
-      <c r="G4" s="216" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="218" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="220" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="218" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="222" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="223"/>
-      <c r="S4" s="223"/>
-      <c r="T4" s="223"/>
-      <c r="U4" s="223"/>
-      <c r="V4" s="224"/>
-      <c r="W4" s="223"/>
-      <c r="X4" s="225"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="217"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="219"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9524,22 +9533,30 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>68</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
-      <c r="G8" s="79"/>
+      <c r="G8" s="79">
+        <v>1</v>
+      </c>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
-      <c r="L8" s="121"/>
+      <c r="L8" s="121">
+        <v>1</v>
+      </c>
       <c r="M8" s="121"/>
       <c r="N8" s="121"/>
       <c r="O8" s="121"/>
@@ -9547,7 +9564,7 @@
       <c r="Q8" s="129"/>
       <c r="R8" s="92">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="133">
         <f t="shared" si="1"/>
@@ -9556,15 +9573,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="116">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="139">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1629</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -9599,22 +9616,28 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>103</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
-      <c r="G9" s="81"/>
+      <c r="G9" s="81">
+        <v>1</v>
+      </c>
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="53"/>
-      <c r="L9" s="130"/>
+      <c r="L9" s="130">
+        <v>1</v>
+      </c>
       <c r="M9" s="130"/>
       <c r="N9" s="130"/>
       <c r="O9" s="130"/>
@@ -9622,7 +9645,7 @@
       <c r="Q9" s="131"/>
       <c r="R9" s="107">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="134">
         <f t="shared" si="1"/>
@@ -9631,15 +9654,15 @@
       <c r="T9" s="53"/>
       <c r="U9" s="140">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V9" s="141">
         <f>U9/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -9674,15 +9697,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>82</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
-      <c r="G10" s="79"/>
+      <c r="G10" s="79">
+        <v>2</v>
+      </c>
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
@@ -9691,13 +9718,15 @@
       <c r="K10" s="41"/>
       <c r="L10" s="121"/>
       <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
+      <c r="N10" s="121">
+        <v>2</v>
+      </c>
       <c r="O10" s="121"/>
       <c r="P10" s="121"/>
       <c r="Q10" s="129"/>
       <c r="R10" s="108">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" s="135">
         <f t="shared" si="1"/>
@@ -9706,15 +9735,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="116">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V10" s="143">
         <f>U10/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1920</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -9749,22 +9778,28 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>41</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
-      <c r="G11" s="79"/>
+      <c r="G11" s="79">
+        <v>1</v>
+      </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="121"/>
+      <c r="L11" s="121">
+        <v>1</v>
+      </c>
       <c r="M11" s="121"/>
       <c r="N11" s="121"/>
       <c r="O11" s="121"/>
@@ -9772,7 +9807,7 @@
       <c r="Q11" s="129"/>
       <c r="R11" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="133">
         <f t="shared" si="1"/>
@@ -9781,15 +9816,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="116">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="139">
         <f>U11/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -9824,7 +9859,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -9832,7 +9869,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -9864,7 +9901,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -9899,47 +9936,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>4050</v>
+      </c>
+      <c r="D13" s="123">
+        <v>11</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="G13" s="81">
+        <v>27</v>
+      </c>
+      <c r="H13" s="82">
+        <v>16</v>
+      </c>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4023</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K13" s="55"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="131"/>
+      <c r="L13" s="130">
+        <v>6</v>
+      </c>
+      <c r="M13" s="130">
+        <v>5</v>
+      </c>
+      <c r="N13" s="130">
+        <v>9</v>
+      </c>
+      <c r="O13" s="130">
+        <v>3</v>
+      </c>
+      <c r="P13" s="130">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="131">
+        <v>3</v>
+      </c>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>96547</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -9981,7 +10038,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -9989,7 +10048,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -10021,7 +10080,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -10281,7 +10340,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -10289,7 +10350,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -10321,7 +10382,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -10431,7 +10492,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -10439,7 +10502,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -10471,7 +10534,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -10506,7 +10569,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -10514,7 +10579,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -10546,7 +10611,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -10581,7 +10646,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -10589,7 +10656,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -10621,7 +10688,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -10656,7 +10723,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -10664,7 +10733,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -10696,7 +10765,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -10738,7 +10807,9 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="119">
+        <v>47</v>
+      </c>
       <c r="D24" s="120"/>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
@@ -10746,7 +10817,7 @@
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
@@ -10778,7 +10849,7 @@
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -10820,7 +10891,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -10828,7 +10901,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -10860,7 +10933,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -10895,19 +10968,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="C26" s="119">
+        <v>125</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
       <c r="E26" s="121"/>
       <c r="F26" s="121"/>
       <c r="G26" s="79"/>
       <c r="H26" s="76"/>
       <c r="I26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J26" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="121"/>
@@ -10935,7 +11012,7 @@
       </c>
       <c r="W26" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3011</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -10951,7 +11028,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="119"/>
+      <c r="C27" s="119">
+        <v>20</v>
+      </c>
       <c r="D27" s="120"/>
       <c r="E27" s="121"/>
       <c r="F27" s="121"/>
@@ -10959,7 +11038,7 @@
       <c r="H27" s="76"/>
       <c r="I27" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J27" s="80">
         <f t="shared" si="4"/>
@@ -10991,7 +11070,7 @@
       </c>
       <c r="W27" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -11069,30 +11148,38 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="119"/>
+      <c r="C29" s="119">
+        <v>107</v>
+      </c>
       <c r="D29" s="120"/>
       <c r="E29" s="121"/>
       <c r="F29" s="121"/>
-      <c r="G29" s="79"/>
+      <c r="G29" s="79">
+        <v>4</v>
+      </c>
       <c r="H29" s="76"/>
       <c r="I29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J29" s="80">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="121"/>
+      <c r="L29" s="121">
+        <v>2</v>
+      </c>
       <c r="M29" s="121"/>
       <c r="N29" s="121"/>
       <c r="O29" s="121"/>
-      <c r="P29" s="121"/>
+      <c r="P29" s="121">
+        <v>2</v>
+      </c>
       <c r="Q29" s="129"/>
       <c r="R29" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S29" s="133">
         <f t="shared" si="7"/>
@@ -11101,15 +11188,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V29" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W29" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -11128,7 +11215,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="119"/>
+      <c r="C30" s="119">
+        <v>10</v>
+      </c>
       <c r="D30" s="120"/>
       <c r="E30" s="121"/>
       <c r="F30" s="121"/>
@@ -11136,7 +11225,7 @@
       <c r="H30" s="76"/>
       <c r="I30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="80">
         <f t="shared" si="4"/>
@@ -11168,7 +11257,7 @@
       </c>
       <c r="W30" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -11180,7 +11269,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="119">
+        <v>60</v>
+      </c>
       <c r="D31" s="120"/>
       <c r="E31" s="121"/>
       <c r="F31" s="121"/>
@@ -11188,7 +11279,7 @@
       <c r="H31" s="76"/>
       <c r="I31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J31" s="80">
         <f t="shared" si="4"/>
@@ -11220,7 +11311,7 @@
       </c>
       <c r="W31" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -11232,15 +11323,19 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="119"/>
+      <c r="C32" s="119">
+        <v>17</v>
+      </c>
       <c r="D32" s="120"/>
       <c r="E32" s="121"/>
       <c r="F32" s="121"/>
-      <c r="G32" s="79"/>
+      <c r="G32" s="79">
+        <v>1</v>
+      </c>
       <c r="H32" s="76"/>
       <c r="I32" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J32" s="80">
         <f t="shared" si="4"/>
@@ -11249,13 +11344,15 @@
       <c r="K32" s="41"/>
       <c r="L32" s="121"/>
       <c r="M32" s="121"/>
-      <c r="N32" s="121"/>
+      <c r="N32" s="121">
+        <v>1</v>
+      </c>
       <c r="O32" s="121"/>
       <c r="P32" s="121"/>
       <c r="Q32" s="129"/>
       <c r="R32" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="133">
         <f t="shared" si="7"/>
@@ -11264,15 +11361,15 @@
       <c r="T32" s="41"/>
       <c r="U32" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V32" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -11336,7 +11433,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="119"/>
+      <c r="C34" s="119">
+        <v>3</v>
+      </c>
       <c r="D34" s="120"/>
       <c r="E34" s="121"/>
       <c r="F34" s="121"/>
@@ -11344,7 +11443,7 @@
       <c r="H34" s="76"/>
       <c r="I34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="80">
         <f t="shared" si="4"/>
@@ -11376,7 +11475,7 @@
       </c>
       <c r="W34" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -11388,47 +11487,63 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="120"/>
+      <c r="C35" s="119">
+        <v>159</v>
+      </c>
+      <c r="D35" s="120">
+        <v>5</v>
+      </c>
       <c r="E35" s="121"/>
       <c r="F35" s="121"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="76"/>
+      <c r="G35" s="79">
+        <v>13</v>
+      </c>
+      <c r="H35" s="76">
+        <v>12</v>
+      </c>
       <c r="I35" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="J35" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="121"/>
+      <c r="L35" s="121">
+        <v>2</v>
+      </c>
       <c r="M35" s="121"/>
-      <c r="N35" s="121"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="121"/>
+      <c r="N35" s="121">
+        <v>10</v>
+      </c>
+      <c r="O35" s="121">
+        <v>12</v>
+      </c>
+      <c r="P35" s="121">
+        <v>1</v>
+      </c>
       <c r="Q35" s="129"/>
       <c r="R35" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S35" s="133">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T35" s="41"/>
       <c r="U35" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="V35" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W35" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3497</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -11544,30 +11659,42 @@
       <c r="B38" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="122"/>
-      <c r="D38" s="123"/>
+      <c r="C38" s="122">
+        <v>4751</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
       <c r="E38" s="124"/>
       <c r="F38" s="124"/>
-      <c r="G38" s="81"/>
+      <c r="G38" s="81">
+        <v>115</v>
+      </c>
       <c r="H38" s="82"/>
       <c r="I38" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4636</v>
       </c>
       <c r="J38" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="53"/>
-      <c r="L38" s="130"/>
+      <c r="L38" s="130">
+        <v>18</v>
+      </c>
       <c r="M38" s="130"/>
-      <c r="N38" s="130"/>
+      <c r="N38" s="130">
+        <v>40</v>
+      </c>
       <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
+      <c r="P38" s="130">
+        <v>57</v>
+      </c>
       <c r="Q38" s="131"/>
       <c r="R38" s="106">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="S38" s="134">
         <f t="shared" si="7"/>
@@ -11576,15 +11703,15 @@
       <c r="T38" s="53"/>
       <c r="U38" s="140">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="V38" s="144">
         <f>U38/6</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="W38" s="142">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>27818</v>
       </c>
       <c r="X38" s="54"/>
     </row>
@@ -11596,7 +11723,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="119"/>
+      <c r="C39" s="119">
+        <v>19</v>
+      </c>
       <c r="D39" s="120"/>
       <c r="E39" s="121"/>
       <c r="F39" s="121"/>
@@ -11604,7 +11733,7 @@
       <c r="H39" s="76"/>
       <c r="I39" s="79">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J39" s="80">
         <f t="shared" si="4"/>
@@ -11636,7 +11765,7 @@
       </c>
       <c r="W39" s="138">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -11700,47 +11829,59 @@
       <c r="B41" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="155"/>
-      <c r="D41" s="156"/>
+      <c r="C41" s="155">
+        <v>560</v>
+      </c>
+      <c r="D41" s="156">
+        <v>12</v>
+      </c>
       <c r="E41" s="157"/>
       <c r="F41" s="157"/>
-      <c r="G41" s="158"/>
-      <c r="H41" s="159"/>
+      <c r="G41" s="158">
+        <v>1</v>
+      </c>
+      <c r="H41" s="159">
+        <v>12</v>
+      </c>
       <c r="I41" s="160">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="J41" s="161">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K41" s="162"/>
-      <c r="L41" s="163"/>
+      <c r="L41" s="163">
+        <v>1</v>
+      </c>
       <c r="M41" s="163"/>
       <c r="N41" s="163"/>
-      <c r="O41" s="163"/>
+      <c r="O41" s="163">
+        <v>12</v>
+      </c>
       <c r="P41" s="163"/>
       <c r="Q41" s="164"/>
       <c r="R41" s="165">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="166">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T41" s="162"/>
       <c r="U41" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V41" s="168">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="168">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>13416</v>
       </c>
       <c r="X41" s="169"/>
     </row>
@@ -11752,30 +11893,40 @@
       <c r="B42" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="172"/>
+      <c r="C42" s="172">
+        <v>1507</v>
+      </c>
       <c r="D42" s="173"/>
       <c r="E42" s="174"/>
       <c r="F42" s="174"/>
-      <c r="G42" s="175"/>
+      <c r="G42" s="175">
+        <v>22</v>
+      </c>
       <c r="H42" s="176"/>
       <c r="I42" s="175">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1485</v>
       </c>
       <c r="J42" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K42" s="178"/>
-      <c r="L42" s="174"/>
+      <c r="L42" s="174">
+        <v>12</v>
+      </c>
       <c r="M42" s="174"/>
-      <c r="N42" s="174"/>
+      <c r="N42" s="174">
+        <v>1</v>
+      </c>
       <c r="O42" s="174"/>
-      <c r="P42" s="174"/>
+      <c r="P42" s="174">
+        <v>9</v>
+      </c>
       <c r="Q42" s="179"/>
       <c r="R42" s="180">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S42" s="181">
         <f t="shared" si="7"/>
@@ -11784,15 +11935,15 @@
       <c r="T42" s="178"/>
       <c r="U42" s="182">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V42" s="183">
         <f>U42/12</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W42" s="184">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>17820</v>
       </c>
       <c r="X42" s="185"/>
     </row>
@@ -11847,30 +11998,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="122"/>
-      <c r="D44" s="123"/>
+      <c r="C44" s="122">
+        <v>34716</v>
+      </c>
+      <c r="D44" s="123">
+        <v>4</v>
+      </c>
       <c r="E44" s="124"/>
       <c r="F44" s="124"/>
-      <c r="G44" s="81"/>
+      <c r="G44" s="81">
+        <v>925</v>
+      </c>
       <c r="H44" s="82"/>
       <c r="I44" s="76">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>33791</v>
       </c>
       <c r="J44" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" s="53"/>
-      <c r="L44" s="130"/>
+      <c r="L44" s="130">
+        <v>308</v>
+      </c>
       <c r="M44" s="130"/>
-      <c r="N44" s="130"/>
+      <c r="N44" s="130">
+        <v>351</v>
+      </c>
       <c r="O44" s="130"/>
-      <c r="P44" s="130"/>
+      <c r="P44" s="130">
+        <v>266</v>
+      </c>
       <c r="Q44" s="131"/>
       <c r="R44" s="187">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="S44" s="188">
         <f t="shared" si="7"/>
@@ -11879,15 +12042,15 @@
       <c r="T44" s="53"/>
       <c r="U44" s="140">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5550</v>
       </c>
       <c r="V44" s="139">
         <f>U44/6</f>
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="W44" s="142">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>202750</v>
       </c>
       <c r="X44" s="54"/>
       <c r="Z44" s="47"/>
@@ -11995,7 +12158,9 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="119"/>
+      <c r="C47" s="119">
+        <v>4</v>
+      </c>
       <c r="D47" s="120"/>
       <c r="E47" s="121"/>
       <c r="F47" s="121"/>
@@ -12003,7 +12168,7 @@
       <c r="H47" s="76"/>
       <c r="I47" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="80">
         <f t="shared" si="4"/>
@@ -12035,7 +12200,7 @@
       </c>
       <c r="W47" s="138">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X47" s="27"/>
     </row>
@@ -12047,19 +12212,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="150"/>
-      <c r="D48" s="151"/>
+      <c r="C48" s="150">
+        <v>2355</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
       <c r="E48" s="130"/>
       <c r="F48" s="130"/>
       <c r="G48" s="152"/>
       <c r="H48" s="148"/>
       <c r="I48" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2355</v>
       </c>
       <c r="J48" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="53"/>
       <c r="L48" s="130"/>
@@ -12087,7 +12256,7 @@
       </c>
       <c r="W48" s="142">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>14134</v>
       </c>
       <c r="X48" s="54"/>
     </row>
@@ -12099,7 +12268,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="119"/>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
       <c r="D49" s="120"/>
       <c r="E49" s="121"/>
       <c r="F49" s="121"/>
@@ -12107,7 +12278,7 @@
       <c r="H49" s="76"/>
       <c r="I49" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="80">
         <f t="shared" si="4"/>
@@ -12139,7 +12310,7 @@
       </c>
       <c r="W49" s="138">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -12255,7 +12426,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="150"/>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
       <c r="D52" s="151"/>
       <c r="E52" s="130"/>
       <c r="F52" s="130"/>
@@ -12263,7 +12436,7 @@
       <c r="H52" s="148"/>
       <c r="I52" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="149">
         <f t="shared" si="4"/>
@@ -12295,7 +12468,7 @@
       </c>
       <c r="W52" s="142">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="54"/>
     </row>
@@ -12359,15 +12532,19 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="119"/>
+      <c r="C54" s="119">
+        <v>7</v>
+      </c>
       <c r="D54" s="120"/>
       <c r="E54" s="121"/>
       <c r="F54" s="121"/>
-      <c r="G54" s="79"/>
+      <c r="G54" s="79">
+        <v>1</v>
+      </c>
       <c r="H54" s="76"/>
       <c r="I54" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J54" s="80">
         <f t="shared" si="4"/>
@@ -12378,11 +12555,13 @@
       <c r="M54" s="121"/>
       <c r="N54" s="121"/>
       <c r="O54" s="121"/>
-      <c r="P54" s="121"/>
+      <c r="P54" s="121">
+        <v>1</v>
+      </c>
       <c r="Q54" s="129"/>
       <c r="R54" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="133">
         <f t="shared" si="7"/>
@@ -12391,15 +12570,15 @@
       <c r="T54" s="41"/>
       <c r="U54" s="116">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V54" s="139">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="138">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -12614,11 +12793,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>48888</v>
       </c>
       <c r="D60" s="57">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -12627,65 +12806,65 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1114</v>
       </c>
       <c r="H60" s="59">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I60" s="59">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>47774</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="77">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="M60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="O60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="Q60" s="78">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R60" s="91">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1114</v>
       </c>
       <c r="S60" s="90">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>7752</v>
       </c>
       <c r="V60" s="111">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="99">
+        <v>1114</v>
+      </c>
+      <c r="W60" s="227">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>394098</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -12693,10 +12872,10 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="V62" s="226"/>
+      <c r="V62" s="203"/>
     </row>
     <row r="63" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G63" s="203" t="s">
+      <c r="G63" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="60"/>
@@ -12714,7 +12893,7 @@
       <c r="S63" s="32"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="204"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="61"/>
       <c r="I64" s="61"/>
       <c r="J64" s="24" t="s">
@@ -12730,7 +12909,7 @@
       <c r="S64" s="35"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="205"/>
+      <c r="G65" s="206"/>
       <c r="H65" s="62"/>
       <c r="I65" s="62"/>
       <c r="J65" s="24" t="s">
@@ -12746,7 +12925,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="206" t="s">
+      <c r="G66" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H66" s="63"/>
@@ -12764,7 +12943,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G67" s="206"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="63"/>
       <c r="I67" s="63"/>
       <c r="J67" s="24" t="s">
@@ -12780,7 +12959,7 @@
       <c r="S67" s="35"/>
     </row>
     <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="207"/>
+      <c r="G68" s="208"/>
       <c r="H68" s="64"/>
       <c r="I68" s="64"/>
       <c r="J68" s="25" t="s">
@@ -13175,17 +13354,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="208">
+      <c r="P1" s="209">
         <v>46084</v>
       </c>
-      <c r="Q1" s="209"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="209"/>
-      <c r="V1" s="209"/>
-      <c r="W1" s="209"/>
-      <c r="X1" s="210"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -13210,62 +13389,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="215"/>
-      <c r="G4" s="216" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="218" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="220" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="218" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="222" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="223"/>
-      <c r="S4" s="223"/>
-      <c r="T4" s="223"/>
-      <c r="U4" s="223"/>
-      <c r="V4" s="224"/>
-      <c r="W4" s="223"/>
-      <c r="X4" s="225"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="217"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="219"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -16599,7 +16778,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="203" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -16617,7 +16796,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="204"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -16633,7 +16812,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="205"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -16649,7 +16828,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="206" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -16667,7 +16846,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="206"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -16683,7 +16862,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="207"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -17078,17 +17257,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="208">
+      <c r="P1" s="209">
         <v>46085</v>
       </c>
-      <c r="Q1" s="209"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="209"/>
-      <c r="V1" s="209"/>
-      <c r="W1" s="209"/>
-      <c r="X1" s="210"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -17113,62 +17292,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="211" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="212" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="215"/>
-      <c r="G4" s="216" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="218" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="220" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="218" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="222" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="223"/>
-      <c r="S4" s="223"/>
-      <c r="T4" s="223"/>
-      <c r="U4" s="223"/>
-      <c r="V4" s="224"/>
-      <c r="W4" s="223"/>
-      <c r="X4" s="225"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="217"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="219"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -20502,7 +20681,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="203" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -20520,7 +20699,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="204"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -20536,7 +20715,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="205"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -20552,7 +20731,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="206" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -20570,7 +20749,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="206"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -20586,7 +20765,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="207"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B319324A-4EED-4467-85CE-EF28F86113AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130956DC-3E46-44AF-9C9C-B7699BB7B831}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -2649,6 +2649,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2717,9 +2720,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3091,15 +3091,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="209"/>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="211"/>
+      <c r="P1" s="210"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="211"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
+      <c r="W1" s="211"/>
+      <c r="X1" s="212"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3124,62 +3124,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="213" t="s">
+      <c r="C4" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="214" t="s">
+      <c r="D4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="215" t="s">
+      <c r="E4" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="216"/>
-      <c r="G4" s="217" t="s">
+      <c r="F4" s="217"/>
+      <c r="G4" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="219" t="s">
+      <c r="H4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="219" t="s">
+      <c r="J4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="223" t="s">
+      <c r="L4" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="224"/>
-      <c r="Q4" s="224"/>
-      <c r="R4" s="224"/>
-      <c r="S4" s="224"/>
-      <c r="T4" s="224"/>
-      <c r="U4" s="224"/>
-      <c r="V4" s="225"/>
-      <c r="W4" s="224"/>
-      <c r="X4" s="226"/>
+      <c r="M4" s="225"/>
+      <c r="N4" s="225"/>
+      <c r="O4" s="225"/>
+      <c r="P4" s="225"/>
+      <c r="Q4" s="225"/>
+      <c r="R4" s="225"/>
+      <c r="S4" s="225"/>
+      <c r="T4" s="225"/>
+      <c r="U4" s="225"/>
+      <c r="V4" s="226"/>
+      <c r="W4" s="225"/>
+      <c r="X4" s="227"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="215"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="218"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="220"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="221"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5430,7 +5430,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="204" t="s">
+      <c r="G62" s="205" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -5448,7 +5448,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="205"/>
+      <c r="G63" s="206"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -5464,7 +5464,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="206"/>
+      <c r="G64" s="207"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -5480,7 +5480,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="207" t="s">
+      <c r="G65" s="208" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -5498,7 +5498,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="207"/>
+      <c r="G66" s="208"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -5514,7 +5514,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="208"/>
+      <c r="G67" s="209"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -5907,15 +5907,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="209">
+      <c r="P1" s="210">
         <v>46058</v>
       </c>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="211"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="212"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -5938,60 +5938,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="213" t="s">
+      <c r="C4" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="214" t="s">
+      <c r="D4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="215" t="s">
+      <c r="E4" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="216"/>
-      <c r="G4" s="217" t="s">
+      <c r="F4" s="217"/>
+      <c r="G4" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="219" t="s">
+      <c r="H4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="219" t="s">
+      <c r="J4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="223" t="s">
+      <c r="L4" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="224"/>
-      <c r="Q4" s="224"/>
-      <c r="R4" s="224"/>
-      <c r="S4" s="224"/>
-      <c r="T4" s="224"/>
-      <c r="U4" s="224"/>
-      <c r="V4" s="226"/>
+      <c r="M4" s="225"/>
+      <c r="N4" s="225"/>
+      <c r="O4" s="225"/>
+      <c r="P4" s="225"/>
+      <c r="Q4" s="225"/>
+      <c r="R4" s="225"/>
+      <c r="S4" s="225"/>
+      <c r="T4" s="225"/>
+      <c r="U4" s="225"/>
+      <c r="V4" s="227"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="215"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="218"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="220"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="221"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8800,7 +8800,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="204" t="s">
+      <c r="G62" s="205" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -8818,7 +8818,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="205"/>
+      <c r="G63" s="206"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -8834,7 +8834,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="206"/>
+      <c r="G64" s="207"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -8850,7 +8850,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="207" t="s">
+      <c r="G65" s="208" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -8868,7 +8868,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="207"/>
+      <c r="G66" s="208"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -8884,7 +8884,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="208"/>
+      <c r="G67" s="209"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -9278,17 +9278,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="209">
+      <c r="P1" s="210">
         <v>46083</v>
       </c>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="211"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
+      <c r="W1" s="211"/>
+      <c r="X1" s="212"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9313,62 +9313,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="213" t="s">
+      <c r="C4" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="214" t="s">
+      <c r="D4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="215" t="s">
+      <c r="E4" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="216"/>
-      <c r="G4" s="217" t="s">
+      <c r="F4" s="217"/>
+      <c r="G4" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="219" t="s">
+      <c r="H4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="219" t="s">
+      <c r="J4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="223" t="s">
+      <c r="L4" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="224"/>
-      <c r="Q4" s="224"/>
-      <c r="R4" s="224"/>
-      <c r="S4" s="224"/>
-      <c r="T4" s="224"/>
-      <c r="U4" s="224"/>
-      <c r="V4" s="225"/>
-      <c r="W4" s="224"/>
-      <c r="X4" s="226"/>
+      <c r="M4" s="225"/>
+      <c r="N4" s="225"/>
+      <c r="O4" s="225"/>
+      <c r="P4" s="225"/>
+      <c r="Q4" s="225"/>
+      <c r="R4" s="225"/>
+      <c r="S4" s="225"/>
+      <c r="T4" s="225"/>
+      <c r="U4" s="225"/>
+      <c r="V4" s="226"/>
+      <c r="W4" s="225"/>
+      <c r="X4" s="227"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="215"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="218"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="220"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="221"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -12862,7 +12862,7 @@
         <f>SUM(V8:V59)</f>
         <v>1114</v>
       </c>
-      <c r="W60" s="227">
+      <c r="W60" s="204">
         <f>SUM(W8:W59)</f>
         <v>394098</v>
       </c>
@@ -12875,7 +12875,7 @@
       <c r="V62" s="203"/>
     </row>
     <row r="63" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G63" s="204" t="s">
+      <c r="G63" s="205" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="60"/>
@@ -12893,7 +12893,7 @@
       <c r="S63" s="32"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="205"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="61"/>
       <c r="I64" s="61"/>
       <c r="J64" s="24" t="s">
@@ -12909,7 +12909,7 @@
       <c r="S64" s="35"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="206"/>
+      <c r="G65" s="207"/>
       <c r="H65" s="62"/>
       <c r="I65" s="62"/>
       <c r="J65" s="24" t="s">
@@ -12925,7 +12925,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="207" t="s">
+      <c r="G66" s="208" t="s">
         <v>64</v>
       </c>
       <c r="H66" s="63"/>
@@ -12943,7 +12943,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G67" s="207"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="63"/>
       <c r="I67" s="63"/>
       <c r="J67" s="24" t="s">
@@ -12959,7 +12959,7 @@
       <c r="S67" s="35"/>
     </row>
     <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="208"/>
+      <c r="G68" s="209"/>
       <c r="H68" s="64"/>
       <c r="I68" s="64"/>
       <c r="J68" s="25" t="s">
@@ -13354,17 +13354,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="209">
+      <c r="P1" s="210">
         <v>46084</v>
       </c>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="211"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
+      <c r="W1" s="211"/>
+      <c r="X1" s="212"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -13389,62 +13389,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="213" t="s">
+      <c r="C4" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="214" t="s">
+      <c r="D4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="215" t="s">
+      <c r="E4" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="216"/>
-      <c r="G4" s="217" t="s">
+      <c r="F4" s="217"/>
+      <c r="G4" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="219" t="s">
+      <c r="H4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="219" t="s">
+      <c r="J4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="223" t="s">
+      <c r="L4" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="224"/>
-      <c r="Q4" s="224"/>
-      <c r="R4" s="224"/>
-      <c r="S4" s="224"/>
-      <c r="T4" s="224"/>
-      <c r="U4" s="224"/>
-      <c r="V4" s="225"/>
-      <c r="W4" s="224"/>
-      <c r="X4" s="226"/>
+      <c r="M4" s="225"/>
+      <c r="N4" s="225"/>
+      <c r="O4" s="225"/>
+      <c r="P4" s="225"/>
+      <c r="Q4" s="225"/>
+      <c r="R4" s="225"/>
+      <c r="S4" s="225"/>
+      <c r="T4" s="225"/>
+      <c r="U4" s="225"/>
+      <c r="V4" s="226"/>
+      <c r="W4" s="225"/>
+      <c r="X4" s="227"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="215"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="218"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="220"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="221"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13609,30 +13609,38 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>67</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
-      <c r="G8" s="79"/>
+      <c r="G8" s="79">
+        <v>1</v>
+      </c>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="121"/>
       <c r="M8" s="121"/>
       <c r="N8" s="121"/>
       <c r="O8" s="121"/>
-      <c r="P8" s="121"/>
+      <c r="P8" s="121">
+        <v>1</v>
+      </c>
       <c r="Q8" s="129"/>
       <c r="R8" s="92">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="133">
         <f t="shared" si="1"/>
@@ -13641,15 +13649,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="116">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="139">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -13684,7 +13692,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>102</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
@@ -13692,7 +13702,7 @@
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
@@ -13724,7 +13734,7 @@
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -13759,30 +13769,40 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>80</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
-      <c r="G10" s="79"/>
+      <c r="G10" s="79">
+        <v>4</v>
+      </c>
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="121"/>
+      <c r="L10" s="121">
+        <v>1</v>
+      </c>
       <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
+      <c r="N10" s="121">
+        <v>2</v>
+      </c>
       <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
+      <c r="P10" s="121">
+        <v>1</v>
+      </c>
       <c r="Q10" s="129"/>
       <c r="R10" s="108">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S10" s="135">
         <f t="shared" si="1"/>
@@ -13791,15 +13811,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="116">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V10" s="143">
         <f>U10/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1824</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -13834,22 +13854,28 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>40</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
-      <c r="G11" s="79"/>
+      <c r="G11" s="79">
+        <v>1</v>
+      </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="121"/>
+      <c r="L11" s="121">
+        <v>1</v>
+      </c>
       <c r="M11" s="121"/>
       <c r="N11" s="121"/>
       <c r="O11" s="121"/>
@@ -13857,7 +13883,7 @@
       <c r="Q11" s="129"/>
       <c r="R11" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="133">
         <f t="shared" si="1"/>
@@ -13866,15 +13892,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="116">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="139">
         <f>U11/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -13909,7 +13935,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -13917,7 +13945,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -13949,7 +13977,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -13984,47 +14012,63 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>4022</v>
+      </c>
+      <c r="D13" s="123">
+        <v>19</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="G13" s="81">
+        <v>22</v>
+      </c>
+      <c r="H13" s="82">
+        <v>23</v>
+      </c>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K13" s="55"/>
       <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
+      <c r="M13" s="130">
+        <v>9</v>
+      </c>
+      <c r="N13" s="130">
+        <v>7</v>
+      </c>
+      <c r="O13" s="130">
+        <v>14</v>
+      </c>
+      <c r="P13" s="130">
+        <v>15</v>
+      </c>
       <c r="Q13" s="131"/>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>95996</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -14066,7 +14110,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -14074,7 +14120,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -14106,7 +14152,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -14366,7 +14412,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -14374,7 +14422,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -14406,7 +14454,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -14516,7 +14564,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -14524,7 +14574,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -14556,7 +14606,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -14591,7 +14641,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -14599,7 +14651,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -14631,7 +14683,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -14666,7 +14718,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -14674,7 +14728,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -14706,7 +14760,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -14741,7 +14795,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -14749,7 +14805,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -14781,7 +14837,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -14823,7 +14879,9 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="119">
+        <v>47</v>
+      </c>
       <c r="D24" s="120"/>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
@@ -14831,7 +14889,7 @@
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
@@ -14863,7 +14921,7 @@
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -14905,7 +14963,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -14913,7 +14973,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -14945,7 +15005,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -14980,19 +15040,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="C26" s="119">
+        <v>125</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
       <c r="E26" s="121"/>
       <c r="F26" s="121"/>
       <c r="G26" s="79"/>
       <c r="H26" s="76"/>
       <c r="I26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J26" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="121"/>
@@ -15020,7 +15084,7 @@
       </c>
       <c r="W26" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3011</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -15036,7 +15100,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="119"/>
+      <c r="C27" s="119">
+        <v>20</v>
+      </c>
       <c r="D27" s="120"/>
       <c r="E27" s="121"/>
       <c r="F27" s="121"/>
@@ -15044,7 +15110,7 @@
       <c r="H27" s="76"/>
       <c r="I27" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J27" s="80">
         <f t="shared" si="4"/>
@@ -15076,7 +15142,7 @@
       </c>
       <c r="W27" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -15154,15 +15220,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="119"/>
+      <c r="C29" s="119">
+        <v>103</v>
+      </c>
       <c r="D29" s="120"/>
       <c r="E29" s="121"/>
       <c r="F29" s="121"/>
-      <c r="G29" s="79"/>
+      <c r="G29" s="79">
+        <v>3</v>
+      </c>
       <c r="H29" s="76"/>
       <c r="I29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29" s="80">
         <f t="shared" si="4"/>
@@ -15173,11 +15243,13 @@
       <c r="M29" s="121"/>
       <c r="N29" s="121"/>
       <c r="O29" s="121"/>
-      <c r="P29" s="121"/>
+      <c r="P29" s="121">
+        <v>3</v>
+      </c>
       <c r="Q29" s="129"/>
       <c r="R29" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S29" s="133">
         <f t="shared" si="7"/>
@@ -15186,15 +15258,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V29" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -15213,7 +15285,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="119"/>
+      <c r="C30" s="119">
+        <v>10</v>
+      </c>
       <c r="D30" s="120"/>
       <c r="E30" s="121"/>
       <c r="F30" s="121"/>
@@ -15221,7 +15295,7 @@
       <c r="H30" s="76"/>
       <c r="I30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="80">
         <f t="shared" si="4"/>
@@ -15253,7 +15327,7 @@
       </c>
       <c r="W30" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -15265,7 +15339,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="119">
+        <v>60</v>
+      </c>
       <c r="D31" s="120"/>
       <c r="E31" s="121"/>
       <c r="F31" s="121"/>
@@ -15273,7 +15349,7 @@
       <c r="H31" s="76"/>
       <c r="I31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J31" s="80">
         <f t="shared" si="4"/>
@@ -15305,7 +15381,7 @@
       </c>
       <c r="W31" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -15317,15 +15393,19 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="119"/>
+      <c r="C32" s="119">
+        <v>16</v>
+      </c>
       <c r="D32" s="120"/>
       <c r="E32" s="121"/>
       <c r="F32" s="121"/>
-      <c r="G32" s="79"/>
+      <c r="G32" s="79">
+        <v>1</v>
+      </c>
       <c r="H32" s="76"/>
       <c r="I32" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J32" s="80">
         <f t="shared" si="4"/>
@@ -15334,13 +15414,15 @@
       <c r="K32" s="41"/>
       <c r="L32" s="121"/>
       <c r="M32" s="121"/>
-      <c r="N32" s="121"/>
+      <c r="N32" s="121">
+        <v>1</v>
+      </c>
       <c r="O32" s="121"/>
       <c r="P32" s="121"/>
       <c r="Q32" s="129"/>
       <c r="R32" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="133">
         <f t="shared" si="7"/>
@@ -15349,15 +15431,15 @@
       <c r="T32" s="41"/>
       <c r="U32" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V32" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -15421,7 +15503,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="119"/>
+      <c r="C34" s="119">
+        <v>3</v>
+      </c>
       <c r="D34" s="120"/>
       <c r="E34" s="121"/>
       <c r="F34" s="121"/>
@@ -15429,7 +15513,7 @@
       <c r="H34" s="76"/>
       <c r="I34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="80">
         <f t="shared" si="4"/>
@@ -15461,7 +15545,7 @@
       </c>
       <c r="W34" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -15473,19 +15557,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="120"/>
+      <c r="C35" s="119">
+        <v>145</v>
+      </c>
+      <c r="D35" s="120">
+        <v>17</v>
+      </c>
       <c r="E35" s="121"/>
       <c r="F35" s="121"/>
       <c r="G35" s="79"/>
       <c r="H35" s="76"/>
       <c r="I35" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="J35" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="121"/>
@@ -15513,7 +15601,7 @@
       </c>
       <c r="W35" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3497</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -15629,30 +15717,42 @@
       <c r="B38" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="122"/>
-      <c r="D38" s="123"/>
+      <c r="C38" s="122">
+        <v>4636</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
       <c r="E38" s="124"/>
       <c r="F38" s="124"/>
-      <c r="G38" s="81"/>
+      <c r="G38" s="81">
+        <v>138</v>
+      </c>
       <c r="H38" s="82"/>
       <c r="I38" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4498</v>
       </c>
       <c r="J38" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="53"/>
-      <c r="L38" s="130"/>
+      <c r="L38" s="130">
+        <v>31</v>
+      </c>
       <c r="M38" s="130"/>
-      <c r="N38" s="130"/>
+      <c r="N38" s="130">
+        <v>71</v>
+      </c>
       <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
+      <c r="P38" s="130">
+        <v>36</v>
+      </c>
       <c r="Q38" s="131"/>
       <c r="R38" s="106">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="S38" s="134">
         <f t="shared" si="7"/>
@@ -15661,15 +15761,15 @@
       <c r="T38" s="53"/>
       <c r="U38" s="140">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>828</v>
       </c>
       <c r="V38" s="144">
         <f>U38/6</f>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="W38" s="142">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>26990</v>
       </c>
       <c r="X38" s="54"/>
     </row>
@@ -15681,7 +15781,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="119"/>
+      <c r="C39" s="119">
+        <v>19</v>
+      </c>
       <c r="D39" s="120"/>
       <c r="E39" s="121"/>
       <c r="F39" s="121"/>
@@ -15689,7 +15791,7 @@
       <c r="H39" s="76"/>
       <c r="I39" s="79">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J39" s="80">
         <f t="shared" si="4"/>
@@ -15721,7 +15823,7 @@
       </c>
       <c r="W39" s="138">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -15785,15 +15887,19 @@
       <c r="B41" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="155"/>
+      <c r="C41" s="155">
+        <v>559</v>
+      </c>
       <c r="D41" s="156"/>
       <c r="E41" s="157"/>
       <c r="F41" s="157"/>
-      <c r="G41" s="158"/>
+      <c r="G41" s="158">
+        <v>1</v>
+      </c>
       <c r="H41" s="159"/>
       <c r="I41" s="160">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="J41" s="161">
         <f t="shared" si="4"/>
@@ -15804,11 +15910,13 @@
       <c r="M41" s="163"/>
       <c r="N41" s="163"/>
       <c r="O41" s="163"/>
-      <c r="P41" s="163"/>
+      <c r="P41" s="163">
+        <v>1</v>
+      </c>
       <c r="Q41" s="164"/>
       <c r="R41" s="165">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="166">
         <f t="shared" si="7"/>
@@ -15817,15 +15925,15 @@
       <c r="T41" s="162"/>
       <c r="U41" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V41" s="168">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="168">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>13392</v>
       </c>
       <c r="X41" s="169"/>
     </row>
@@ -15837,30 +15945,40 @@
       <c r="B42" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="172"/>
+      <c r="C42" s="172">
+        <v>1485</v>
+      </c>
       <c r="D42" s="173"/>
       <c r="E42" s="174"/>
       <c r="F42" s="174"/>
-      <c r="G42" s="175"/>
+      <c r="G42" s="175">
+        <v>29</v>
+      </c>
       <c r="H42" s="176"/>
       <c r="I42" s="175">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1456</v>
       </c>
       <c r="J42" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K42" s="178"/>
-      <c r="L42" s="174"/>
+      <c r="L42" s="174">
+        <v>7</v>
+      </c>
       <c r="M42" s="174"/>
-      <c r="N42" s="174"/>
+      <c r="N42" s="174">
+        <v>2</v>
+      </c>
       <c r="O42" s="174"/>
-      <c r="P42" s="174"/>
+      <c r="P42" s="174">
+        <v>20</v>
+      </c>
       <c r="Q42" s="179"/>
       <c r="R42" s="180">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S42" s="181">
         <f t="shared" si="7"/>
@@ -15869,15 +15987,15 @@
       <c r="T42" s="178"/>
       <c r="U42" s="182">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="V42" s="183">
         <f>U42/12</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="W42" s="184">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>17472</v>
       </c>
       <c r="X42" s="185"/>
     </row>
@@ -15932,30 +16050,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="122"/>
-      <c r="D44" s="123"/>
+      <c r="C44" s="122">
+        <v>33791</v>
+      </c>
+      <c r="D44" s="123">
+        <v>4</v>
+      </c>
       <c r="E44" s="124"/>
       <c r="F44" s="124"/>
-      <c r="G44" s="81"/>
+      <c r="G44" s="81">
+        <v>897</v>
+      </c>
       <c r="H44" s="82"/>
       <c r="I44" s="76">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>32894</v>
       </c>
       <c r="J44" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" s="53"/>
-      <c r="L44" s="130"/>
+      <c r="L44" s="130">
+        <v>382</v>
+      </c>
       <c r="M44" s="130"/>
-      <c r="N44" s="130"/>
+      <c r="N44" s="130">
+        <v>224</v>
+      </c>
       <c r="O44" s="130"/>
-      <c r="P44" s="130"/>
+      <c r="P44" s="130">
+        <v>291</v>
+      </c>
       <c r="Q44" s="131"/>
       <c r="R44" s="187">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="S44" s="188">
         <f t="shared" si="7"/>
@@ -15964,15 +16094,15 @@
       <c r="T44" s="53"/>
       <c r="U44" s="140">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5382</v>
       </c>
       <c r="V44" s="139">
         <f>U44/6</f>
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="W44" s="142">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>197368</v>
       </c>
       <c r="X44" s="54"/>
       <c r="Z44" s="47"/>
@@ -16080,7 +16210,9 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="119"/>
+      <c r="C47" s="119">
+        <v>4</v>
+      </c>
       <c r="D47" s="120"/>
       <c r="E47" s="121"/>
       <c r="F47" s="121"/>
@@ -16088,7 +16220,7 @@
       <c r="H47" s="76"/>
       <c r="I47" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="80">
         <f t="shared" si="4"/>
@@ -16120,7 +16252,7 @@
       </c>
       <c r="W47" s="138">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X47" s="27"/>
     </row>
@@ -16132,22 +16264,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="150"/>
-      <c r="D48" s="151"/>
+      <c r="C48" s="150">
+        <v>2355</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
       <c r="E48" s="130"/>
       <c r="F48" s="130"/>
-      <c r="G48" s="152"/>
+      <c r="G48" s="152">
+        <v>3</v>
+      </c>
       <c r="H48" s="148"/>
       <c r="I48" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="J48" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="53"/>
-      <c r="L48" s="130"/>
+      <c r="L48" s="130">
+        <v>3</v>
+      </c>
       <c r="M48" s="130"/>
       <c r="N48" s="130"/>
       <c r="O48" s="130"/>
@@ -16155,7 +16295,7 @@
       <c r="Q48" s="131"/>
       <c r="R48" s="106">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S48" s="153">
         <f t="shared" si="7"/>
@@ -16164,15 +16304,15 @@
       <c r="T48" s="53"/>
       <c r="U48" s="140">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V48" s="144">
         <f>U48/6</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W48" s="142">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>14116</v>
       </c>
       <c r="X48" s="54"/>
     </row>
@@ -16184,7 +16324,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="119"/>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
       <c r="D49" s="120"/>
       <c r="E49" s="121"/>
       <c r="F49" s="121"/>
@@ -16192,7 +16334,7 @@
       <c r="H49" s="76"/>
       <c r="I49" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="80">
         <f t="shared" si="4"/>
@@ -16224,7 +16366,7 @@
       </c>
       <c r="W49" s="138">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -16340,7 +16482,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="150"/>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
       <c r="D52" s="151"/>
       <c r="E52" s="130"/>
       <c r="F52" s="130"/>
@@ -16348,7 +16492,7 @@
       <c r="H52" s="148"/>
       <c r="I52" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="149">
         <f t="shared" si="4"/>
@@ -16380,7 +16524,7 @@
       </c>
       <c r="W52" s="142">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="54"/>
     </row>
@@ -16444,7 +16588,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="119"/>
+      <c r="C54" s="119">
+        <v>6</v>
+      </c>
       <c r="D54" s="120"/>
       <c r="E54" s="121"/>
       <c r="F54" s="121"/>
@@ -16452,7 +16598,7 @@
       <c r="H54" s="76"/>
       <c r="I54" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J54" s="80">
         <f t="shared" si="4"/>
@@ -16484,7 +16630,7 @@
       </c>
       <c r="W54" s="138">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -16699,11 +16845,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>47772</v>
       </c>
       <c r="D60" s="57">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -16712,40 +16858,40 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H60" s="59">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I60" s="59">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>46672</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="77">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="M60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="O60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="Q60" s="78">
         <f t="shared" si="20"/>
@@ -16753,24 +16899,24 @@
       </c>
       <c r="R60" s="91">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="S60" s="90">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>7368</v>
       </c>
       <c r="V60" s="111">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="99">
+        <v>1100</v>
+      </c>
+      <c r="W60" s="204">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>386707</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -16778,7 +16924,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="204" t="s">
+      <c r="G62" s="205" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -16796,7 +16942,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="205"/>
+      <c r="G63" s="206"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -16812,7 +16958,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="206"/>
+      <c r="G64" s="207"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -16828,7 +16974,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="207" t="s">
+      <c r="G65" s="208" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -16846,7 +16992,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="207"/>
+      <c r="G66" s="208"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -16862,7 +17008,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="208"/>
+      <c r="G67" s="209"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -17257,17 +17403,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="209">
+      <c r="P1" s="210">
         <v>46085</v>
       </c>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="211"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
+      <c r="W1" s="211"/>
+      <c r="X1" s="212"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -17292,62 +17438,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="213" t="s">
+      <c r="C4" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="214" t="s">
+      <c r="D4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="215" t="s">
+      <c r="E4" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="216"/>
-      <c r="G4" s="217" t="s">
+      <c r="F4" s="217"/>
+      <c r="G4" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="219" t="s">
+      <c r="H4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="219" t="s">
+      <c r="J4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="223" t="s">
+      <c r="L4" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="224"/>
-      <c r="Q4" s="224"/>
-      <c r="R4" s="224"/>
-      <c r="S4" s="224"/>
-      <c r="T4" s="224"/>
-      <c r="U4" s="224"/>
-      <c r="V4" s="225"/>
-      <c r="W4" s="224"/>
-      <c r="X4" s="226"/>
+      <c r="M4" s="225"/>
+      <c r="N4" s="225"/>
+      <c r="O4" s="225"/>
+      <c r="P4" s="225"/>
+      <c r="Q4" s="225"/>
+      <c r="R4" s="225"/>
+      <c r="S4" s="225"/>
+      <c r="T4" s="225"/>
+      <c r="U4" s="225"/>
+      <c r="V4" s="226"/>
+      <c r="W4" s="225"/>
+      <c r="X4" s="227"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="215"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="218"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="220"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="221"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -20681,7 +20827,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="204" t="s">
+      <c r="G62" s="205" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -20699,7 +20845,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="205"/>
+      <c r="G63" s="206"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -20715,7 +20861,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="206"/>
+      <c r="G64" s="207"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -20731,7 +20877,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="207" t="s">
+      <c r="G65" s="208" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -20749,7 +20895,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="207"/>
+      <c r="G66" s="208"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -20765,7 +20911,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="208"/>
+      <c r="G67" s="209"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130956DC-3E46-44AF-9C9C-B7699BB7B831}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA271396-3170-4527-AE1B-C391042DEBEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -18,12 +18,14 @@
     <sheet name="03,02" sheetId="91" r:id="rId3"/>
     <sheet name="03,03" sheetId="92" r:id="rId4"/>
     <sheet name="03,04" sheetId="93" r:id="rId5"/>
+    <sheet name="03,05" sheetId="94" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02,05 PROMO'!$A$1:$W$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03,02'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'03,03'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'03,04'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'03,05'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -385,8 +387,94 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{51370760-45DE-4990-B7D9-B05FAC41B28D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{363A9AF1-D2D1-488B-B2AA-68DBFE71FB90}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{395E873B-B4FE-406E-8636-AC1C79D8012E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2038,7 +2126,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2652,6 +2740,15 @@
     <xf numFmtId="167" fontId="2" fillId="5" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3091,15 +3188,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="210"/>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
-      <c r="W1" s="211"/>
-      <c r="X1" s="212"/>
+      <c r="P1" s="213"/>
+      <c r="Q1" s="214"/>
+      <c r="R1" s="214"/>
+      <c r="S1" s="214"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="215"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3124,62 +3221,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="216" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="217" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="215" t="s">
+      <c r="D4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="216" t="s">
+      <c r="E4" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="217"/>
-      <c r="G4" s="218" t="s">
+      <c r="F4" s="220"/>
+      <c r="G4" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="220" t="s">
+      <c r="H4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="222" t="s">
+      <c r="I4" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220" t="s">
+      <c r="J4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="224" t="s">
+      <c r="L4" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="225"/>
-      <c r="N4" s="225"/>
-      <c r="O4" s="225"/>
-      <c r="P4" s="225"/>
-      <c r="Q4" s="225"/>
-      <c r="R4" s="225"/>
-      <c r="S4" s="225"/>
-      <c r="T4" s="225"/>
-      <c r="U4" s="225"/>
-      <c r="V4" s="226"/>
-      <c r="W4" s="225"/>
-      <c r="X4" s="227"/>
+      <c r="M4" s="228"/>
+      <c r="N4" s="228"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="228"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="228"/>
+      <c r="X4" s="230"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="213"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="218"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="219"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="221"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="224"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5430,7 +5527,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="205" t="s">
+      <c r="G62" s="208" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -5448,7 +5545,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="206"/>
+      <c r="G63" s="209"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -5464,7 +5561,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="207"/>
+      <c r="G64" s="210"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -5480,7 +5577,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="208" t="s">
+      <c r="G65" s="211" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -5498,7 +5595,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="208"/>
+      <c r="G66" s="211"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -5514,7 +5611,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="209"/>
+      <c r="G67" s="212"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -5907,15 +6004,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="210">
+      <c r="P1" s="213">
         <v>46058</v>
       </c>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="212"/>
+      <c r="Q1" s="214"/>
+      <c r="R1" s="214"/>
+      <c r="S1" s="214"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="215"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -5938,60 +6035,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="216" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="217" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="215" t="s">
+      <c r="D4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="216" t="s">
+      <c r="E4" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="217"/>
-      <c r="G4" s="218" t="s">
+      <c r="F4" s="220"/>
+      <c r="G4" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="220" t="s">
+      <c r="H4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="222" t="s">
+      <c r="I4" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220" t="s">
+      <c r="J4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="224" t="s">
+      <c r="L4" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="225"/>
-      <c r="N4" s="225"/>
-      <c r="O4" s="225"/>
-      <c r="P4" s="225"/>
-      <c r="Q4" s="225"/>
-      <c r="R4" s="225"/>
-      <c r="S4" s="225"/>
-      <c r="T4" s="225"/>
-      <c r="U4" s="225"/>
-      <c r="V4" s="227"/>
+      <c r="M4" s="228"/>
+      <c r="N4" s="228"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="228"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="230"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="213"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="218"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="219"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="221"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="224"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8800,7 +8897,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="205" t="s">
+      <c r="G62" s="208" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -8818,7 +8915,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="206"/>
+      <c r="G63" s="209"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -8834,7 +8931,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="207"/>
+      <c r="G64" s="210"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -8850,7 +8947,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="208" t="s">
+      <c r="G65" s="211" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -8868,7 +8965,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="208"/>
+      <c r="G66" s="211"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -8884,7 +8981,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="209"/>
+      <c r="G67" s="212"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -9278,17 +9375,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="210">
+      <c r="P1" s="213">
         <v>46083</v>
       </c>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
-      <c r="W1" s="211"/>
-      <c r="X1" s="212"/>
+      <c r="Q1" s="214"/>
+      <c r="R1" s="214"/>
+      <c r="S1" s="214"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="215"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9313,62 +9410,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="216" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="217" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="215" t="s">
+      <c r="D4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="216" t="s">
+      <c r="E4" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="217"/>
-      <c r="G4" s="218" t="s">
+      <c r="F4" s="220"/>
+      <c r="G4" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="220" t="s">
+      <c r="H4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="222" t="s">
+      <c r="I4" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220" t="s">
+      <c r="J4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="224" t="s">
+      <c r="L4" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="225"/>
-      <c r="N4" s="225"/>
-      <c r="O4" s="225"/>
-      <c r="P4" s="225"/>
-      <c r="Q4" s="225"/>
-      <c r="R4" s="225"/>
-      <c r="S4" s="225"/>
-      <c r="T4" s="225"/>
-      <c r="U4" s="225"/>
-      <c r="V4" s="226"/>
-      <c r="W4" s="225"/>
-      <c r="X4" s="227"/>
+      <c r="M4" s="228"/>
+      <c r="N4" s="228"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="228"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="228"/>
+      <c r="X4" s="230"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="213"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="218"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="219"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="221"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="224"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -12875,7 +12972,7 @@
       <c r="V62" s="203"/>
     </row>
     <row r="63" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G63" s="205" t="s">
+      <c r="G63" s="208" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="60"/>
@@ -12893,7 +12990,7 @@
       <c r="S63" s="32"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="206"/>
+      <c r="G64" s="209"/>
       <c r="H64" s="61"/>
       <c r="I64" s="61"/>
       <c r="J64" s="24" t="s">
@@ -12909,7 +13006,7 @@
       <c r="S64" s="35"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="207"/>
+      <c r="G65" s="210"/>
       <c r="H65" s="62"/>
       <c r="I65" s="62"/>
       <c r="J65" s="24" t="s">
@@ -12925,7 +13022,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="208" t="s">
+      <c r="G66" s="211" t="s">
         <v>64</v>
       </c>
       <c r="H66" s="63"/>
@@ -12943,7 +13040,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G67" s="208"/>
+      <c r="G67" s="211"/>
       <c r="H67" s="63"/>
       <c r="I67" s="63"/>
       <c r="J67" s="24" t="s">
@@ -12959,7 +13056,7 @@
       <c r="S67" s="35"/>
     </row>
     <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="209"/>
+      <c r="G68" s="212"/>
       <c r="H68" s="64"/>
       <c r="I68" s="64"/>
       <c r="J68" s="25" t="s">
@@ -13354,17 +13451,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="210">
+      <c r="P1" s="213">
         <v>46084</v>
       </c>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
-      <c r="W1" s="211"/>
-      <c r="X1" s="212"/>
+      <c r="Q1" s="214"/>
+      <c r="R1" s="214"/>
+      <c r="S1" s="214"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="215"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -13389,62 +13486,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="216" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="217" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="215" t="s">
+      <c r="D4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="216" t="s">
+      <c r="E4" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="217"/>
-      <c r="G4" s="218" t="s">
+      <c r="F4" s="220"/>
+      <c r="G4" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="220" t="s">
+      <c r="H4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="222" t="s">
+      <c r="I4" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220" t="s">
+      <c r="J4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="224" t="s">
+      <c r="L4" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="225"/>
-      <c r="N4" s="225"/>
-      <c r="O4" s="225"/>
-      <c r="P4" s="225"/>
-      <c r="Q4" s="225"/>
-      <c r="R4" s="225"/>
-      <c r="S4" s="225"/>
-      <c r="T4" s="225"/>
-      <c r="U4" s="225"/>
-      <c r="V4" s="226"/>
-      <c r="W4" s="225"/>
-      <c r="X4" s="227"/>
+      <c r="M4" s="228"/>
+      <c r="N4" s="228"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="228"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="228"/>
+      <c r="X4" s="230"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="213"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="218"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="219"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="221"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="224"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -16924,7 +17021,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="205" t="s">
+      <c r="G62" s="208" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -16942,7 +17039,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="206"/>
+      <c r="G63" s="209"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -16958,7 +17055,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="207"/>
+      <c r="G64" s="210"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -16974,7 +17071,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="208" t="s">
+      <c r="G65" s="211" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -16992,7 +17089,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="208"/>
+      <c r="G66" s="211"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -17008,7 +17105,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="209"/>
+      <c r="G67" s="212"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -17403,17 +17500,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="210">
+      <c r="P1" s="213">
         <v>46085</v>
       </c>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
-      <c r="W1" s="211"/>
-      <c r="X1" s="212"/>
+      <c r="Q1" s="214"/>
+      <c r="R1" s="214"/>
+      <c r="S1" s="214"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="215"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -17438,62 +17535,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="216" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="217" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="215" t="s">
+      <c r="D4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="216" t="s">
+      <c r="E4" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="217"/>
-      <c r="G4" s="218" t="s">
+      <c r="F4" s="220"/>
+      <c r="G4" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="220" t="s">
+      <c r="H4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="222" t="s">
+      <c r="I4" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220" t="s">
+      <c r="J4" s="223" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="224" t="s">
+      <c r="L4" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="225"/>
-      <c r="N4" s="225"/>
-      <c r="O4" s="225"/>
-      <c r="P4" s="225"/>
-      <c r="Q4" s="225"/>
-      <c r="R4" s="225"/>
-      <c r="S4" s="225"/>
-      <c r="T4" s="225"/>
-      <c r="U4" s="225"/>
-      <c r="V4" s="226"/>
-      <c r="W4" s="225"/>
-      <c r="X4" s="227"/>
+      <c r="M4" s="228"/>
+      <c r="N4" s="228"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="228"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="228"/>
+      <c r="X4" s="230"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="213"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="218"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="219"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="221"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="224"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17658,19 +17755,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>66</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
       <c r="G8" s="79"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="121"/>
@@ -17698,7 +17799,7 @@
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -17733,7 +17834,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>102</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
@@ -17741,7 +17844,7 @@
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
@@ -17773,7 +17876,7 @@
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -17808,15 +17911,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>76</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
-      <c r="G10" s="79"/>
+      <c r="G10" s="79">
+        <v>8</v>
+      </c>
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
@@ -17827,11 +17934,13 @@
       <c r="M10" s="121"/>
       <c r="N10" s="121"/>
       <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
+      <c r="P10" s="121">
+        <v>8</v>
+      </c>
       <c r="Q10" s="129"/>
       <c r="R10" s="108">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S10" s="135">
         <f t="shared" si="1"/>
@@ -17840,15 +17949,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="116">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V10" s="143">
         <f>U10/24</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -17883,15 +17992,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>39</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
-      <c r="G11" s="79"/>
+      <c r="G11" s="79">
+        <v>3</v>
+      </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
@@ -17900,13 +18013,17 @@
       <c r="K11" s="41"/>
       <c r="L11" s="121"/>
       <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
+      <c r="N11" s="121">
+        <v>2</v>
+      </c>
       <c r="O11" s="121"/>
-      <c r="P11" s="121"/>
+      <c r="P11" s="121">
+        <v>1</v>
+      </c>
       <c r="Q11" s="129"/>
       <c r="R11" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" s="133">
         <f t="shared" si="1"/>
@@ -17915,15 +18032,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="116">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V11" s="139">
         <f>U11/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -17958,7 +18075,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -17966,7 +18085,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -17998,7 +18117,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -18033,47 +18152,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>3999</v>
+      </c>
+      <c r="D13" s="123">
+        <v>20</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="G13" s="81">
+        <v>40</v>
+      </c>
+      <c r="H13" s="82">
+        <v>26</v>
+      </c>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3959</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="K13" s="55"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="131"/>
+      <c r="L13" s="130">
+        <v>18</v>
+      </c>
+      <c r="M13" s="130">
+        <v>14</v>
+      </c>
+      <c r="N13" s="130">
+        <v>14</v>
+      </c>
+      <c r="O13" s="130">
+        <v>5</v>
+      </c>
+      <c r="P13" s="130">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="131">
+        <v>7</v>
+      </c>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>95010</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -18115,7 +18254,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -18123,7 +18264,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -18155,7 +18296,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -18415,7 +18556,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -18423,7 +18566,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -18455,7 +18598,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -18565,7 +18708,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -18573,7 +18718,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -18605,7 +18750,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -18640,7 +18785,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -18648,7 +18795,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -18680,7 +18827,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -18715,7 +18862,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -18723,7 +18872,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -18755,7 +18904,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -18790,7 +18939,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -18798,7 +18949,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -18830,7 +18981,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -18872,7 +19023,9 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="119">
+        <v>47</v>
+      </c>
       <c r="D24" s="120"/>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
@@ -18880,7 +19033,7 @@
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
@@ -18912,7 +19065,7 @@
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -18954,7 +19107,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -18962,7 +19117,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -18994,7 +19149,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -19029,6 +19184,3991 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="C26" s="119">
+        <v>125</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="79">
+        <v>2</v>
+      </c>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76">
+        <f t="shared" si="4"/>
+        <v>123</v>
+      </c>
+      <c r="J26" s="80">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="121">
+        <v>2</v>
+      </c>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="129"/>
+      <c r="R26" s="92">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S26" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="116">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V26" s="139">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W26" s="138">
+        <f t="shared" si="8"/>
+        <v>2963</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="119">
+        <v>20</v>
+      </c>
+      <c r="D27" s="120"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="J27" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="138">
+        <f t="shared" si="8"/>
+        <v>480</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="119"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="119">
+        <v>100</v>
+      </c>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="79">
+        <v>3</v>
+      </c>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76">
+        <f t="shared" si="4"/>
+        <v>97</v>
+      </c>
+      <c r="J29" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="121"/>
+      <c r="P29" s="121"/>
+      <c r="Q29" s="129"/>
+      <c r="R29" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="138">
+        <f t="shared" si="8"/>
+        <v>2328</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="119">
+        <v>10</v>
+      </c>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J30" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="129"/>
+      <c r="R30" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="138">
+        <f t="shared" si="8"/>
+        <v>240</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="119">
+        <v>60</v>
+      </c>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J31" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="129"/>
+      <c r="R31" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="138">
+        <f t="shared" si="8"/>
+        <v>1440</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="119">
+        <v>15</v>
+      </c>
+      <c r="D32" s="120"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="J32" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="138">
+        <f t="shared" si="8"/>
+        <v>360</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="129"/>
+      <c r="R33" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="119">
+        <v>3</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J34" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="129"/>
+      <c r="R34" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="138">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="119">
+        <v>145</v>
+      </c>
+      <c r="D35" s="120">
+        <v>17</v>
+      </c>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="79">
+        <v>10</v>
+      </c>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="J35" s="80">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="121">
+        <v>10</v>
+      </c>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="129"/>
+      <c r="R35" s="92">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S35" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="116">
+        <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="V35" s="139">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="W35" s="138">
+        <f t="shared" si="8"/>
+        <v>3257</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="121"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="129"/>
+      <c r="R36" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="119"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="129"/>
+      <c r="R37" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="122">
+        <v>4498</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="81">
+        <v>146</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="148">
+        <f t="shared" si="4"/>
+        <v>4352</v>
+      </c>
+      <c r="J38" s="149">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K38" s="53"/>
+      <c r="L38" s="130">
+        <v>117</v>
+      </c>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130">
+        <v>29</v>
+      </c>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="106">
+        <f t="shared" si="7"/>
+        <v>146</v>
+      </c>
+      <c r="S38" s="134">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="53"/>
+      <c r="U38" s="140">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>876</v>
+      </c>
+      <c r="V38" s="144">
+        <f>U38/6</f>
+        <v>146</v>
+      </c>
+      <c r="W38" s="142">
+        <f>I38*6+J38</f>
+        <v>26114</v>
+      </c>
+      <c r="X38" s="54"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="119">
+        <v>19</v>
+      </c>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="79">
+        <v>1</v>
+      </c>
+      <c r="H39" s="76"/>
+      <c r="I39" s="79">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="J39" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="121"/>
+      <c r="P39" s="121">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="129"/>
+      <c r="R39" s="105">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S39" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="116">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>24</v>
+      </c>
+      <c r="V39" s="118">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W39" s="138">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>432</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="129"/>
+      <c r="R40" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="145">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="146">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="101"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="155">
+        <v>558</v>
+      </c>
+      <c r="D41" s="156"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="159"/>
+      <c r="I41" s="160">
+        <f t="shared" si="4"/>
+        <v>558</v>
+      </c>
+      <c r="J41" s="161">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="162"/>
+      <c r="L41" s="163"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="163"/>
+      <c r="O41" s="163"/>
+      <c r="P41" s="163"/>
+      <c r="Q41" s="164"/>
+      <c r="R41" s="165">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="166">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="162"/>
+      <c r="U41" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="168">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="168">
+        <f t="shared" si="10"/>
+        <v>13392</v>
+      </c>
+      <c r="X41" s="169"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="171" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="172">
+        <v>1456</v>
+      </c>
+      <c r="D42" s="173"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="175">
+        <v>6</v>
+      </c>
+      <c r="H42" s="176"/>
+      <c r="I42" s="175">
+        <f t="shared" si="4"/>
+        <v>1450</v>
+      </c>
+      <c r="J42" s="177">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="178"/>
+      <c r="L42" s="174">
+        <v>6</v>
+      </c>
+      <c r="M42" s="174"/>
+      <c r="N42" s="174"/>
+      <c r="O42" s="174"/>
+      <c r="P42" s="174"/>
+      <c r="Q42" s="179"/>
+      <c r="R42" s="180">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="S42" s="181">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="178"/>
+      <c r="U42" s="182">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>72</v>
+      </c>
+      <c r="V42" s="183">
+        <f>U42/12</f>
+        <v>6</v>
+      </c>
+      <c r="W42" s="184">
+        <f>I42*12+J42</f>
+        <v>17400</v>
+      </c>
+      <c r="X42" s="185"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="119"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="116"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="122">
+        <v>32894</v>
+      </c>
+      <c r="D44" s="123">
+        <v>4</v>
+      </c>
+      <c r="E44" s="124"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="81">
+        <v>955</v>
+      </c>
+      <c r="H44" s="82"/>
+      <c r="I44" s="76">
+        <f>C44+E44-G44</f>
+        <v>31939</v>
+      </c>
+      <c r="J44" s="186">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K44" s="53"/>
+      <c r="L44" s="130">
+        <v>359</v>
+      </c>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130">
+        <v>326</v>
+      </c>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130">
+        <v>270</v>
+      </c>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="187">
+        <f t="shared" si="7"/>
+        <v>955</v>
+      </c>
+      <c r="S44" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="53"/>
+      <c r="U44" s="140">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>5730</v>
+      </c>
+      <c r="V44" s="139">
+        <f>U44/6</f>
+        <v>955</v>
+      </c>
+      <c r="W44" s="142">
+        <f>I44*6+J44</f>
+        <v>191638</v>
+      </c>
+      <c r="X44" s="54"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="119"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="121"/>
+      <c r="G45" s="79"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="129"/>
+      <c r="R45" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="116"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="138"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="119"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="121"/>
+      <c r="P46" s="121"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="137">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="116">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="143">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="138">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="119">
+        <v>4</v>
+      </c>
+      <c r="D47" s="120"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J47" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="121"/>
+      <c r="P47" s="121"/>
+      <c r="Q47" s="129"/>
+      <c r="R47" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="139">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="138">
+        <f t="shared" si="13"/>
+        <v>96</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="150">
+        <v>2352</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="152">
+        <v>3</v>
+      </c>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148">
+        <f t="shared" si="4"/>
+        <v>2349</v>
+      </c>
+      <c r="J48" s="149">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K48" s="53"/>
+      <c r="L48" s="130">
+        <v>3</v>
+      </c>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130"/>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="106">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S48" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="53"/>
+      <c r="U48" s="140">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>18</v>
+      </c>
+      <c r="V48" s="144">
+        <f>U48/6</f>
+        <v>3</v>
+      </c>
+      <c r="W48" s="142">
+        <f>I48*6+J48</f>
+        <v>14098</v>
+      </c>
+      <c r="X48" s="54"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
+      <c r="D49" s="120"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="129"/>
+      <c r="R49" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="116">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="118">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="138">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="119"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="129"/>
+      <c r="R50" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="119"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="121"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="129"/>
+      <c r="R51" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
+      <c r="D52" s="151"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="152"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="53"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="130"/>
+      <c r="O52" s="130"/>
+      <c r="P52" s="130"/>
+      <c r="Q52" s="131"/>
+      <c r="R52" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="53"/>
+      <c r="U52" s="140">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="144">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="142">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="54"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="119"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="121"/>
+      <c r="P53" s="121"/>
+      <c r="Q53" s="129"/>
+      <c r="R53" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="116">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="118">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="138">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="119">
+        <v>6</v>
+      </c>
+      <c r="D54" s="120"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="79"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="J54" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="129"/>
+      <c r="R54" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="116">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="139">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="138">
+        <f t="shared" si="19"/>
+        <v>144</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="119"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="129"/>
+      <c r="R55" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="116"/>
+      <c r="V55" s="139"/>
+      <c r="W55" s="138"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="119"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="121"/>
+      <c r="P56" s="121"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="139"/>
+      <c r="W56" s="138"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="129"/>
+      <c r="R57" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="116"/>
+      <c r="V57" s="139"/>
+      <c r="W57" s="138"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="121"/>
+      <c r="F58" s="121"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121"/>
+      <c r="O58" s="121"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="129"/>
+      <c r="R58" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="116"/>
+      <c r="V58" s="139"/>
+      <c r="W58" s="138"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="121"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="121"/>
+      <c r="M59" s="121"/>
+      <c r="N59" s="121"/>
+      <c r="O59" s="121"/>
+      <c r="P59" s="121"/>
+      <c r="Q59" s="129"/>
+      <c r="R59" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="116"/>
+      <c r="V59" s="139"/>
+      <c r="W59" s="138"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>46671</v>
+      </c>
+      <c r="D60" s="57">
+        <f>SUM(D8:D59)</f>
+        <v>79</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1177</v>
+      </c>
+      <c r="H60" s="59">
+        <f>SUM(H8:H59)</f>
+        <v>26</v>
+      </c>
+      <c r="I60" s="59">
+        <f>SUM(I8:I59)</f>
+        <v>45494</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>53</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="77">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>515</v>
+      </c>
+      <c r="M60" s="77">
+        <f t="shared" si="20"/>
+        <v>14</v>
+      </c>
+      <c r="N60" s="77">
+        <f t="shared" si="20"/>
+        <v>342</v>
+      </c>
+      <c r="O60" s="77">
+        <f t="shared" si="20"/>
+        <v>5</v>
+      </c>
+      <c r="P60" s="77">
+        <f t="shared" si="20"/>
+        <v>317</v>
+      </c>
+      <c r="Q60" s="78">
+        <f t="shared" si="20"/>
+        <v>7</v>
+      </c>
+      <c r="R60" s="91">
+        <f t="shared" si="20"/>
+        <v>1174</v>
+      </c>
+      <c r="S60" s="90">
+        <f t="shared" si="20"/>
+        <v>26</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>8232</v>
+      </c>
+      <c r="V60" s="111">
+        <f>SUM(V8:V59)</f>
+        <v>1174</v>
+      </c>
+      <c r="W60" s="204">
+        <f>SUM(W8:W59)</f>
+        <v>378377</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="112"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="208" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="209"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="71"/>
+      <c r="R63" s="71"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="210"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="67"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="72"/>
+      <c r="R64" s="72"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="211" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="72"/>
+      <c r="R65" s="72"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="211"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="71"/>
+      <c r="R66" s="71"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="212"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="68"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="73"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="189" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="190"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="69"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="74"/>
+      <c r="R69" s="74"/>
+      <c r="S69" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="110" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7752F64C-9CBB-404D-8082-999D1B2E0E47}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="213">
+        <v>46086</v>
+      </c>
+      <c r="Q1" s="214"/>
+      <c r="R1" s="214"/>
+      <c r="S1" s="214"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="215"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="216" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="217" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="218" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="219" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="220"/>
+      <c r="G4" s="221" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="223" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="225" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="223" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="227" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="228"/>
+      <c r="N4" s="228"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="228"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="228"/>
+      <c r="U4" s="228"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="228"/>
+      <c r="X4" s="230"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="207" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="224"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="100" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="132"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="80">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="92">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="116">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="139">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="138">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="81">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="53"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="53"/>
+      <c r="U9" s="140">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="141">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="54"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="116">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="143">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="116">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="139">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="116">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="139">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="103">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="55"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="106">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="134">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="55"/>
+      <c r="U13" s="140">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="144">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="142">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="105">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="138">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="119"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="119"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="129"/>
+      <c r="R22" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="119"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="129"/>
+      <c r="R24" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="C26" s="119"/>
       <c r="D26" s="120"/>
       <c r="E26" s="121"/>
@@ -20827,7 +24967,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="205" t="s">
+      <c r="G62" s="208" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -20845,7 +24985,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="206"/>
+      <c r="G63" s="209"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -20861,7 +25001,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="207"/>
+      <c r="G64" s="210"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -20877,7 +25017,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="208" t="s">
+      <c r="G65" s="211" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -20895,7 +25035,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="208"/>
+      <c r="G66" s="211"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -20911,7 +25051,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="209"/>
+      <c r="G67" s="212"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -20931,10 +25071,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="189" t="s">
+      <c r="C69" s="205" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="190"/>
+      <c r="D69" s="206"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA271396-3170-4527-AE1B-C391042DEBEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B0EE00-C07C-41D5-9F41-3A096659FF0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="03,03" sheetId="92" r:id="rId4"/>
     <sheet name="03,04" sheetId="93" r:id="rId5"/>
     <sheet name="03,05" sheetId="94" r:id="rId6"/>
+    <sheet name="03,06" sheetId="95" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02,05 PROMO'!$A$1:$W$61</definedName>
@@ -26,6 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'03,03'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'03,04'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'03,05'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'03,06'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -473,8 +475,94 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{87B92613-E2CE-4532-AFA4-6FD99B843C74}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{19F0AF7B-2601-4B51-AE82-914C50742E64}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{BAB533F9-3325-4863-9A2B-0F5B6FD6FF82}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2126,7 +2214,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2749,6 +2837,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3188,15 +3285,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="213"/>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="214"/>
-      <c r="S1" s="214"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="215"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="218"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3221,62 +3318,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="217" t="s">
+      <c r="C4" s="220" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="218" t="s">
+      <c r="D4" s="221" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="219" t="s">
+      <c r="E4" s="222" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="220"/>
-      <c r="G4" s="221" t="s">
+      <c r="F4" s="223"/>
+      <c r="G4" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="223" t="s">
+      <c r="H4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="227" t="s">
+      <c r="L4" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="229"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="231"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="231"/>
+      <c r="U4" s="231"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="231"/>
+      <c r="X4" s="233"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="224"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="227"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5527,7 +5624,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="208" t="s">
+      <c r="G62" s="211" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -5545,7 +5642,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="209"/>
+      <c r="G63" s="212"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -5561,7 +5658,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="210"/>
+      <c r="G64" s="213"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -5577,7 +5674,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="211" t="s">
+      <c r="G65" s="214" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -5595,7 +5692,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="211"/>
+      <c r="G66" s="214"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -5611,7 +5708,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="212"/>
+      <c r="G67" s="215"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -6004,15 +6101,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="213">
+      <c r="P1" s="216">
         <v>46058</v>
       </c>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="214"/>
-      <c r="S1" s="214"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="215"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="218"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6035,60 +6132,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="217" t="s">
+      <c r="C4" s="220" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="218" t="s">
+      <c r="D4" s="221" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="219" t="s">
+      <c r="E4" s="222" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="220"/>
-      <c r="G4" s="221" t="s">
+      <c r="F4" s="223"/>
+      <c r="G4" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="223" t="s">
+      <c r="H4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="227" t="s">
+      <c r="L4" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="231"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="231"/>
+      <c r="U4" s="231"/>
+      <c r="V4" s="233"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="224"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="227"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8897,7 +8994,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="208" t="s">
+      <c r="G62" s="211" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -8915,7 +9012,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="209"/>
+      <c r="G63" s="212"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -8931,7 +9028,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="210"/>
+      <c r="G64" s="213"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -8947,7 +9044,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="211" t="s">
+      <c r="G65" s="214" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -8965,7 +9062,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="211"/>
+      <c r="G66" s="214"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -8981,7 +9078,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="212"/>
+      <c r="G67" s="215"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -9375,17 +9472,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="213">
+      <c r="P1" s="216">
         <v>46083</v>
       </c>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="214"/>
-      <c r="S1" s="214"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="215"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="218"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9410,62 +9507,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="217" t="s">
+      <c r="C4" s="220" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="218" t="s">
+      <c r="D4" s="221" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="219" t="s">
+      <c r="E4" s="222" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="220"/>
-      <c r="G4" s="221" t="s">
+      <c r="F4" s="223"/>
+      <c r="G4" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="223" t="s">
+      <c r="H4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="227" t="s">
+      <c r="L4" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="229"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="231"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="231"/>
+      <c r="U4" s="231"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="231"/>
+      <c r="X4" s="233"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="224"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="227"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -12972,7 +13069,7 @@
       <c r="V62" s="203"/>
     </row>
     <row r="63" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G63" s="208" t="s">
+      <c r="G63" s="211" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="60"/>
@@ -12990,7 +13087,7 @@
       <c r="S63" s="32"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="61"/>
       <c r="I64" s="61"/>
       <c r="J64" s="24" t="s">
@@ -13006,7 +13103,7 @@
       <c r="S64" s="35"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210"/>
+      <c r="G65" s="213"/>
       <c r="H65" s="62"/>
       <c r="I65" s="62"/>
       <c r="J65" s="24" t="s">
@@ -13022,7 +13119,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="211" t="s">
+      <c r="G66" s="214" t="s">
         <v>64</v>
       </c>
       <c r="H66" s="63"/>
@@ -13040,7 +13137,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="63"/>
       <c r="I67" s="63"/>
       <c r="J67" s="24" t="s">
@@ -13056,7 +13153,7 @@
       <c r="S67" s="35"/>
     </row>
     <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="212"/>
+      <c r="G68" s="215"/>
       <c r="H68" s="64"/>
       <c r="I68" s="64"/>
       <c r="J68" s="25" t="s">
@@ -13451,17 +13548,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="213">
+      <c r="P1" s="216">
         <v>46084</v>
       </c>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="214"/>
-      <c r="S1" s="214"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="215"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="218"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -13486,62 +13583,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="217" t="s">
+      <c r="C4" s="220" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="218" t="s">
+      <c r="D4" s="221" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="219" t="s">
+      <c r="E4" s="222" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="220"/>
-      <c r="G4" s="221" t="s">
+      <c r="F4" s="223"/>
+      <c r="G4" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="223" t="s">
+      <c r="H4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="227" t="s">
+      <c r="L4" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="229"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="231"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="231"/>
+      <c r="U4" s="231"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="231"/>
+      <c r="X4" s="233"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="224"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="227"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17021,7 +17118,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="208" t="s">
+      <c r="G62" s="211" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -17039,7 +17136,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="209"/>
+      <c r="G63" s="212"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -17055,7 +17152,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="210"/>
+      <c r="G64" s="213"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -17071,7 +17168,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="211" t="s">
+      <c r="G65" s="214" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -17089,7 +17186,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="211"/>
+      <c r="G66" s="214"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -17105,7 +17202,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="212"/>
+      <c r="G67" s="215"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -17500,17 +17597,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="213">
+      <c r="P1" s="216">
         <v>46085</v>
       </c>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="214"/>
-      <c r="S1" s="214"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="215"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="218"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -17535,62 +17632,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="217" t="s">
+      <c r="C4" s="220" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="218" t="s">
+      <c r="D4" s="221" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="219" t="s">
+      <c r="E4" s="222" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="220"/>
-      <c r="G4" s="221" t="s">
+      <c r="F4" s="223"/>
+      <c r="G4" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="223" t="s">
+      <c r="H4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="227" t="s">
+      <c r="L4" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="229"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="231"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="231"/>
+      <c r="U4" s="231"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="231"/>
+      <c r="X4" s="233"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="224"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="227"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21064,7 +21161,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="208" t="s">
+      <c r="G62" s="211" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -21082,7 +21179,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="209"/>
+      <c r="G63" s="212"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -21098,7 +21195,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="210"/>
+      <c r="G64" s="213"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -21114,7 +21211,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="211" t="s">
+      <c r="G65" s="214" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -21132,7 +21229,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="211"/>
+      <c r="G66" s="214"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -21148,7 +21245,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="212"/>
+      <c r="G67" s="215"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -21543,17 +21640,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="213">
+      <c r="P1" s="216">
         <v>46086</v>
       </c>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="214"/>
-      <c r="S1" s="214"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="215"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="218"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -21578,62 +21675,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="217" t="s">
+      <c r="C4" s="220" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="218" t="s">
+      <c r="D4" s="221" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="219" t="s">
+      <c r="E4" s="222" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="220"/>
-      <c r="G4" s="221" t="s">
+      <c r="F4" s="223"/>
+      <c r="G4" s="224" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="223" t="s">
+      <c r="H4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="227" t="s">
+      <c r="L4" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="228"/>
-      <c r="U4" s="228"/>
-      <c r="V4" s="229"/>
-      <c r="W4" s="228"/>
-      <c r="X4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="231"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="231"/>
+      <c r="U4" s="231"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="231"/>
+      <c r="X4" s="233"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="224"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="227"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21798,30 +21895,36 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>66</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
       <c r="G8" s="79"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="121"/>
       <c r="M8" s="121"/>
       <c r="N8" s="121"/>
       <c r="O8" s="121"/>
-      <c r="P8" s="121"/>
+      <c r="P8" s="121">
+        <v>1</v>
+      </c>
       <c r="Q8" s="129"/>
       <c r="R8" s="92">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="133">
         <f t="shared" si="1"/>
@@ -21830,15 +21933,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="116">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="139">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -21873,7 +21976,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>102</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
@@ -21881,7 +21986,7 @@
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
@@ -21913,7 +22018,7 @@
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -21948,15 +22053,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>68</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
-      <c r="G10" s="79"/>
+      <c r="G10" s="79">
+        <v>17</v>
+      </c>
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
@@ -21965,13 +22074,15 @@
       <c r="K10" s="41"/>
       <c r="L10" s="121"/>
       <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
+      <c r="N10" s="121">
+        <v>17</v>
+      </c>
       <c r="O10" s="121"/>
       <c r="P10" s="121"/>
       <c r="Q10" s="129"/>
       <c r="R10" s="108">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S10" s="135">
         <f t="shared" si="1"/>
@@ -21980,15 +22091,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="116">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="V10" s="143">
         <f>U10/24</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1224</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -22023,15 +22134,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>36</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
-      <c r="G11" s="79"/>
+      <c r="G11" s="79">
+        <v>13</v>
+      </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
@@ -22040,13 +22155,15 @@
       <c r="K11" s="41"/>
       <c r="L11" s="121"/>
       <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
+      <c r="N11" s="121">
+        <v>13</v>
+      </c>
       <c r="O11" s="121"/>
       <c r="P11" s="121"/>
       <c r="Q11" s="129"/>
       <c r="R11" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S11" s="133">
         <f t="shared" si="1"/>
@@ -22055,15 +22172,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="116">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="V11" s="139">
         <f>U11/24</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -22098,7 +22215,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -22106,7 +22225,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -22138,7 +22257,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -22173,30 +22292,40 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>3958</v>
+      </c>
+      <c r="D13" s="123">
+        <v>18</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
+      <c r="G13" s="81">
+        <v>17</v>
+      </c>
       <c r="H13" s="82"/>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3941</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K13" s="55"/>
-      <c r="L13" s="130"/>
+      <c r="L13" s="130">
+        <v>10</v>
+      </c>
       <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
+      <c r="N13" s="130">
+        <v>7</v>
+      </c>
       <c r="O13" s="130"/>
       <c r="P13" s="130"/>
       <c r="Q13" s="131"/>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
@@ -22205,15 +22334,15 @@
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>94602</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -22255,7 +22384,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -22263,7 +22394,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -22295,7 +22426,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -22555,7 +22686,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -22563,7 +22696,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -22595,7 +22728,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -22705,7 +22838,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -22713,7 +22848,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -22745,7 +22880,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -22780,7 +22915,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -22788,7 +22925,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -22820,7 +22957,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -22855,7 +22992,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -22863,7 +23002,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -22895,7 +23034,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -22930,7 +23069,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -22938,7 +23079,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -22970,7 +23111,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -23012,22 +23153,28 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="119">
+        <v>47</v>
+      </c>
       <c r="D24" s="120"/>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
-      <c r="G24" s="79"/>
+      <c r="G24" s="79">
+        <v>2</v>
+      </c>
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K24" s="42"/>
-      <c r="L24" s="121"/>
+      <c r="L24" s="121">
+        <v>2</v>
+      </c>
       <c r="M24" s="121"/>
       <c r="N24" s="121"/>
       <c r="O24" s="121"/>
@@ -23035,7 +23182,7 @@
       <c r="Q24" s="129"/>
       <c r="R24" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" s="133">
         <f t="shared" si="7"/>
@@ -23044,15 +23191,15 @@
       <c r="T24" s="42"/>
       <c r="U24" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V24" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -23094,7 +23241,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -23102,7 +23251,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -23134,7 +23283,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -23169,6 +23318,4003 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="C26" s="119">
+        <v>123</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="79">
+        <v>1</v>
+      </c>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76">
+        <f t="shared" si="4"/>
+        <v>122</v>
+      </c>
+      <c r="J26" s="80">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="121">
+        <v>1</v>
+      </c>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="129"/>
+      <c r="R26" s="92">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S26" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="116">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V26" s="139">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W26" s="138">
+        <f t="shared" si="8"/>
+        <v>2939</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="119">
+        <v>20</v>
+      </c>
+      <c r="D27" s="120"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="79">
+        <v>4</v>
+      </c>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="J27" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121">
+        <v>4</v>
+      </c>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="92">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="S27" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="116">
+        <f t="shared" si="5"/>
+        <v>96</v>
+      </c>
+      <c r="V27" s="139">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="W27" s="138">
+        <f t="shared" si="8"/>
+        <v>384</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="119"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="119">
+        <v>97</v>
+      </c>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="79">
+        <v>2</v>
+      </c>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76">
+        <f t="shared" si="4"/>
+        <v>95</v>
+      </c>
+      <c r="J29" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121">
+        <v>2</v>
+      </c>
+      <c r="O29" s="121"/>
+      <c r="P29" s="121"/>
+      <c r="Q29" s="129"/>
+      <c r="R29" s="92">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S29" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="116">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V29" s="139">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W29" s="138">
+        <f t="shared" si="8"/>
+        <v>2280</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="119">
+        <v>10</v>
+      </c>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J30" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="129"/>
+      <c r="R30" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="138">
+        <f t="shared" si="8"/>
+        <v>240</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="119">
+        <v>60</v>
+      </c>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J31" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="129"/>
+      <c r="R31" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="138">
+        <f t="shared" si="8"/>
+        <v>1440</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="119">
+        <v>15</v>
+      </c>
+      <c r="D32" s="120"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="79">
+        <v>11</v>
+      </c>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J32" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121">
+        <v>11</v>
+      </c>
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="92">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="S32" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="116">
+        <f t="shared" si="5"/>
+        <v>264</v>
+      </c>
+      <c r="V32" s="139">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="W32" s="138">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="129"/>
+      <c r="R33" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="119">
+        <v>3</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="79">
+        <v>3</v>
+      </c>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121">
+        <v>3</v>
+      </c>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="129"/>
+      <c r="R34" s="92">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S34" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="116">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="V34" s="139">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W34" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="119">
+        <v>135</v>
+      </c>
+      <c r="D35" s="120">
+        <v>17</v>
+      </c>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="J35" s="80">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="129"/>
+      <c r="R35" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="138">
+        <f t="shared" si="8"/>
+        <v>3257</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="121"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="129"/>
+      <c r="R36" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="119"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="129"/>
+      <c r="R37" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="122">
+        <v>4352</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="81">
+        <v>34</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="148">
+        <f t="shared" si="4"/>
+        <v>4318</v>
+      </c>
+      <c r="J38" s="149">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K38" s="53"/>
+      <c r="L38" s="130">
+        <v>10</v>
+      </c>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130">
+        <v>24</v>
+      </c>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130"/>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="106">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="S38" s="134">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="53"/>
+      <c r="U38" s="140">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>204</v>
+      </c>
+      <c r="V38" s="144">
+        <f>U38/6</f>
+        <v>34</v>
+      </c>
+      <c r="W38" s="142">
+        <f>I38*6+J38</f>
+        <v>25910</v>
+      </c>
+      <c r="X38" s="54"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="119">
+        <v>18</v>
+      </c>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="79">
+        <v>6</v>
+      </c>
+      <c r="H39" s="76"/>
+      <c r="I39" s="79">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="J39" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121">
+        <v>6</v>
+      </c>
+      <c r="O39" s="121"/>
+      <c r="P39" s="121"/>
+      <c r="Q39" s="129"/>
+      <c r="R39" s="105">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="S39" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="116">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>144</v>
+      </c>
+      <c r="V39" s="118">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="W39" s="138">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>288</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="129"/>
+      <c r="R40" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="145">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="146">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="101"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="155">
+        <v>558</v>
+      </c>
+      <c r="D41" s="156"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="159"/>
+      <c r="I41" s="160">
+        <f t="shared" si="4"/>
+        <v>558</v>
+      </c>
+      <c r="J41" s="161">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="162"/>
+      <c r="L41" s="163"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="163"/>
+      <c r="O41" s="163"/>
+      <c r="P41" s="163"/>
+      <c r="Q41" s="164"/>
+      <c r="R41" s="165">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="166">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="162"/>
+      <c r="U41" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="168">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="168">
+        <f t="shared" si="10"/>
+        <v>13392</v>
+      </c>
+      <c r="X41" s="169"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="171" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="172">
+        <v>1450</v>
+      </c>
+      <c r="D42" s="173"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="175">
+        <v>1</v>
+      </c>
+      <c r="H42" s="176"/>
+      <c r="I42" s="175">
+        <f t="shared" si="4"/>
+        <v>1449</v>
+      </c>
+      <c r="J42" s="177">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="178"/>
+      <c r="L42" s="174"/>
+      <c r="M42" s="174"/>
+      <c r="N42" s="174">
+        <v>1</v>
+      </c>
+      <c r="O42" s="174"/>
+      <c r="P42" s="174"/>
+      <c r="Q42" s="179"/>
+      <c r="R42" s="180">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S42" s="181">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="178"/>
+      <c r="U42" s="182">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>12</v>
+      </c>
+      <c r="V42" s="183">
+        <f>U42/12</f>
+        <v>1</v>
+      </c>
+      <c r="W42" s="184">
+        <f>I42*12+J42</f>
+        <v>17388</v>
+      </c>
+      <c r="X42" s="185"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="119"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="116"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="122">
+        <v>31939</v>
+      </c>
+      <c r="D44" s="123">
+        <v>4</v>
+      </c>
+      <c r="E44" s="124"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="81">
+        <v>623</v>
+      </c>
+      <c r="H44" s="82"/>
+      <c r="I44" s="76">
+        <f>C44+E44-G44</f>
+        <v>31316</v>
+      </c>
+      <c r="J44" s="186">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K44" s="53"/>
+      <c r="L44" s="130">
+        <v>377</v>
+      </c>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130">
+        <v>246</v>
+      </c>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130"/>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="187">
+        <f t="shared" si="7"/>
+        <v>623</v>
+      </c>
+      <c r="S44" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="53"/>
+      <c r="U44" s="140">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>3738</v>
+      </c>
+      <c r="V44" s="139">
+        <f>U44/6</f>
+        <v>623</v>
+      </c>
+      <c r="W44" s="142">
+        <f>I44*6+J44</f>
+        <v>187900</v>
+      </c>
+      <c r="X44" s="54"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="119"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="121"/>
+      <c r="G45" s="79"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="129"/>
+      <c r="R45" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="116"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="138"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="119"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="121"/>
+      <c r="P46" s="121"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="137">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="116">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="143">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="138">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="119">
+        <v>4</v>
+      </c>
+      <c r="D47" s="120"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="79">
+        <v>4</v>
+      </c>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121">
+        <v>4</v>
+      </c>
+      <c r="O47" s="121"/>
+      <c r="P47" s="121"/>
+      <c r="Q47" s="129"/>
+      <c r="R47" s="92">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="S47" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="116">
+        <f t="shared" si="11"/>
+        <v>96</v>
+      </c>
+      <c r="V47" s="139">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="W47" s="138">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="150">
+        <v>2349</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="152"/>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148">
+        <f t="shared" si="4"/>
+        <v>2349</v>
+      </c>
+      <c r="J48" s="149">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K48" s="53"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130"/>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="53"/>
+      <c r="U48" s="140">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="144">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="142">
+        <f>I48*6+J48</f>
+        <v>14098</v>
+      </c>
+      <c r="X48" s="54"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
+      <c r="D49" s="120"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="129"/>
+      <c r="R49" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="116">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="118">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="138">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="119"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="129"/>
+      <c r="R50" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="119"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="121"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="129"/>
+      <c r="R51" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
+      <c r="D52" s="151"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="152"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="53"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="130"/>
+      <c r="O52" s="130"/>
+      <c r="P52" s="130"/>
+      <c r="Q52" s="131"/>
+      <c r="R52" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="53"/>
+      <c r="U52" s="140">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="144">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="142">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="54"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="119"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="121"/>
+      <c r="P53" s="121"/>
+      <c r="Q53" s="129"/>
+      <c r="R53" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="116">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="118">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="138">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="119">
+        <v>6</v>
+      </c>
+      <c r="D54" s="120"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="79">
+        <v>1</v>
+      </c>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J54" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121">
+        <v>1</v>
+      </c>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="129"/>
+      <c r="R54" s="92">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S54" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="116">
+        <f t="shared" si="17"/>
+        <v>24</v>
+      </c>
+      <c r="V54" s="139">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="W54" s="138">
+        <f t="shared" si="19"/>
+        <v>120</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="119"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="129"/>
+      <c r="R55" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="116"/>
+      <c r="V55" s="139"/>
+      <c r="W55" s="138"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="119"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="121"/>
+      <c r="P56" s="121"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="139"/>
+      <c r="W56" s="138"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="129"/>
+      <c r="R57" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="116"/>
+      <c r="V57" s="139"/>
+      <c r="W57" s="138"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="121"/>
+      <c r="F58" s="121"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121"/>
+      <c r="O58" s="121"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="129"/>
+      <c r="R58" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="116"/>
+      <c r="V58" s="139"/>
+      <c r="W58" s="138"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="121"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="121"/>
+      <c r="M59" s="121"/>
+      <c r="N59" s="121"/>
+      <c r="O59" s="121"/>
+      <c r="P59" s="121"/>
+      <c r="Q59" s="129"/>
+      <c r="R59" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="116"/>
+      <c r="V59" s="139"/>
+      <c r="W59" s="138"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>45493</v>
+      </c>
+      <c r="D60" s="57">
+        <f>SUM(D8:D59)</f>
+        <v>77</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>739</v>
+      </c>
+      <c r="H60" s="59">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="59">
+        <f>SUM(I8:I59)</f>
+        <v>44754</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>77</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="77">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>400</v>
+      </c>
+      <c r="M60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="77">
+        <f t="shared" si="20"/>
+        <v>339</v>
+      </c>
+      <c r="O60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="77">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="Q60" s="78">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="91">
+        <f t="shared" si="20"/>
+        <v>740</v>
+      </c>
+      <c r="S60" s="90">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>5922</v>
+      </c>
+      <c r="V60" s="111">
+        <f>SUM(V8:V59)</f>
+        <v>740</v>
+      </c>
+      <c r="W60" s="204">
+        <f>SUM(W8:W59)</f>
+        <v>372479</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="112"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="211" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="212"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="71"/>
+      <c r="R63" s="71"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="213"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="67"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="72"/>
+      <c r="R64" s="72"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="214" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="72"/>
+      <c r="R65" s="72"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="214"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="71"/>
+      <c r="R66" s="71"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="215"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="68"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="73"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="205" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="206"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="69"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="74"/>
+      <c r="R69" s="74"/>
+      <c r="S69" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="110" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D56B4F-BBDA-4848-8850-351661DB2A38}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="216">
+        <v>46087</v>
+      </c>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="218"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="219" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="220" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="221" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="222" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="223"/>
+      <c r="G4" s="224" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="226" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="228" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="226" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="230" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="231"/>
+      <c r="Q4" s="231"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="231"/>
+      <c r="U4" s="231"/>
+      <c r="V4" s="232"/>
+      <c r="W4" s="231"/>
+      <c r="X4" s="233"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="221"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="210" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="225"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="227"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="100" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="132"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="80">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="92">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="116">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="139">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="138">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="81">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="53"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="53"/>
+      <c r="U9" s="140">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="141">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="54"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="116">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="143">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="116">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="139">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="116">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="139">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="103">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="55"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="106">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="134">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="55"/>
+      <c r="U13" s="140">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="144">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="142">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="105">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="138">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="119"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="119"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="129"/>
+      <c r="R22" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="119"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="129"/>
+      <c r="R24" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="C26" s="119"/>
       <c r="D26" s="120"/>
       <c r="E26" s="121"/>
@@ -24967,7 +29113,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="208" t="s">
+      <c r="G62" s="211" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -24985,7 +29131,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="209"/>
+      <c r="G63" s="212"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -25001,7 +29147,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="210"/>
+      <c r="G64" s="213"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -25017,7 +29163,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="211" t="s">
+      <c r="G65" s="214" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -25035,7 +29181,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="211"/>
+      <c r="G66" s="214"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -25051,7 +29197,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="212"/>
+      <c r="G67" s="215"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -25071,10 +29217,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="205" t="s">
+      <c r="C69" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="206"/>
+      <c r="D69" s="209"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B0EE00-C07C-41D5-9F41-3A096659FF0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF94812F-9C84-42AD-8B7E-96ADDEE84DDE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="03,04" sheetId="93" r:id="rId5"/>
     <sheet name="03,05" sheetId="94" r:id="rId6"/>
     <sheet name="03,06" sheetId="95" r:id="rId7"/>
+    <sheet name="03,07" sheetId="96" r:id="rId8"/>
+    <sheet name="03,08" sheetId="97" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02,05 PROMO'!$A$1:$W$61</definedName>
@@ -28,6 +30,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'03,04'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'03,05'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'03,06'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'03,07'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'03,08'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -561,8 +565,180 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{7286417F-C385-440F-A262-9AB5207CB92C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{82502BB1-4DEB-4776-890B-153599080D83}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{1F5568FC-08E9-4837-9C64-2FDB0E9F27BC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{81329A7A-5050-4421-942D-F5FEAF9A57BF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{8EB2B452-E134-4101-B9AA-EEF74B8A8304}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{DCCBA941-3F55-489C-B3C4-1FCAB656EAF8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2214,7 +2390,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2846,6 +3022,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3285,15 +3470,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="218"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3318,62 +3503,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="223"/>
-      <c r="G4" s="224" t="s">
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="226" t="s">
+      <c r="H4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="231"/>
-      <c r="N4" s="231"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="231"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="231"/>
-      <c r="X4" s="233"/>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="225"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5624,7 +5809,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="211" t="s">
+      <c r="G62" s="214" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -5642,7 +5827,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="212"/>
+      <c r="G63" s="215"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -5658,7 +5843,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="213"/>
+      <c r="G64" s="216"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -5674,7 +5859,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="214" t="s">
+      <c r="G65" s="217" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -5692,7 +5877,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="214"/>
+      <c r="G66" s="217"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -5708,7 +5893,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="215"/>
+      <c r="G67" s="218"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -6101,15 +6286,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="216">
+      <c r="P1" s="219">
         <v>46058</v>
       </c>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="218"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="221"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6132,60 +6317,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="223"/>
-      <c r="G4" s="224" t="s">
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="226" t="s">
+      <c r="H4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="231"/>
-      <c r="N4" s="231"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="231"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="233"/>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="236"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="225"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8994,7 +9179,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="211" t="s">
+      <c r="G62" s="214" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -9012,7 +9197,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="212"/>
+      <c r="G63" s="215"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -9028,7 +9213,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="213"/>
+      <c r="G64" s="216"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -9044,7 +9229,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="214" t="s">
+      <c r="G65" s="217" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -9062,7 +9247,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="214"/>
+      <c r="G66" s="217"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -9078,7 +9263,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="215"/>
+      <c r="G67" s="218"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -9472,17 +9657,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="216">
+      <c r="P1" s="219">
         <v>46083</v>
       </c>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="218"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9507,62 +9692,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="223"/>
-      <c r="G4" s="224" t="s">
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="226" t="s">
+      <c r="H4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="231"/>
-      <c r="N4" s="231"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="231"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="231"/>
-      <c r="X4" s="233"/>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="225"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13069,7 +13254,7 @@
       <c r="V62" s="203"/>
     </row>
     <row r="63" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G63" s="211" t="s">
+      <c r="G63" s="214" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="60"/>
@@ -13087,7 +13272,7 @@
       <c r="S63" s="32"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="212"/>
+      <c r="G64" s="215"/>
       <c r="H64" s="61"/>
       <c r="I64" s="61"/>
       <c r="J64" s="24" t="s">
@@ -13103,7 +13288,7 @@
       <c r="S64" s="35"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="213"/>
+      <c r="G65" s="216"/>
       <c r="H65" s="62"/>
       <c r="I65" s="62"/>
       <c r="J65" s="24" t="s">
@@ -13119,7 +13304,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="214" t="s">
+      <c r="G66" s="217" t="s">
         <v>64</v>
       </c>
       <c r="H66" s="63"/>
@@ -13137,7 +13322,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G67" s="214"/>
+      <c r="G67" s="217"/>
       <c r="H67" s="63"/>
       <c r="I67" s="63"/>
       <c r="J67" s="24" t="s">
@@ -13153,7 +13338,7 @@
       <c r="S67" s="35"/>
     </row>
     <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="215"/>
+      <c r="G68" s="218"/>
       <c r="H68" s="64"/>
       <c r="I68" s="64"/>
       <c r="J68" s="25" t="s">
@@ -13548,17 +13733,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="216">
+      <c r="P1" s="219">
         <v>46084</v>
       </c>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="218"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -13583,62 +13768,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="223"/>
-      <c r="G4" s="224" t="s">
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="226" t="s">
+      <c r="H4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="231"/>
-      <c r="N4" s="231"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="231"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="231"/>
-      <c r="X4" s="233"/>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="225"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17118,7 +17303,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="211" t="s">
+      <c r="G62" s="214" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -17136,7 +17321,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="212"/>
+      <c r="G63" s="215"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -17152,7 +17337,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="213"/>
+      <c r="G64" s="216"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -17168,7 +17353,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="214" t="s">
+      <c r="G65" s="217" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -17186,7 +17371,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="214"/>
+      <c r="G66" s="217"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -17202,7 +17387,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="215"/>
+      <c r="G67" s="218"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -17597,17 +17782,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="216">
+      <c r="P1" s="219">
         <v>46085</v>
       </c>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="218"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -17632,62 +17817,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="223"/>
-      <c r="G4" s="224" t="s">
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="226" t="s">
+      <c r="H4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="231"/>
-      <c r="N4" s="231"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="231"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="231"/>
-      <c r="X4" s="233"/>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="225"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21161,7 +21346,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="211" t="s">
+      <c r="G62" s="214" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -21179,7 +21364,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="212"/>
+      <c r="G63" s="215"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -21195,7 +21380,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="213"/>
+      <c r="G64" s="216"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -21211,7 +21396,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="214" t="s">
+      <c r="G65" s="217" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -21229,7 +21414,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="214"/>
+      <c r="G66" s="217"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -21245,7 +21430,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="215"/>
+      <c r="G67" s="218"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -21640,17 +21825,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="216">
+      <c r="P1" s="219">
         <v>46086</v>
       </c>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="218"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -21675,62 +21860,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="223"/>
-      <c r="G4" s="224" t="s">
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="226" t="s">
+      <c r="H4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="231"/>
-      <c r="N4" s="231"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="231"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="231"/>
-      <c r="X4" s="233"/>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="225"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25210,7 +25395,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="211" t="s">
+      <c r="G62" s="214" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -25228,7 +25413,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="212"/>
+      <c r="G63" s="215"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -25244,7 +25429,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="213"/>
+      <c r="G64" s="216"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -25260,7 +25445,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="214" t="s">
+      <c r="G65" s="217" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -25278,7 +25463,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="214"/>
+      <c r="G66" s="217"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -25294,7 +25479,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="215"/>
+      <c r="G67" s="218"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -25689,17 +25874,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="216">
+      <c r="P1" s="219">
         <v>46087</v>
       </c>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="218"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -25724,62 +25909,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="222" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="223"/>
-      <c r="G4" s="224" t="s">
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="226" t="s">
+      <c r="H4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="228" t="s">
+      <c r="I4" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="226" t="s">
+      <c r="J4" s="229" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="231"/>
-      <c r="N4" s="231"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="231"/>
-      <c r="Q4" s="231"/>
-      <c r="R4" s="231"/>
-      <c r="S4" s="231"/>
-      <c r="T4" s="231"/>
-      <c r="U4" s="231"/>
-      <c r="V4" s="232"/>
-      <c r="W4" s="231"/>
-      <c r="X4" s="233"/>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="210" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="225"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25944,19 +26129,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>66</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
       <c r="G8" s="79"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="121"/>
@@ -25984,7 +26173,7 @@
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -26019,7 +26208,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>102</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
@@ -26027,7 +26218,7 @@
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
@@ -26059,7 +26250,7 @@
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -26094,7 +26285,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>51</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
@@ -26102,7 +26295,7 @@
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
@@ -26134,7 +26327,7 @@
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1224</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -26169,7 +26362,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>23</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
@@ -26177,7 +26372,7 @@
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
@@ -26209,7 +26404,7 @@
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -26244,7 +26439,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -26252,7 +26449,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -26284,7 +26481,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -26319,47 +26516,59 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>3941</v>
+      </c>
+      <c r="D13" s="123">
+        <v>18</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="G13" s="81">
+        <v>13</v>
+      </c>
+      <c r="H13" s="82">
+        <v>13</v>
+      </c>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3928</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K13" s="55"/>
       <c r="L13" s="130"/>
       <c r="M13" s="130"/>
       <c r="N13" s="130"/>
       <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="131"/>
+      <c r="P13" s="130">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="131">
+        <v>13</v>
+      </c>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>94277</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -26401,7 +26610,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -26409,7 +26620,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -26441,7 +26652,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -26701,7 +26912,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -26709,7 +26922,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -26741,7 +26954,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -26851,7 +27064,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -26859,7 +27074,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -26891,7 +27106,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -26926,7 +27141,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -26934,7 +27151,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -26966,7 +27183,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -27001,7 +27218,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -27009,7 +27228,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -27041,7 +27260,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -27076,7 +27295,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -27084,7 +27305,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -27116,7 +27337,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -27158,7 +27379,9 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="119">
+        <v>45</v>
+      </c>
       <c r="D24" s="120"/>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
@@ -27166,7 +27389,7 @@
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
@@ -27198,7 +27421,7 @@
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -27240,7 +27463,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -27248,7 +27473,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -27280,7 +27505,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -27315,19 +27540,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="C26" s="119">
+        <v>122</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
       <c r="E26" s="121"/>
       <c r="F26" s="121"/>
       <c r="G26" s="79"/>
       <c r="H26" s="76"/>
       <c r="I26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="J26" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="121"/>
@@ -27355,7 +27584,7 @@
       </c>
       <c r="W26" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2939</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -27371,7 +27600,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="119"/>
+      <c r="C27" s="119">
+        <v>16</v>
+      </c>
       <c r="D27" s="120"/>
       <c r="E27" s="121"/>
       <c r="F27" s="121"/>
@@ -27379,7 +27610,7 @@
       <c r="H27" s="76"/>
       <c r="I27" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J27" s="80">
         <f t="shared" si="4"/>
@@ -27411,7 +27642,7 @@
       </c>
       <c r="W27" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -27489,7 +27720,9 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="119"/>
+      <c r="C29" s="119">
+        <v>95</v>
+      </c>
       <c r="D29" s="120"/>
       <c r="E29" s="121"/>
       <c r="F29" s="121"/>
@@ -27497,7 +27730,7 @@
       <c r="H29" s="76"/>
       <c r="I29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J29" s="80">
         <f t="shared" si="4"/>
@@ -27529,7 +27762,7 @@
       </c>
       <c r="W29" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -27548,7 +27781,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="119"/>
+      <c r="C30" s="119">
+        <v>10</v>
+      </c>
       <c r="D30" s="120"/>
       <c r="E30" s="121"/>
       <c r="F30" s="121"/>
@@ -27556,7 +27791,7 @@
       <c r="H30" s="76"/>
       <c r="I30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="80">
         <f t="shared" si="4"/>
@@ -27588,7 +27823,7 @@
       </c>
       <c r="W30" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -27600,7 +27835,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="119">
+        <v>60</v>
+      </c>
       <c r="D31" s="120"/>
       <c r="E31" s="121"/>
       <c r="F31" s="121"/>
@@ -27608,7 +27845,7 @@
       <c r="H31" s="76"/>
       <c r="I31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J31" s="80">
         <f t="shared" si="4"/>
@@ -27640,7 +27877,7 @@
       </c>
       <c r="W31" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -27652,7 +27889,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="119"/>
+      <c r="C32" s="119">
+        <v>4</v>
+      </c>
       <c r="D32" s="120"/>
       <c r="E32" s="121"/>
       <c r="F32" s="121"/>
@@ -27660,7 +27899,7 @@
       <c r="H32" s="76"/>
       <c r="I32" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J32" s="80">
         <f t="shared" si="4"/>
@@ -27692,7 +27931,7 @@
       </c>
       <c r="W32" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -27808,19 +28047,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="120"/>
+      <c r="C35" s="119">
+        <v>135</v>
+      </c>
+      <c r="D35" s="120">
+        <v>17</v>
+      </c>
       <c r="E35" s="121"/>
       <c r="F35" s="121"/>
       <c r="G35" s="79"/>
       <c r="H35" s="76"/>
       <c r="I35" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="J35" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="121"/>
@@ -27848,7 +28091,7 @@
       </c>
       <c r="W35" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3257</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -27964,6 +28207,3946 @@
       <c r="B38" s="147" t="s">
         <v>33</v>
       </c>
+      <c r="C38" s="122">
+        <v>4318</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="81">
+        <v>111</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="148">
+        <f t="shared" si="4"/>
+        <v>4207</v>
+      </c>
+      <c r="J38" s="149">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K38" s="53"/>
+      <c r="L38" s="130"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130">
+        <v>111</v>
+      </c>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="106">
+        <f t="shared" si="7"/>
+        <v>111</v>
+      </c>
+      <c r="S38" s="134">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="53"/>
+      <c r="U38" s="140">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>666</v>
+      </c>
+      <c r="V38" s="144">
+        <f>U38/6</f>
+        <v>111</v>
+      </c>
+      <c r="W38" s="142">
+        <f>I38*6+J38</f>
+        <v>25244</v>
+      </c>
+      <c r="X38" s="54"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="119">
+        <v>12</v>
+      </c>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="79">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="J39" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="121"/>
+      <c r="P39" s="121"/>
+      <c r="Q39" s="129"/>
+      <c r="R39" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="116">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="138">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>288</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="129"/>
+      <c r="R40" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="145">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="146">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="101"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="155">
+        <v>558</v>
+      </c>
+      <c r="D41" s="156"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="159"/>
+      <c r="I41" s="160">
+        <f t="shared" si="4"/>
+        <v>558</v>
+      </c>
+      <c r="J41" s="161">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="162"/>
+      <c r="L41" s="163"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="163"/>
+      <c r="O41" s="163"/>
+      <c r="P41" s="163"/>
+      <c r="Q41" s="164"/>
+      <c r="R41" s="165">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="166">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="162"/>
+      <c r="U41" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="168">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="168">
+        <f t="shared" si="10"/>
+        <v>13392</v>
+      </c>
+      <c r="X41" s="169"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="171" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="172">
+        <v>1449</v>
+      </c>
+      <c r="D42" s="173"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="175">
+        <v>10</v>
+      </c>
+      <c r="H42" s="176"/>
+      <c r="I42" s="175">
+        <f t="shared" si="4"/>
+        <v>1439</v>
+      </c>
+      <c r="J42" s="177">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="178"/>
+      <c r="L42" s="174"/>
+      <c r="M42" s="174"/>
+      <c r="N42" s="174"/>
+      <c r="O42" s="174"/>
+      <c r="P42" s="174">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="179"/>
+      <c r="R42" s="180">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S42" s="181">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="178"/>
+      <c r="U42" s="182">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>120</v>
+      </c>
+      <c r="V42" s="183">
+        <f>U42/12</f>
+        <v>10</v>
+      </c>
+      <c r="W42" s="184">
+        <f>I42*12+J42</f>
+        <v>17268</v>
+      </c>
+      <c r="X42" s="185"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="119"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="116"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="122">
+        <v>31316</v>
+      </c>
+      <c r="D44" s="123">
+        <v>4</v>
+      </c>
+      <c r="E44" s="124"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="81">
+        <v>355</v>
+      </c>
+      <c r="H44" s="82"/>
+      <c r="I44" s="76">
+        <f>C44+E44-G44</f>
+        <v>30961</v>
+      </c>
+      <c r="J44" s="186">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K44" s="53"/>
+      <c r="L44" s="130"/>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130"/>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130">
+        <v>355</v>
+      </c>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="187">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+      <c r="S44" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="53"/>
+      <c r="U44" s="140">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>2130</v>
+      </c>
+      <c r="V44" s="139">
+        <f>U44/6</f>
+        <v>355</v>
+      </c>
+      <c r="W44" s="142">
+        <f>I44*6+J44</f>
+        <v>185770</v>
+      </c>
+      <c r="X44" s="54"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="119"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="121"/>
+      <c r="G45" s="79"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="129"/>
+      <c r="R45" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="116"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="138"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="119"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="121"/>
+      <c r="P46" s="121"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="137">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="116">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="143">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="138">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="119"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="121"/>
+      <c r="P47" s="121"/>
+      <c r="Q47" s="129"/>
+      <c r="R47" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="139">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="138">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="150">
+        <f>2349</f>
+        <v>2349</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="152"/>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148">
+        <f t="shared" si="4"/>
+        <v>2349</v>
+      </c>
+      <c r="J48" s="149">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K48" s="53"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130"/>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="53"/>
+      <c r="U48" s="140">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="144">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="142">
+        <f>I48*6+J48</f>
+        <v>14098</v>
+      </c>
+      <c r="X48" s="54"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
+      <c r="D49" s="120"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="129"/>
+      <c r="R49" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="116">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="118">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="138">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="119"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="129"/>
+      <c r="R50" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="119"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="121"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="129"/>
+      <c r="R51" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
+      <c r="D52" s="151"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="152"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="53"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="130"/>
+      <c r="O52" s="130"/>
+      <c r="P52" s="130"/>
+      <c r="Q52" s="131"/>
+      <c r="R52" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="53"/>
+      <c r="U52" s="140">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="144">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="142">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="54"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="119"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="121"/>
+      <c r="P53" s="121"/>
+      <c r="Q53" s="129"/>
+      <c r="R53" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="116">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="118">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="138">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="119">
+        <v>5</v>
+      </c>
+      <c r="D54" s="120"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="79"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J54" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="129"/>
+      <c r="R54" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="116">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="139">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="138">
+        <f t="shared" si="19"/>
+        <v>120</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="119"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="129"/>
+      <c r="R55" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="116"/>
+      <c r="V55" s="139"/>
+      <c r="W55" s="138"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="119"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="121"/>
+      <c r="P56" s="121"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="139"/>
+      <c r="W56" s="138"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="129"/>
+      <c r="R57" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="116"/>
+      <c r="V57" s="139"/>
+      <c r="W57" s="138"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="121"/>
+      <c r="F58" s="121"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121"/>
+      <c r="O58" s="121"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="129"/>
+      <c r="R58" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="116"/>
+      <c r="V58" s="139"/>
+      <c r="W58" s="138"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="121"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="121"/>
+      <c r="M59" s="121"/>
+      <c r="N59" s="121"/>
+      <c r="O59" s="121"/>
+      <c r="P59" s="121"/>
+      <c r="Q59" s="129"/>
+      <c r="R59" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="116"/>
+      <c r="V59" s="139"/>
+      <c r="W59" s="138"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>44754</v>
+      </c>
+      <c r="D60" s="57">
+        <f>SUM(D8:D59)</f>
+        <v>77</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>489</v>
+      </c>
+      <c r="H60" s="59">
+        <f>SUM(H8:H59)</f>
+        <v>13</v>
+      </c>
+      <c r="I60" s="59">
+        <f>SUM(I8:I59)</f>
+        <v>44265</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>64</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="77">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="77">
+        <f t="shared" si="20"/>
+        <v>489</v>
+      </c>
+      <c r="Q60" s="78">
+        <f t="shared" si="20"/>
+        <v>13</v>
+      </c>
+      <c r="R60" s="91">
+        <f t="shared" si="20"/>
+        <v>489</v>
+      </c>
+      <c r="S60" s="90">
+        <f t="shared" si="20"/>
+        <v>13</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>3228</v>
+      </c>
+      <c r="V60" s="111">
+        <f>SUM(V8:V59)</f>
+        <v>489</v>
+      </c>
+      <c r="W60" s="204">
+        <f>SUM(W8:W59)</f>
+        <v>369238</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="112"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="214" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="215"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="71"/>
+      <c r="R63" s="71"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="216"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="67"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="72"/>
+      <c r="R64" s="72"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="217" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="72"/>
+      <c r="R65" s="72"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="217"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="71"/>
+      <c r="R66" s="71"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="218"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="68"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="73"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="208" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="209"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="69"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="74"/>
+      <c r="R69" s="74"/>
+      <c r="S69" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="110" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD14D743-CA9C-4AAC-8035-6E5856B3D30E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="219">
+        <v>46088</v>
+      </c>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="223" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="224" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="225" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="229" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="231" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="229" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="233" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="213" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="100" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="132"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="80">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="92">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="116">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="139">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="138">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="81">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="53"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="53"/>
+      <c r="U9" s="140">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="141">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="54"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="116">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="143">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="116">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="139">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="116">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="139">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="103">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="55"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="106">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="134">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="55"/>
+      <c r="U13" s="140">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="144">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="142">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="105">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="138">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="119"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="119"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="129"/>
+      <c r="R22" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="119"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="129"/>
+      <c r="R24" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="119"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="129"/>
+      <c r="R26" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="119"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="119"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="119"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="121"/>
+      <c r="P29" s="121"/>
+      <c r="Q29" s="129"/>
+      <c r="R29" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="119"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="129"/>
+      <c r="R30" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="119"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="129"/>
+      <c r="R31" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="119"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="129"/>
+      <c r="R33" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="119"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="129"/>
+      <c r="R34" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="119"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="129"/>
+      <c r="R35" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="121"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="129"/>
+      <c r="R36" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="119"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="129"/>
+      <c r="R37" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="147" t="s">
+        <v>33</v>
+      </c>
       <c r="C38" s="122"/>
       <c r="D38" s="123"/>
       <c r="E38" s="124"/>
@@ -29113,7 +33296,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="211" t="s">
+      <c r="G62" s="214" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -29131,7 +33314,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="212"/>
+      <c r="G63" s="215"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -29147,7 +33330,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="213"/>
+      <c r="G64" s="216"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -29163,7 +33346,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="214" t="s">
+      <c r="G65" s="217" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -29181,7 +33364,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="214"/>
+      <c r="G66" s="217"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -29197,7 +33380,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="215"/>
+      <c r="G67" s="218"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -29217,10 +33400,3913 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="208" t="s">
+      <c r="C69" s="211" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="209"/>
+      <c r="D69" s="212"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="69"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="74"/>
+      <c r="R69" s="74"/>
+      <c r="S69" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="110" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C94B190-FADE-4B77-A489-9A6036655427}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="219">
+        <v>46089</v>
+      </c>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="221"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="223" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="224" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="225" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="226"/>
+      <c r="G4" s="227" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="229" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="231" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="229" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="233" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="234"/>
+      <c r="N4" s="234"/>
+      <c r="O4" s="234"/>
+      <c r="P4" s="234"/>
+      <c r="Q4" s="234"/>
+      <c r="R4" s="234"/>
+      <c r="S4" s="234"/>
+      <c r="T4" s="234"/>
+      <c r="U4" s="234"/>
+      <c r="V4" s="235"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="236"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="222"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="213" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="228"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="230"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="100" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="132"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="80">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="92">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="116">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="139">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="138">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="81">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="53"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="53"/>
+      <c r="U9" s="140">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="141">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="54"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="116">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="143">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="116">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="139">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="116">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="139">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="103">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="55"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="106">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="134">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="55"/>
+      <c r="U13" s="140">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="144">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="142">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="105">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="138">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="119"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="119"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="129"/>
+      <c r="R22" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="119"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="129"/>
+      <c r="R24" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="119"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="129"/>
+      <c r="R26" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="119"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="119"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="119"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="121"/>
+      <c r="P29" s="121"/>
+      <c r="Q29" s="129"/>
+      <c r="R29" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="119"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="129"/>
+      <c r="R30" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="119"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="129"/>
+      <c r="R31" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="119"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="129"/>
+      <c r="R33" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="119"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="129"/>
+      <c r="R34" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="119"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="129"/>
+      <c r="R35" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="121"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="129"/>
+      <c r="R36" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="119"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="129"/>
+      <c r="R37" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="122"/>
+      <c r="D38" s="123"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="53"/>
+      <c r="L38" s="130"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130"/>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="134">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="53"/>
+      <c r="U38" s="140">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="144">
+        <f>U38/6</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="142">
+        <f>I38*6+J38</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="54"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="119"/>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="121"/>
+      <c r="P39" s="121"/>
+      <c r="Q39" s="129"/>
+      <c r="R39" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="116">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="138">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="129"/>
+      <c r="R40" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="145">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="146">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="101"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="155"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="159"/>
+      <c r="I41" s="160">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="161">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="162"/>
+      <c r="L41" s="163"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="163"/>
+      <c r="O41" s="163"/>
+      <c r="P41" s="163"/>
+      <c r="Q41" s="164"/>
+      <c r="R41" s="165">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="166">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="162"/>
+      <c r="U41" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="168">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="168">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="169"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="171" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="172"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="175"/>
+      <c r="H42" s="176"/>
+      <c r="I42" s="175">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="177">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="178"/>
+      <c r="L42" s="174"/>
+      <c r="M42" s="174"/>
+      <c r="N42" s="174"/>
+      <c r="O42" s="174"/>
+      <c r="P42" s="174"/>
+      <c r="Q42" s="179"/>
+      <c r="R42" s="180">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="181">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="178"/>
+      <c r="U42" s="182">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="183">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="184">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="185"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="119"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="116"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="122"/>
+      <c r="D44" s="123"/>
+      <c r="E44" s="124"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="76">
+        <f>C44+E44-G44</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="53"/>
+      <c r="L44" s="130"/>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130"/>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130"/>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="187">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="53"/>
+      <c r="U44" s="140">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="139">
+        <f>U44/6</f>
+        <v>0</v>
+      </c>
+      <c r="W44" s="142">
+        <f>I44*6+J44</f>
+        <v>0</v>
+      </c>
+      <c r="X44" s="54"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="119"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="121"/>
+      <c r="G45" s="79"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="129"/>
+      <c r="R45" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="116"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="138"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="119"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="121"/>
+      <c r="P46" s="121"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="137">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="116">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="143">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="138">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="119"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="121"/>
+      <c r="P47" s="121"/>
+      <c r="Q47" s="129"/>
+      <c r="R47" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="139">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="138">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="150"/>
+      <c r="D48" s="151"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="152"/>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="53"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130"/>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="53"/>
+      <c r="U48" s="140">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="144">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="142">
+        <f>I48*6+J48</f>
+        <v>0</v>
+      </c>
+      <c r="X48" s="54"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="119"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="129"/>
+      <c r="R49" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="116">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="118">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="138">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>0</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="119"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="129"/>
+      <c r="R50" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="119"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="121"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="129"/>
+      <c r="R51" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="150"/>
+      <c r="D52" s="151"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="152"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="53"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="130"/>
+      <c r="O52" s="130"/>
+      <c r="P52" s="130"/>
+      <c r="Q52" s="131"/>
+      <c r="R52" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="53"/>
+      <c r="U52" s="140">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="144">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="142">
+        <f>I52*6+J52</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="54"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="119"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="121"/>
+      <c r="P53" s="121"/>
+      <c r="Q53" s="129"/>
+      <c r="R53" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="116">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="118">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="138">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="119"/>
+      <c r="D54" s="120"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="79"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="129"/>
+      <c r="R54" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="116">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="139">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="138">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="119"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="129"/>
+      <c r="R55" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="116"/>
+      <c r="V55" s="139"/>
+      <c r="W55" s="138"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="119"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="121"/>
+      <c r="P56" s="121"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="139"/>
+      <c r="W56" s="138"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="129"/>
+      <c r="R57" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="116"/>
+      <c r="V57" s="139"/>
+      <c r="W57" s="138"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="121"/>
+      <c r="F58" s="121"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121"/>
+      <c r="O58" s="121"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="129"/>
+      <c r="R58" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="116"/>
+      <c r="V58" s="139"/>
+      <c r="W58" s="138"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="121"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="121"/>
+      <c r="M59" s="121"/>
+      <c r="N59" s="121"/>
+      <c r="O59" s="121"/>
+      <c r="P59" s="121"/>
+      <c r="Q59" s="129"/>
+      <c r="R59" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="116"/>
+      <c r="V59" s="139"/>
+      <c r="W59" s="138"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="57">
+        <f>SUM(D8:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="59">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="59">
+        <f>SUM(I8:I59)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="77">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="78">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="91">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="90">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="111">
+        <f>SUM(V8:V59)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="99">
+        <f>SUM(W8:W59)</f>
+        <v>0</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="112"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="214" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="215"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="71"/>
+      <c r="R63" s="71"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="216"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="67"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="72"/>
+      <c r="R64" s="72"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="217" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="72"/>
+      <c r="R65" s="72"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="217"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="71"/>
+      <c r="R66" s="71"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="218"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="68"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="73"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="211" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="212"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF94812F-9C84-42AD-8B7E-96ADDEE84DDE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A4CB95-49AD-4913-96A4-BA614389924E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="03,06" sheetId="95" r:id="rId7"/>
     <sheet name="03,07" sheetId="96" r:id="rId8"/>
     <sheet name="03,08" sheetId="97" r:id="rId9"/>
+    <sheet name="03,10" sheetId="98" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02,05 PROMO'!$A$1:$W$61</definedName>
@@ -32,6 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'03,06'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'03,07'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'03,08'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'03,10'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -737,8 +739,94 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{0A7E7E3D-DE30-42E5-B00C-DE280631C96D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{DC7499D7-1B48-423A-A9D8-818F52948928}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{32B494F3-E934-4A9A-A447-22DB39C8B493}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2390,7 +2478,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3031,6 +3119,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3470,15 +3567,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="P1" s="222"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3503,62 +3600,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5809,7 +5906,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -5827,7 +5924,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -5843,7 +5940,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -5859,7 +5956,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -5877,7 +5974,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -5893,7 +5990,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -6234,6 +6331,3909 @@
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAA9D48-D6D6-479F-B839-87AFD04FE0ED}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="222">
+        <v>46091</v>
+      </c>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="225" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="226" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="227" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="228" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="232" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="234" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="232" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="236" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="216" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="100" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="132"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="80">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="92">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="116">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="139">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="138">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="81">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="53"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="53"/>
+      <c r="U9" s="140">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="141">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="54"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="116">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="143">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="116">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="139">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="116">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="139">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="103">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="55"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="106">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="134">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="55"/>
+      <c r="U13" s="140">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="144">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="142">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="105">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="138">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="119"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="119"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="129"/>
+      <c r="R22" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="119"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="129"/>
+      <c r="R24" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="119"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="129"/>
+      <c r="R26" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="119"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121"/>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="119"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="119"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="121"/>
+      <c r="P29" s="121"/>
+      <c r="Q29" s="129"/>
+      <c r="R29" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="119"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="129"/>
+      <c r="R30" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="119"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="129"/>
+      <c r="R31" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="119"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="129"/>
+      <c r="R33" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="119"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="129"/>
+      <c r="R34" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="119"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="129"/>
+      <c r="R35" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="121"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="129"/>
+      <c r="R36" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="119"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="129"/>
+      <c r="R37" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="122"/>
+      <c r="D38" s="123"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="53"/>
+      <c r="L38" s="130"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130"/>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="134">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="53"/>
+      <c r="U38" s="140">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="144">
+        <f>U38/6</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="142">
+        <f>I38*6+J38</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="54"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="119"/>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="121"/>
+      <c r="P39" s="121"/>
+      <c r="Q39" s="129"/>
+      <c r="R39" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="116">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="138">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="129"/>
+      <c r="R40" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="145">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="146">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="101"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="155"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="159"/>
+      <c r="I41" s="160">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="161">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="162"/>
+      <c r="L41" s="163"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="163"/>
+      <c r="O41" s="163"/>
+      <c r="P41" s="163"/>
+      <c r="Q41" s="164"/>
+      <c r="R41" s="165">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="166">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="162"/>
+      <c r="U41" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="168">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="168">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="169"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="171" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="172"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="175"/>
+      <c r="H42" s="176"/>
+      <c r="I42" s="175">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="177">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="178"/>
+      <c r="L42" s="174"/>
+      <c r="M42" s="174"/>
+      <c r="N42" s="174"/>
+      <c r="O42" s="174"/>
+      <c r="P42" s="174"/>
+      <c r="Q42" s="179"/>
+      <c r="R42" s="180">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="181">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="178"/>
+      <c r="U42" s="182">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="183">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="184">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="185"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="119"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="116"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="122"/>
+      <c r="D44" s="123"/>
+      <c r="E44" s="124"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="76">
+        <f>C44+E44-G44</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="53"/>
+      <c r="L44" s="130"/>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130"/>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130"/>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="187">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="53"/>
+      <c r="U44" s="140">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="139">
+        <f>U44/6</f>
+        <v>0</v>
+      </c>
+      <c r="W44" s="142">
+        <f>I44*6+J44</f>
+        <v>0</v>
+      </c>
+      <c r="X44" s="54"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="119"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="121"/>
+      <c r="G45" s="79"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="129"/>
+      <c r="R45" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="116"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="138"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="119"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="121"/>
+      <c r="P46" s="121"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="137">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="116">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="143">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="138">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="119"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="121"/>
+      <c r="P47" s="121"/>
+      <c r="Q47" s="129"/>
+      <c r="R47" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="139">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="138">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="150"/>
+      <c r="D48" s="151"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="152"/>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="53"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130"/>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="53"/>
+      <c r="U48" s="140">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="144">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="142">
+        <f>I48*6+J48</f>
+        <v>0</v>
+      </c>
+      <c r="X48" s="54"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="119"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="129"/>
+      <c r="R49" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="116">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="118">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="138">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>0</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="119"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="129"/>
+      <c r="R50" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="119"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="121"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="129"/>
+      <c r="R51" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="150"/>
+      <c r="D52" s="151"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="152"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="53"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="130"/>
+      <c r="O52" s="130"/>
+      <c r="P52" s="130"/>
+      <c r="Q52" s="131"/>
+      <c r="R52" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="53"/>
+      <c r="U52" s="140">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="144">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="142">
+        <f>I52*6+J52</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="54"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="119"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="121"/>
+      <c r="P53" s="121"/>
+      <c r="Q53" s="129"/>
+      <c r="R53" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="116">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="118">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="138">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="119"/>
+      <c r="D54" s="120"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="79"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="129"/>
+      <c r="R54" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="116">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="139">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="138">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="119"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="129"/>
+      <c r="R55" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="116"/>
+      <c r="V55" s="139"/>
+      <c r="W55" s="138"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="119"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="121"/>
+      <c r="P56" s="121"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="139"/>
+      <c r="W56" s="138"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="129"/>
+      <c r="R57" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="116"/>
+      <c r="V57" s="139"/>
+      <c r="W57" s="138"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="121"/>
+      <c r="F58" s="121"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121"/>
+      <c r="O58" s="121"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="129"/>
+      <c r="R58" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="116"/>
+      <c r="V58" s="139"/>
+      <c r="W58" s="138"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="121"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="121"/>
+      <c r="M59" s="121"/>
+      <c r="N59" s="121"/>
+      <c r="O59" s="121"/>
+      <c r="P59" s="121"/>
+      <c r="Q59" s="129"/>
+      <c r="R59" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="116"/>
+      <c r="V59" s="139"/>
+      <c r="W59" s="138"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="57">
+        <f>SUM(D8:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="59">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="59">
+        <f>SUM(I8:I59)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="77">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="77">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="78">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="91">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="90">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="111">
+        <f>SUM(V8:V59)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="99">
+        <f>SUM(W8:W59)</f>
+        <v>0</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="112"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="217" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="218"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="71"/>
+      <c r="R63" s="71"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="219"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="67"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="72"/>
+      <c r="R64" s="72"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="220" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="72"/>
+      <c r="R65" s="72"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="220"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="71"/>
+      <c r="R66" s="71"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="221"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="68"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="73"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="214" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="215"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="69"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="74"/>
+      <c r="R69" s="74"/>
+      <c r="S69" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="110" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6286,15 +10286,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
+      <c r="P1" s="222">
         <v>46058</v>
       </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="221"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="224"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6317,60 +10317,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="239"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9179,7 +13179,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -9197,7 +13197,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -9213,7 +13213,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -9229,7 +13229,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -9247,7 +13247,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -9263,7 +13263,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -9657,17 +13657,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
+      <c r="P1" s="222">
         <v>46083</v>
       </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9692,62 +13692,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13254,7 +17254,7 @@
       <c r="V62" s="203"/>
     </row>
     <row r="63" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G63" s="214" t="s">
+      <c r="G63" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="60"/>
@@ -13272,7 +17272,7 @@
       <c r="S63" s="32"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="215"/>
+      <c r="G64" s="218"/>
       <c r="H64" s="61"/>
       <c r="I64" s="61"/>
       <c r="J64" s="24" t="s">
@@ -13288,7 +17288,7 @@
       <c r="S64" s="35"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="216"/>
+      <c r="G65" s="219"/>
       <c r="H65" s="62"/>
       <c r="I65" s="62"/>
       <c r="J65" s="24" t="s">
@@ -13304,7 +17304,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217" t="s">
+      <c r="G66" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H66" s="63"/>
@@ -13322,7 +17322,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G67" s="217"/>
+      <c r="G67" s="220"/>
       <c r="H67" s="63"/>
       <c r="I67" s="63"/>
       <c r="J67" s="24" t="s">
@@ -13338,7 +17338,7 @@
       <c r="S67" s="35"/>
     </row>
     <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="218"/>
+      <c r="G68" s="221"/>
       <c r="H68" s="64"/>
       <c r="I68" s="64"/>
       <c r="J68" s="25" t="s">
@@ -13733,17 +17733,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
+      <c r="P1" s="222">
         <v>46084</v>
       </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -13768,62 +17768,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17303,7 +21303,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -17321,7 +21321,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -17337,7 +21337,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -17353,7 +21353,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -17371,7 +21371,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -17387,7 +21387,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -17782,17 +21782,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
+      <c r="P1" s="222">
         <v>46085</v>
       </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -17817,62 +21817,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21346,7 +25346,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -21364,7 +25364,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -21380,7 +25380,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -21396,7 +25396,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -21414,7 +25414,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -21430,7 +25430,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -21825,17 +25825,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
+      <c r="P1" s="222">
         <v>46086</v>
       </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -21860,62 +25860,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25395,7 +29395,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -25413,7 +29413,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -25429,7 +29429,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -25445,7 +29445,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -25463,7 +29463,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -25479,7 +29479,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -25874,17 +29874,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
+      <c r="P1" s="222">
         <v>46087</v>
       </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -25909,62 +29909,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="210" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -29393,7 +33393,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -29411,7 +33411,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -29427,7 +33427,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -29443,7 +33443,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -29461,7 +33461,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -29477,7 +33477,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -29872,17 +33872,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
+      <c r="P1" s="222">
         <v>46088</v>
       </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -29907,62 +33907,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30127,19 +34127,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>66</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
       <c r="G8" s="79"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="121"/>
@@ -30167,7 +34171,7 @@
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -30202,7 +34206,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>102</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
@@ -30210,7 +34216,7 @@
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
@@ -30242,7 +34248,7 @@
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -30277,30 +34283,40 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>51</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
-      <c r="G10" s="79"/>
+      <c r="G10" s="79">
+        <v>18</v>
+      </c>
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="121"/>
+      <c r="L10" s="121">
+        <v>2</v>
+      </c>
       <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
+      <c r="N10" s="121">
+        <v>1</v>
+      </c>
       <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
+      <c r="P10" s="121">
+        <v>15</v>
+      </c>
       <c r="Q10" s="129"/>
       <c r="R10" s="108">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S10" s="135">
         <f t="shared" si="1"/>
@@ -30309,15 +34325,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="116">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="V10" s="143">
         <f>U10/24</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -30352,30 +34368,38 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>23</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
-      <c r="G11" s="79"/>
+      <c r="G11" s="79">
+        <v>16</v>
+      </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="121"/>
+      <c r="L11" s="121">
+        <v>1</v>
+      </c>
       <c r="M11" s="121"/>
       <c r="N11" s="121"/>
       <c r="O11" s="121"/>
-      <c r="P11" s="121"/>
+      <c r="P11" s="121">
+        <v>15</v>
+      </c>
       <c r="Q11" s="129"/>
       <c r="R11" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S11" s="133">
         <f t="shared" si="1"/>
@@ -30384,15 +34408,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="116">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V11" s="139">
         <f>U11/24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -30427,7 +34451,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -30435,7 +34461,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -30467,7 +34493,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -30502,30 +34528,42 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>3928</v>
+      </c>
+      <c r="D13" s="123">
+        <v>5</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
+      <c r="G13" s="81">
+        <v>30</v>
+      </c>
       <c r="H13" s="82"/>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3898</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K13" s="55"/>
-      <c r="L13" s="130"/>
+      <c r="L13" s="130">
+        <v>1</v>
+      </c>
       <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
+      <c r="N13" s="130">
+        <v>10</v>
+      </c>
       <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
+      <c r="P13" s="130">
+        <v>19</v>
+      </c>
       <c r="Q13" s="131"/>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
@@ -30534,15 +34572,15 @@
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>93557</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -30584,7 +34622,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -30592,7 +34632,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -30624,7 +34664,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -30884,7 +34924,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -30892,7 +34934,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -30924,7 +34966,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -31034,7 +35076,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -31042,7 +35086,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -31074,7 +35118,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -31109,7 +35153,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -31117,7 +35163,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -31149,7 +35195,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -31184,7 +35230,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -31192,7 +35240,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -31224,7 +35272,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -31259,7 +35307,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -31267,7 +35317,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -31299,7 +35349,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -31341,30 +35391,38 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="119">
+        <v>45</v>
+      </c>
       <c r="D24" s="120"/>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
-      <c r="G24" s="79"/>
+      <c r="G24" s="79">
+        <v>3</v>
+      </c>
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K24" s="42"/>
-      <c r="L24" s="121"/>
+      <c r="L24" s="121">
+        <v>2</v>
+      </c>
       <c r="M24" s="121"/>
       <c r="N24" s="121"/>
       <c r="O24" s="121"/>
-      <c r="P24" s="121"/>
+      <c r="P24" s="121">
+        <v>1</v>
+      </c>
       <c r="Q24" s="129"/>
       <c r="R24" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S24" s="133">
         <f t="shared" si="7"/>
@@ -31373,15 +35431,15 @@
       <c r="T24" s="42"/>
       <c r="U24" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V24" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -31423,7 +35481,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -31431,7 +35491,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -31463,7 +35523,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -31498,22 +35558,30 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="C26" s="119">
+        <v>122</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
       <c r="E26" s="121"/>
       <c r="F26" s="121"/>
-      <c r="G26" s="79"/>
+      <c r="G26" s="79">
+        <v>2</v>
+      </c>
       <c r="H26" s="76"/>
       <c r="I26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J26" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
-      <c r="L26" s="121"/>
+      <c r="L26" s="121">
+        <v>2</v>
+      </c>
       <c r="M26" s="121"/>
       <c r="N26" s="121"/>
       <c r="O26" s="121"/>
@@ -31521,7 +35589,7 @@
       <c r="Q26" s="129"/>
       <c r="R26" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="133">
         <f t="shared" si="7"/>
@@ -31530,15 +35598,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -31554,7 +35622,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="119"/>
+      <c r="C27" s="119">
+        <v>16</v>
+      </c>
       <c r="D27" s="120"/>
       <c r="E27" s="121"/>
       <c r="F27" s="121"/>
@@ -31562,7 +35632,7 @@
       <c r="H27" s="76"/>
       <c r="I27" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J27" s="80">
         <f t="shared" si="4"/>
@@ -31594,7 +35664,7 @@
       </c>
       <c r="W27" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -31672,30 +35742,40 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="119"/>
+      <c r="C29" s="119">
+        <v>95</v>
+      </c>
       <c r="D29" s="120"/>
       <c r="E29" s="121"/>
       <c r="F29" s="121"/>
-      <c r="G29" s="79"/>
+      <c r="G29" s="79">
+        <v>5</v>
+      </c>
       <c r="H29" s="76"/>
       <c r="I29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J29" s="80">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="121"/>
+      <c r="L29" s="121">
+        <v>1</v>
+      </c>
       <c r="M29" s="121"/>
-      <c r="N29" s="121"/>
+      <c r="N29" s="121">
+        <v>2</v>
+      </c>
       <c r="O29" s="121"/>
-      <c r="P29" s="121"/>
+      <c r="P29" s="121">
+        <v>2</v>
+      </c>
       <c r="Q29" s="129"/>
       <c r="R29" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S29" s="133">
         <f t="shared" si="7"/>
@@ -31704,15 +35784,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V29" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W29" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -31731,7 +35811,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="119"/>
+      <c r="C30" s="119">
+        <v>10</v>
+      </c>
       <c r="D30" s="120"/>
       <c r="E30" s="121"/>
       <c r="F30" s="121"/>
@@ -31739,7 +35821,7 @@
       <c r="H30" s="76"/>
       <c r="I30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="80">
         <f t="shared" si="4"/>
@@ -31771,7 +35853,7 @@
       </c>
       <c r="W30" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -31783,7 +35865,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="119">
+        <v>60</v>
+      </c>
       <c r="D31" s="120"/>
       <c r="E31" s="121"/>
       <c r="F31" s="121"/>
@@ -31791,7 +35875,7 @@
       <c r="H31" s="76"/>
       <c r="I31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J31" s="80">
         <f t="shared" si="4"/>
@@ -31823,7 +35907,7 @@
       </c>
       <c r="W31" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -31835,15 +35919,19 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="119"/>
+      <c r="C32" s="119">
+        <v>4</v>
+      </c>
       <c r="D32" s="120"/>
       <c r="E32" s="121"/>
       <c r="F32" s="121"/>
-      <c r="G32" s="79"/>
+      <c r="G32" s="79">
+        <v>2</v>
+      </c>
       <c r="H32" s="76"/>
       <c r="I32" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="80">
         <f t="shared" si="4"/>
@@ -31854,11 +35942,13 @@
       <c r="M32" s="121"/>
       <c r="N32" s="121"/>
       <c r="O32" s="121"/>
-      <c r="P32" s="121"/>
+      <c r="P32" s="121">
+        <v>2</v>
+      </c>
       <c r="Q32" s="129"/>
       <c r="R32" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32" s="133">
         <f t="shared" si="7"/>
@@ -31867,15 +35957,15 @@
       <c r="T32" s="41"/>
       <c r="U32" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V32" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W32" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -31991,19 +36081,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="120"/>
+      <c r="C35" s="119">
+        <v>135</v>
+      </c>
+      <c r="D35" s="120">
+        <v>17</v>
+      </c>
       <c r="E35" s="121"/>
       <c r="F35" s="121"/>
       <c r="G35" s="79"/>
       <c r="H35" s="76"/>
       <c r="I35" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="J35" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="121"/>
@@ -32031,7 +36125,7 @@
       </c>
       <c r="W35" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3257</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -32147,30 +36241,42 @@
       <c r="B38" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="122"/>
-      <c r="D38" s="123"/>
+      <c r="C38" s="122">
+        <v>4207</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
       <c r="E38" s="124"/>
       <c r="F38" s="124"/>
-      <c r="G38" s="81"/>
+      <c r="G38" s="81">
+        <v>144</v>
+      </c>
       <c r="H38" s="82"/>
       <c r="I38" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4063</v>
       </c>
       <c r="J38" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="53"/>
-      <c r="L38" s="130"/>
+      <c r="L38" s="130">
+        <v>17</v>
+      </c>
       <c r="M38" s="130"/>
-      <c r="N38" s="130"/>
+      <c r="N38" s="130">
+        <v>68</v>
+      </c>
       <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
+      <c r="P38" s="130">
+        <v>59</v>
+      </c>
       <c r="Q38" s="131"/>
       <c r="R38" s="106">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="S38" s="134">
         <f t="shared" si="7"/>
@@ -32179,15 +36285,15 @@
       <c r="T38" s="53"/>
       <c r="U38" s="140">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="V38" s="144">
         <f>U38/6</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="W38" s="142">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>24380</v>
       </c>
       <c r="X38" s="54"/>
     </row>
@@ -32199,7 +36305,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="119"/>
+      <c r="C39" s="119">
+        <v>12</v>
+      </c>
       <c r="D39" s="120"/>
       <c r="E39" s="121"/>
       <c r="F39" s="121"/>
@@ -32207,7 +36315,7 @@
       <c r="H39" s="76"/>
       <c r="I39" s="79">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J39" s="80">
         <f t="shared" si="4"/>
@@ -32239,7 +36347,7 @@
       </c>
       <c r="W39" s="138">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -32303,22 +36411,28 @@
       <c r="B41" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="155"/>
+      <c r="C41" s="155">
+        <v>558</v>
+      </c>
       <c r="D41" s="156"/>
       <c r="E41" s="157"/>
       <c r="F41" s="157"/>
-      <c r="G41" s="158"/>
+      <c r="G41" s="158">
+        <v>50</v>
+      </c>
       <c r="H41" s="159"/>
       <c r="I41" s="160">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="J41" s="161">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K41" s="162"/>
-      <c r="L41" s="163"/>
+      <c r="L41" s="163">
+        <v>50</v>
+      </c>
       <c r="M41" s="163"/>
       <c r="N41" s="163"/>
       <c r="O41" s="163"/>
@@ -32326,7 +36440,7 @@
       <c r="Q41" s="164"/>
       <c r="R41" s="165">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S41" s="166">
         <f t="shared" si="7"/>
@@ -32335,15 +36449,15 @@
       <c r="T41" s="162"/>
       <c r="U41" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="V41" s="168">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W41" s="168">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>12192</v>
       </c>
       <c r="X41" s="169"/>
     </row>
@@ -32355,15 +36469,19 @@
       <c r="B42" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="172"/>
+      <c r="C42" s="172">
+        <v>1439</v>
+      </c>
       <c r="D42" s="173"/>
       <c r="E42" s="174"/>
       <c r="F42" s="174"/>
-      <c r="G42" s="175"/>
+      <c r="G42" s="175">
+        <v>16</v>
+      </c>
       <c r="H42" s="176"/>
       <c r="I42" s="175">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="J42" s="177">
         <f t="shared" si="4"/>
@@ -32372,13 +36490,17 @@
       <c r="K42" s="178"/>
       <c r="L42" s="174"/>
       <c r="M42" s="174"/>
-      <c r="N42" s="174"/>
+      <c r="N42" s="174">
+        <v>4</v>
+      </c>
       <c r="O42" s="174"/>
-      <c r="P42" s="174"/>
+      <c r="P42" s="174">
+        <v>12</v>
+      </c>
       <c r="Q42" s="179"/>
       <c r="R42" s="180">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S42" s="181">
         <f t="shared" si="7"/>
@@ -32387,15 +36509,15 @@
       <c r="T42" s="178"/>
       <c r="U42" s="182">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V42" s="183">
         <f>U42/12</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W42" s="184">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>17076</v>
       </c>
       <c r="X42" s="185"/>
     </row>
@@ -32450,30 +36572,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="122"/>
-      <c r="D44" s="123"/>
+      <c r="C44" s="122">
+        <v>30961</v>
+      </c>
+      <c r="D44" s="123">
+        <v>4</v>
+      </c>
       <c r="E44" s="124"/>
       <c r="F44" s="124"/>
-      <c r="G44" s="81"/>
+      <c r="G44" s="81">
+        <v>1136</v>
+      </c>
       <c r="H44" s="82"/>
       <c r="I44" s="76">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>29825</v>
       </c>
       <c r="J44" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" s="53"/>
-      <c r="L44" s="130"/>
+      <c r="L44" s="130">
+        <v>319</v>
+      </c>
       <c r="M44" s="130"/>
-      <c r="N44" s="130"/>
+      <c r="N44" s="130">
+        <v>385</v>
+      </c>
       <c r="O44" s="130"/>
-      <c r="P44" s="130"/>
+      <c r="P44" s="130">
+        <v>432</v>
+      </c>
       <c r="Q44" s="131"/>
       <c r="R44" s="187">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1136</v>
       </c>
       <c r="S44" s="188">
         <f t="shared" si="7"/>
@@ -32482,15 +36616,15 @@
       <c r="T44" s="53"/>
       <c r="U44" s="140">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>6816</v>
       </c>
       <c r="V44" s="139">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1136</v>
       </c>
       <c r="W44" s="142">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>178954</v>
       </c>
       <c r="X44" s="54"/>
       <c r="Z44" s="47"/>
@@ -32650,22 +36784,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="150"/>
-      <c r="D48" s="151"/>
+      <c r="C48" s="150">
+        <v>2349</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
       <c r="E48" s="130"/>
       <c r="F48" s="130"/>
-      <c r="G48" s="152"/>
+      <c r="G48" s="152">
+        <v>1</v>
+      </c>
       <c r="H48" s="148"/>
       <c r="I48" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2348</v>
       </c>
       <c r="J48" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="53"/>
-      <c r="L48" s="130"/>
+      <c r="L48" s="130">
+        <v>1</v>
+      </c>
       <c r="M48" s="130"/>
       <c r="N48" s="130"/>
       <c r="O48" s="130"/>
@@ -32673,7 +36815,7 @@
       <c r="Q48" s="131"/>
       <c r="R48" s="106">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="153">
         <f t="shared" si="7"/>
@@ -32682,15 +36824,15 @@
       <c r="T48" s="53"/>
       <c r="U48" s="140">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V48" s="144">
         <f>U48/6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="142">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>14092</v>
       </c>
       <c r="X48" s="54"/>
     </row>
@@ -32702,7 +36844,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="119"/>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
       <c r="D49" s="120"/>
       <c r="E49" s="121"/>
       <c r="F49" s="121"/>
@@ -32710,7 +36854,7 @@
       <c r="H49" s="76"/>
       <c r="I49" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="80">
         <f t="shared" si="4"/>
@@ -32742,7 +36886,7 @@
       </c>
       <c r="W49" s="138">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -32858,7 +37002,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="150"/>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
       <c r="D52" s="151"/>
       <c r="E52" s="130"/>
       <c r="F52" s="130"/>
@@ -32866,7 +37012,7 @@
       <c r="H52" s="148"/>
       <c r="I52" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="149">
         <f t="shared" si="4"/>
@@ -32898,7 +37044,7 @@
       </c>
       <c r="W52" s="142">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="54"/>
     </row>
@@ -32962,7 +37108,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="119"/>
+      <c r="C54" s="119">
+        <v>5</v>
+      </c>
       <c r="D54" s="120"/>
       <c r="E54" s="121"/>
       <c r="F54" s="121"/>
@@ -32970,7 +37118,7 @@
       <c r="H54" s="76"/>
       <c r="I54" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J54" s="80">
         <f t="shared" si="4"/>
@@ -33002,7 +37150,7 @@
       </c>
       <c r="W54" s="138">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -33217,11 +37365,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>44265</v>
       </c>
       <c r="D60" s="57">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -33230,7 +37378,7 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="H60" s="59">
         <f>SUM(H8:H59)</f>
@@ -33238,16 +37386,16 @@
       </c>
       <c r="I60" s="59">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>42842</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="77">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="M60" s="77">
         <f t="shared" si="20"/>
@@ -33255,7 +37403,7 @@
       </c>
       <c r="N60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="O60" s="77">
         <f t="shared" si="20"/>
@@ -33263,7 +37411,7 @@
       </c>
       <c r="P60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="Q60" s="78">
         <f t="shared" si="20"/>
@@ -33271,7 +37419,7 @@
       </c>
       <c r="R60" s="91">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="S60" s="90">
         <f t="shared" si="20"/>
@@ -33280,15 +37428,15 @@
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>10902</v>
       </c>
       <c r="V60" s="111">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="99">
+        <v>1423</v>
+      </c>
+      <c r="W60" s="204">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>358336</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -33296,7 +37444,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -33314,7 +37462,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -33330,7 +37478,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -33346,7 +37494,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -33364,7 +37512,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -33380,7 +37528,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -33775,17 +37923,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="219">
-        <v>46089</v>
-      </c>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="221"/>
+      <c r="P1" s="222">
+        <v>46090</v>
+      </c>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="224"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -33810,62 +37958,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="222" t="s">
+      <c r="B4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="223" t="s">
+      <c r="C4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="227" t="s">
+      <c r="F4" s="229"/>
+      <c r="G4" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="229" t="s">
+      <c r="H4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="231" t="s">
+      <c r="I4" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="229" t="s">
+      <c r="J4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="234"/>
-      <c r="N4" s="234"/>
-      <c r="O4" s="234"/>
-      <c r="P4" s="234"/>
-      <c r="Q4" s="234"/>
-      <c r="R4" s="234"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="236"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="239"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="222"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="228"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="233"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -37199,7 +41347,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="214" t="s">
+      <c r="G62" s="217" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -37217,7 +41365,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="215"/>
+      <c r="G63" s="218"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -37233,7 +41381,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="216"/>
+      <c r="G64" s="219"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -37249,7 +41397,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="217" t="s">
+      <c r="G65" s="220" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -37267,7 +41415,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="217"/>
+      <c r="G66" s="220"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -37283,7 +41431,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="218"/>
+      <c r="G67" s="221"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A4CB95-49AD-4913-96A4-BA614389924E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503ACAAE-91FF-4EFC-974D-38D44F47755C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="03,05" sheetId="94" r:id="rId6"/>
     <sheet name="03,06" sheetId="95" r:id="rId7"/>
     <sheet name="03,07" sheetId="96" r:id="rId8"/>
-    <sheet name="03,08" sheetId="97" r:id="rId9"/>
+    <sheet name="03,09" sheetId="97" r:id="rId9"/>
     <sheet name="03,10" sheetId="98" r:id="rId10"/>
   </sheets>
   <definedNames>
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'03,05'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'03,06'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'03,07'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'03,08'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'03,09'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'03,10'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
@@ -38178,22 +38178,30 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>66</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
-      <c r="G8" s="79"/>
+      <c r="G8" s="79">
+        <v>1</v>
+      </c>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
-      <c r="L8" s="121"/>
+      <c r="L8" s="121">
+        <v>1</v>
+      </c>
       <c r="M8" s="121"/>
       <c r="N8" s="121"/>
       <c r="O8" s="121"/>
@@ -38201,7 +38209,7 @@
       <c r="Q8" s="129"/>
       <c r="R8" s="92">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="133">
         <f t="shared" si="1"/>
@@ -38210,15 +38218,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="116">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="139">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -38253,7 +38261,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>102</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
@@ -38261,7 +38271,7 @@
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
@@ -38293,7 +38303,7 @@
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -38328,7 +38338,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>33</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
@@ -38336,7 +38348,7 @@
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
@@ -38368,7 +38380,7 @@
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -38403,7 +38415,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>7</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
@@ -38411,7 +38425,7 @@
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
@@ -38443,7 +38457,7 @@
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -38478,7 +38492,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -38486,7 +38502,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -38518,7 +38534,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -38553,47 +38569,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>3898</v>
+      </c>
+      <c r="D13" s="123">
+        <v>5</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="G13" s="81">
+        <v>55</v>
+      </c>
+      <c r="H13" s="82">
+        <v>13</v>
+      </c>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3843</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K13" s="55"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
+      <c r="L13" s="130">
+        <v>20</v>
+      </c>
+      <c r="M13" s="130">
+        <v>5</v>
+      </c>
+      <c r="N13" s="130">
+        <v>20</v>
+      </c>
+      <c r="O13" s="130">
+        <v>8</v>
+      </c>
+      <c r="P13" s="130">
+        <v>15</v>
+      </c>
       <c r="Q13" s="131"/>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>92224</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -38635,7 +38669,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -38643,7 +38679,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -38675,7 +38711,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -38935,7 +38971,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -38943,7 +38981,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -38975,7 +39013,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -39085,7 +39123,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -39093,7 +39133,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -39125,7 +39165,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -39160,7 +39200,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -39168,7 +39210,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -39200,7 +39242,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -39235,7 +39277,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -39243,7 +39287,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -39275,7 +39319,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -39310,7 +39354,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -39318,7 +39364,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -39350,7 +39396,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -39392,30 +39438,38 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="119">
+        <v>42</v>
+      </c>
       <c r="D24" s="120"/>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
-      <c r="G24" s="79"/>
+      <c r="G24" s="79">
+        <v>3</v>
+      </c>
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K24" s="42"/>
-      <c r="L24" s="121"/>
+      <c r="L24" s="121">
+        <v>2</v>
+      </c>
       <c r="M24" s="121"/>
       <c r="N24" s="121"/>
       <c r="O24" s="121"/>
-      <c r="P24" s="121"/>
+      <c r="P24" s="121">
+        <v>1</v>
+      </c>
       <c r="Q24" s="129"/>
       <c r="R24" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S24" s="133">
         <f t="shared" si="7"/>
@@ -39424,15 +39478,15 @@
       <c r="T24" s="42"/>
       <c r="U24" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V24" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -39474,7 +39528,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -39482,7 +39538,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -39514,7 +39570,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -39549,19 +39605,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="C26" s="119">
+        <v>120</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
       <c r="E26" s="121"/>
       <c r="F26" s="121"/>
       <c r="G26" s="79"/>
       <c r="H26" s="76"/>
       <c r="I26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J26" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="121"/>
@@ -39589,7 +39649,7 @@
       </c>
       <c r="W26" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -39605,7 +39665,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="119"/>
+      <c r="C27" s="119">
+        <v>16</v>
+      </c>
       <c r="D27" s="120"/>
       <c r="E27" s="121"/>
       <c r="F27" s="121"/>
@@ -39613,7 +39675,7 @@
       <c r="H27" s="76"/>
       <c r="I27" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J27" s="80">
         <f t="shared" si="4"/>
@@ -39645,7 +39707,7 @@
       </c>
       <c r="W27" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -39723,30 +39785,38 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="119"/>
+      <c r="C29" s="119">
+        <v>90</v>
+      </c>
       <c r="D29" s="120"/>
       <c r="E29" s="121"/>
       <c r="F29" s="121"/>
-      <c r="G29" s="79"/>
+      <c r="G29" s="79">
+        <v>3</v>
+      </c>
       <c r="H29" s="76"/>
       <c r="I29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J29" s="80">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="121"/>
+      <c r="L29" s="121">
+        <v>1</v>
+      </c>
       <c r="M29" s="121"/>
       <c r="N29" s="121"/>
       <c r="O29" s="121"/>
-      <c r="P29" s="121"/>
+      <c r="P29" s="121">
+        <v>2</v>
+      </c>
       <c r="Q29" s="129"/>
       <c r="R29" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S29" s="133">
         <f t="shared" si="7"/>
@@ -39755,15 +39825,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V29" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -39782,7 +39852,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="119"/>
+      <c r="C30" s="119">
+        <v>10</v>
+      </c>
       <c r="D30" s="120"/>
       <c r="E30" s="121"/>
       <c r="F30" s="121"/>
@@ -39790,7 +39862,7 @@
       <c r="H30" s="76"/>
       <c r="I30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="80">
         <f t="shared" si="4"/>
@@ -39822,7 +39894,7 @@
       </c>
       <c r="W30" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -39834,7 +39906,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="119">
+        <v>60</v>
+      </c>
       <c r="D31" s="120"/>
       <c r="E31" s="121"/>
       <c r="F31" s="121"/>
@@ -39842,7 +39916,7 @@
       <c r="H31" s="76"/>
       <c r="I31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J31" s="80">
         <f t="shared" si="4"/>
@@ -39874,7 +39948,7 @@
       </c>
       <c r="W31" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -39886,7 +39960,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="119"/>
+      <c r="C32" s="119">
+        <v>2</v>
+      </c>
       <c r="D32" s="120"/>
       <c r="E32" s="121"/>
       <c r="F32" s="121"/>
@@ -39894,7 +39970,7 @@
       <c r="H32" s="76"/>
       <c r="I32" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="80">
         <f t="shared" si="4"/>
@@ -39926,7 +40002,7 @@
       </c>
       <c r="W32" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -40042,47 +40118,59 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="120"/>
+      <c r="C35" s="119">
+        <v>135</v>
+      </c>
+      <c r="D35" s="120">
+        <v>17</v>
+      </c>
       <c r="E35" s="121"/>
       <c r="F35" s="121"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="76"/>
+      <c r="G35" s="79">
+        <v>1</v>
+      </c>
+      <c r="H35" s="76">
+        <v>12</v>
+      </c>
       <c r="I35" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="J35" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="121"/>
-      <c r="M35" s="121"/>
+      <c r="L35" s="121">
+        <v>1</v>
+      </c>
+      <c r="M35" s="121">
+        <v>12</v>
+      </c>
       <c r="N35" s="121"/>
       <c r="O35" s="121"/>
       <c r="P35" s="121"/>
       <c r="Q35" s="129"/>
       <c r="R35" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="133">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T35" s="41"/>
       <c r="U35" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V35" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3221</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -40198,30 +40286,42 @@
       <c r="B38" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="122"/>
-      <c r="D38" s="123"/>
+      <c r="C38" s="122">
+        <v>4063</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
       <c r="E38" s="124"/>
       <c r="F38" s="124"/>
-      <c r="G38" s="81"/>
+      <c r="G38" s="81">
+        <v>248</v>
+      </c>
       <c r="H38" s="82"/>
       <c r="I38" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3815</v>
       </c>
       <c r="J38" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="53"/>
-      <c r="L38" s="130"/>
+      <c r="L38" s="130">
+        <v>67</v>
+      </c>
       <c r="M38" s="130"/>
-      <c r="N38" s="130"/>
+      <c r="N38" s="130">
+        <v>118</v>
+      </c>
       <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
+      <c r="P38" s="130">
+        <v>63</v>
+      </c>
       <c r="Q38" s="131"/>
       <c r="R38" s="106">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="S38" s="134">
         <f t="shared" si="7"/>
@@ -40230,15 +40330,15 @@
       <c r="T38" s="53"/>
       <c r="U38" s="140">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="V38" s="144">
         <f>U38/6</f>
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="W38" s="142">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>22892</v>
       </c>
       <c r="X38" s="54"/>
     </row>
@@ -40250,7 +40350,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="119"/>
+      <c r="C39" s="119">
+        <v>12</v>
+      </c>
       <c r="D39" s="120"/>
       <c r="E39" s="121"/>
       <c r="F39" s="121"/>
@@ -40258,7 +40360,7 @@
       <c r="H39" s="76"/>
       <c r="I39" s="79">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J39" s="80">
         <f t="shared" si="4"/>
@@ -40290,7 +40392,7 @@
       </c>
       <c r="W39" s="138">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -40354,15 +40456,19 @@
       <c r="B41" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="155"/>
+      <c r="C41" s="155">
+        <v>508</v>
+      </c>
       <c r="D41" s="156"/>
       <c r="E41" s="157"/>
       <c r="F41" s="157"/>
-      <c r="G41" s="158"/>
+      <c r="G41" s="158">
+        <v>1</v>
+      </c>
       <c r="H41" s="159"/>
       <c r="I41" s="160">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="J41" s="161">
         <f t="shared" si="4"/>
@@ -40373,11 +40479,13 @@
       <c r="M41" s="163"/>
       <c r="N41" s="163"/>
       <c r="O41" s="163"/>
-      <c r="P41" s="163"/>
+      <c r="P41" s="163">
+        <v>1</v>
+      </c>
       <c r="Q41" s="164"/>
       <c r="R41" s="165">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="166">
         <f t="shared" si="7"/>
@@ -40386,15 +40494,15 @@
       <c r="T41" s="162"/>
       <c r="U41" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V41" s="168">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="168">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>12168</v>
       </c>
       <c r="X41" s="169"/>
     </row>
@@ -40406,30 +40514,42 @@
       <c r="B42" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="172"/>
-      <c r="D42" s="173"/>
+      <c r="C42" s="172">
+        <v>1422</v>
+      </c>
+      <c r="D42" s="173">
+        <v>9</v>
+      </c>
       <c r="E42" s="174"/>
       <c r="F42" s="174"/>
-      <c r="G42" s="175"/>
+      <c r="G42" s="175">
+        <v>67</v>
+      </c>
       <c r="H42" s="176"/>
       <c r="I42" s="175">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1355</v>
       </c>
       <c r="J42" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K42" s="178"/>
-      <c r="L42" s="174"/>
+      <c r="L42" s="174">
+        <v>55</v>
+      </c>
       <c r="M42" s="174"/>
-      <c r="N42" s="174"/>
+      <c r="N42" s="174">
+        <v>1</v>
+      </c>
       <c r="O42" s="174"/>
-      <c r="P42" s="174"/>
+      <c r="P42" s="174">
+        <v>11</v>
+      </c>
       <c r="Q42" s="179"/>
       <c r="R42" s="180">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="S42" s="181">
         <f t="shared" si="7"/>
@@ -40438,15 +40558,15 @@
       <c r="T42" s="178"/>
       <c r="U42" s="182">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="V42" s="183">
         <f>U42/12</f>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="W42" s="184">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>16269</v>
       </c>
       <c r="X42" s="185"/>
     </row>
@@ -40501,30 +40621,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="122"/>
-      <c r="D44" s="123"/>
+      <c r="C44" s="122">
+        <v>29825</v>
+      </c>
+      <c r="D44" s="123">
+        <v>3</v>
+      </c>
       <c r="E44" s="124"/>
       <c r="F44" s="124"/>
-      <c r="G44" s="81"/>
+      <c r="G44" s="81">
+        <v>1465</v>
+      </c>
       <c r="H44" s="82"/>
       <c r="I44" s="76">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>28360</v>
       </c>
       <c r="J44" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="53"/>
-      <c r="L44" s="130"/>
+      <c r="L44" s="130">
+        <v>558</v>
+      </c>
       <c r="M44" s="130"/>
-      <c r="N44" s="130"/>
+      <c r="N44" s="130">
+        <v>538</v>
+      </c>
       <c r="O44" s="130"/>
-      <c r="P44" s="130"/>
+      <c r="P44" s="130">
+        <v>369</v>
+      </c>
       <c r="Q44" s="131"/>
       <c r="R44" s="187">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="S44" s="188">
         <f t="shared" si="7"/>
@@ -40533,15 +40665,15 @@
       <c r="T44" s="53"/>
       <c r="U44" s="140">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>8790</v>
       </c>
       <c r="V44" s="139">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="W44" s="142">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>170163</v>
       </c>
       <c r="X44" s="54"/>
       <c r="Z44" s="47"/>
@@ -40701,19 +40833,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="150"/>
-      <c r="D48" s="151"/>
+      <c r="C48" s="150">
+        <v>2348</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
       <c r="E48" s="130"/>
       <c r="F48" s="130"/>
       <c r="G48" s="152"/>
       <c r="H48" s="148"/>
       <c r="I48" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2348</v>
       </c>
       <c r="J48" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="53"/>
       <c r="L48" s="130"/>
@@ -40741,7 +40877,7 @@
       </c>
       <c r="W48" s="142">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>14092</v>
       </c>
       <c r="X48" s="54"/>
     </row>
@@ -40753,7 +40889,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="119"/>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
       <c r="D49" s="120"/>
       <c r="E49" s="121"/>
       <c r="F49" s="121"/>
@@ -40761,7 +40899,7 @@
       <c r="H49" s="76"/>
       <c r="I49" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="80">
         <f t="shared" si="4"/>
@@ -40793,7 +40931,7 @@
       </c>
       <c r="W49" s="138">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -40909,7 +41047,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="150"/>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
       <c r="D52" s="151"/>
       <c r="E52" s="130"/>
       <c r="F52" s="130"/>
@@ -40917,7 +41057,7 @@
       <c r="H52" s="148"/>
       <c r="I52" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="149">
         <f t="shared" si="4"/>
@@ -40949,7 +41089,7 @@
       </c>
       <c r="W52" s="142">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="54"/>
     </row>
@@ -41013,7 +41153,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="119"/>
+      <c r="C54" s="119">
+        <v>5</v>
+      </c>
       <c r="D54" s="120"/>
       <c r="E54" s="121"/>
       <c r="F54" s="121"/>
@@ -41021,7 +41163,7 @@
       <c r="H54" s="76"/>
       <c r="I54" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J54" s="80">
         <f t="shared" si="4"/>
@@ -41053,7 +41195,7 @@
       </c>
       <c r="W54" s="138">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -41268,11 +41410,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>42841</v>
       </c>
       <c r="D60" s="57">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -41281,40 +41423,40 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="H60" s="59">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I60" s="59">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>40997</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="77">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="M60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="O60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="Q60" s="78">
         <f t="shared" si="20"/>
@@ -41322,24 +41464,24 @@
       </c>
       <c r="R60" s="91">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="S60" s="90">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>12618</v>
       </c>
       <c r="V60" s="111">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="99">
+        <v>1844</v>
+      </c>
+      <c r="W60" s="204">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>345689</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2AB7A2-9340-4543-B7B0-7E63FEB6CECC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0797D517-98B5-452B-81AD-58DF73AEAEF4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15021,19 +15021,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>63</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
       <c r="G8" s="79"/>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="121"/>
@@ -15061,7 +15065,7 @@
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -15096,7 +15100,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>100</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
@@ -15104,7 +15110,7 @@
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
@@ -15136,7 +15142,7 @@
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -15171,15 +15177,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>31</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
-      <c r="G10" s="79"/>
+      <c r="G10" s="79">
+        <v>1</v>
+      </c>
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
@@ -15190,11 +15200,13 @@
       <c r="M10" s="121"/>
       <c r="N10" s="121"/>
       <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
+      <c r="P10" s="121">
+        <v>1</v>
+      </c>
       <c r="Q10" s="129"/>
       <c r="R10" s="108">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="135">
         <f t="shared" si="1"/>
@@ -15203,15 +15215,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="116">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V10" s="143">
         <f>U10/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -15246,15 +15258,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>4</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
-      <c r="G11" s="79"/>
+      <c r="G11" s="79">
+        <v>1</v>
+      </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="80">
         <f t="shared" si="0"/>
@@ -15265,11 +15281,13 @@
       <c r="M11" s="121"/>
       <c r="N11" s="121"/>
       <c r="O11" s="121"/>
-      <c r="P11" s="121"/>
+      <c r="P11" s="121">
+        <v>1</v>
+      </c>
       <c r="Q11" s="129"/>
       <c r="R11" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="133">
         <f t="shared" si="1"/>
@@ -15278,15 +15296,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="116">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="139">
         <f>U11/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -15321,7 +15339,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
@@ -15329,7 +15349,7 @@
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
@@ -15361,7 +15381,7 @@
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -15396,47 +15416,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>3773</v>
+      </c>
+      <c r="D13" s="123">
+        <v>14</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="G13" s="81">
+        <v>45</v>
+      </c>
+      <c r="H13" s="82">
+        <v>21</v>
+      </c>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="K13" s="55"/>
-      <c r="L13" s="130"/>
+      <c r="L13" s="130">
+        <v>15</v>
+      </c>
       <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="131"/>
+      <c r="N13" s="130">
+        <v>16</v>
+      </c>
+      <c r="O13" s="130">
+        <v>17</v>
+      </c>
+      <c r="P13" s="130">
+        <v>14</v>
+      </c>
+      <c r="Q13" s="131">
+        <v>4</v>
+      </c>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>89465</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -15478,7 +15516,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
@@ -15486,7 +15526,7 @@
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -15518,7 +15558,7 @@
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -15778,7 +15818,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -15786,7 +15828,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -15818,7 +15860,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -15928,7 +15970,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -15936,7 +15980,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -15968,7 +16012,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -16003,7 +16047,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -16011,7 +16057,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -16043,7 +16089,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -16078,7 +16124,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -16086,7 +16134,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -16118,7 +16166,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -16153,7 +16201,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
@@ -16161,7 +16211,7 @@
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -16193,7 +16243,7 @@
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -16235,19 +16285,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="120"/>
+      <c r="C24" s="119">
+        <v>38</v>
+      </c>
+      <c r="D24" s="120">
+        <v>19</v>
+      </c>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
       <c r="G24" s="79"/>
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="121"/>
@@ -16275,7 +16329,7 @@
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -16317,7 +16371,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
@@ -16325,7 +16381,7 @@
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -16357,7 +16413,7 @@
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -16392,19 +16448,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
+      <c r="C26" s="119">
+        <v>120</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
       <c r="E26" s="121"/>
       <c r="F26" s="121"/>
       <c r="G26" s="79"/>
       <c r="H26" s="76"/>
       <c r="I26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J26" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="121"/>
@@ -16432,7 +16492,7 @@
       </c>
       <c r="W26" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -16448,7 +16508,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="119"/>
+      <c r="C27" s="119">
+        <v>16</v>
+      </c>
       <c r="D27" s="120"/>
       <c r="E27" s="121"/>
       <c r="F27" s="121"/>
@@ -16456,7 +16518,7 @@
       <c r="H27" s="76"/>
       <c r="I27" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J27" s="80">
         <f t="shared" si="4"/>
@@ -16488,7 +16550,7 @@
       </c>
       <c r="W27" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -16566,15 +16628,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="119"/>
+      <c r="C29" s="119">
+        <v>84</v>
+      </c>
       <c r="D29" s="120"/>
       <c r="E29" s="121"/>
       <c r="F29" s="121"/>
-      <c r="G29" s="79"/>
+      <c r="G29" s="79">
+        <v>3</v>
+      </c>
       <c r="H29" s="76"/>
       <c r="I29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="J29" s="80">
         <f t="shared" si="4"/>
@@ -16585,11 +16651,13 @@
       <c r="M29" s="121"/>
       <c r="N29" s="121"/>
       <c r="O29" s="121"/>
-      <c r="P29" s="121"/>
+      <c r="P29" s="121">
+        <v>3</v>
+      </c>
       <c r="Q29" s="129"/>
       <c r="R29" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S29" s="133">
         <f t="shared" si="7"/>
@@ -16598,15 +16666,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V29" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -16625,7 +16693,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="119"/>
+      <c r="C30" s="119">
+        <v>8</v>
+      </c>
       <c r="D30" s="120"/>
       <c r="E30" s="121"/>
       <c r="F30" s="121"/>
@@ -16633,7 +16703,7 @@
       <c r="H30" s="76"/>
       <c r="I30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J30" s="80">
         <f t="shared" si="4"/>
@@ -16665,7 +16735,7 @@
       </c>
       <c r="W30" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -16677,7 +16747,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="119">
+        <v>58</v>
+      </c>
       <c r="D31" s="120"/>
       <c r="E31" s="121"/>
       <c r="F31" s="121"/>
@@ -16685,7 +16757,7 @@
       <c r="H31" s="76"/>
       <c r="I31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J31" s="80">
         <f t="shared" si="4"/>
@@ -16717,7 +16789,7 @@
       </c>
       <c r="W31" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -16729,7 +16801,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="119"/>
+      <c r="C32" s="119">
+        <v>1</v>
+      </c>
       <c r="D32" s="120"/>
       <c r="E32" s="121"/>
       <c r="F32" s="121"/>
@@ -16737,7 +16811,7 @@
       <c r="H32" s="76"/>
       <c r="I32" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="80">
         <f t="shared" si="4"/>
@@ -16769,7 +16843,7 @@
       </c>
       <c r="W32" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -16885,30 +16959,40 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="120"/>
+      <c r="C35" s="119">
+        <v>128</v>
+      </c>
+      <c r="D35" s="120">
+        <v>5</v>
+      </c>
       <c r="E35" s="121"/>
       <c r="F35" s="121"/>
-      <c r="G35" s="79"/>
+      <c r="G35" s="79">
+        <v>12</v>
+      </c>
       <c r="H35" s="76"/>
       <c r="I35" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="J35" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="121"/>
       <c r="M35" s="121"/>
-      <c r="N35" s="121"/>
+      <c r="N35" s="121">
+        <v>10</v>
+      </c>
       <c r="O35" s="121"/>
-      <c r="P35" s="121"/>
+      <c r="P35" s="121">
+        <v>2</v>
+      </c>
       <c r="Q35" s="129"/>
       <c r="R35" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S35" s="133">
         <f t="shared" si="7"/>
@@ -16917,15 +17001,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V35" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W35" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2789</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -17041,30 +17125,42 @@
       <c r="B38" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="122"/>
-      <c r="D38" s="123"/>
+      <c r="C38" s="122">
+        <v>3780</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
       <c r="E38" s="124"/>
       <c r="F38" s="124"/>
-      <c r="G38" s="81"/>
+      <c r="G38" s="81">
+        <v>124</v>
+      </c>
       <c r="H38" s="82"/>
       <c r="I38" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3656</v>
       </c>
       <c r="J38" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="53"/>
-      <c r="L38" s="130"/>
+      <c r="L38" s="130">
+        <v>4</v>
+      </c>
       <c r="M38" s="130"/>
-      <c r="N38" s="130"/>
+      <c r="N38" s="130">
+        <v>90</v>
+      </c>
       <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
+      <c r="P38" s="130">
+        <v>30</v>
+      </c>
       <c r="Q38" s="131"/>
       <c r="R38" s="106">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="S38" s="134">
         <f t="shared" si="7"/>
@@ -17073,15 +17169,15 @@
       <c r="T38" s="53"/>
       <c r="U38" s="140">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="V38" s="144">
         <f>U38/6</f>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="W38" s="142">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>21938</v>
       </c>
       <c r="X38" s="54"/>
     </row>
@@ -17093,15 +17189,19 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="119"/>
+      <c r="C39" s="119">
+        <v>12</v>
+      </c>
       <c r="D39" s="120"/>
       <c r="E39" s="121"/>
       <c r="F39" s="121"/>
-      <c r="G39" s="79"/>
+      <c r="G39" s="79">
+        <v>1</v>
+      </c>
       <c r="H39" s="76"/>
       <c r="I39" s="79">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J39" s="80">
         <f t="shared" si="4"/>
@@ -17110,13 +17210,15 @@
       <c r="K39" s="41"/>
       <c r="L39" s="121"/>
       <c r="M39" s="121"/>
-      <c r="N39" s="121"/>
+      <c r="N39" s="121">
+        <v>1</v>
+      </c>
       <c r="O39" s="121"/>
       <c r="P39" s="121"/>
       <c r="Q39" s="129"/>
       <c r="R39" s="105">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="135">
         <f t="shared" si="7"/>
@@ -17125,15 +17227,15 @@
       <c r="T39" s="41"/>
       <c r="U39" s="116">
         <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V39" s="118">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="138">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -17197,7 +17299,9 @@
       <c r="B41" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="155"/>
+      <c r="C41" s="155">
+        <v>504</v>
+      </c>
       <c r="D41" s="156"/>
       <c r="E41" s="157"/>
       <c r="F41" s="157"/>
@@ -17205,7 +17309,7 @@
       <c r="H41" s="159"/>
       <c r="I41" s="160">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="J41" s="161">
         <f t="shared" si="4"/>
@@ -17237,7 +17341,7 @@
       </c>
       <c r="W41" s="168">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>12096</v>
       </c>
       <c r="X41" s="169"/>
     </row>
@@ -17249,30 +17353,38 @@
       <c r="B42" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="172"/>
-      <c r="D42" s="173"/>
+      <c r="C42" s="172">
+        <v>1324</v>
+      </c>
+      <c r="D42" s="173">
+        <v>9</v>
+      </c>
       <c r="E42" s="174"/>
       <c r="F42" s="174"/>
-      <c r="G42" s="175"/>
+      <c r="G42" s="175">
+        <v>15</v>
+      </c>
       <c r="H42" s="176"/>
       <c r="I42" s="175">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1309</v>
       </c>
       <c r="J42" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K42" s="178"/>
       <c r="L42" s="174"/>
       <c r="M42" s="174"/>
       <c r="N42" s="174"/>
       <c r="O42" s="174"/>
-      <c r="P42" s="174"/>
+      <c r="P42" s="174">
+        <v>15</v>
+      </c>
       <c r="Q42" s="179"/>
       <c r="R42" s="180">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S42" s="181">
         <f t="shared" si="7"/>
@@ -17281,15 +17393,15 @@
       <c r="T42" s="178"/>
       <c r="U42" s="182">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="V42" s="183">
         <f>U42/12</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W42" s="184">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>15717</v>
       </c>
       <c r="X42" s="185"/>
     </row>
@@ -17344,30 +17456,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="122"/>
-      <c r="D44" s="123"/>
+      <c r="C44" s="122">
+        <v>26219</v>
+      </c>
+      <c r="D44" s="123">
+        <v>3</v>
+      </c>
       <c r="E44" s="124"/>
       <c r="F44" s="124"/>
-      <c r="G44" s="81"/>
+      <c r="G44" s="81">
+        <v>1189</v>
+      </c>
       <c r="H44" s="82"/>
       <c r="I44" s="76">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>25030</v>
       </c>
       <c r="J44" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="53"/>
-      <c r="L44" s="130"/>
+      <c r="L44" s="130">
+        <v>431</v>
+      </c>
       <c r="M44" s="130"/>
-      <c r="N44" s="130"/>
+      <c r="N44" s="130">
+        <v>395</v>
+      </c>
       <c r="O44" s="130"/>
-      <c r="P44" s="130"/>
+      <c r="P44" s="130">
+        <v>363</v>
+      </c>
       <c r="Q44" s="131"/>
       <c r="R44" s="187">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="S44" s="188">
         <f t="shared" si="7"/>
@@ -17376,15 +17500,15 @@
       <c r="T44" s="53"/>
       <c r="U44" s="140">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7134</v>
       </c>
       <c r="V44" s="139">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="W44" s="142">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>150183</v>
       </c>
       <c r="X44" s="54"/>
       <c r="Z44" s="47"/>
@@ -17544,19 +17668,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="150"/>
-      <c r="D48" s="151"/>
+      <c r="C48" s="150">
+        <v>2347</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
       <c r="E48" s="130"/>
       <c r="F48" s="130"/>
       <c r="G48" s="152"/>
       <c r="H48" s="148"/>
       <c r="I48" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2347</v>
       </c>
       <c r="J48" s="149">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="53"/>
       <c r="L48" s="130"/>
@@ -17584,7 +17712,7 @@
       </c>
       <c r="W48" s="142">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>14086</v>
       </c>
       <c r="X48" s="54"/>
     </row>
@@ -17596,7 +17724,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="119"/>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
       <c r="D49" s="120"/>
       <c r="E49" s="121"/>
       <c r="F49" s="121"/>
@@ -17604,7 +17734,7 @@
       <c r="H49" s="76"/>
       <c r="I49" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="80">
         <f t="shared" si="4"/>
@@ -17636,7 +17766,7 @@
       </c>
       <c r="W49" s="138">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -17752,7 +17882,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="150"/>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
       <c r="D52" s="151"/>
       <c r="E52" s="130"/>
       <c r="F52" s="130"/>
@@ -17760,7 +17892,7 @@
       <c r="H52" s="148"/>
       <c r="I52" s="148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="149">
         <f t="shared" si="4"/>
@@ -17792,7 +17924,7 @@
       </c>
       <c r="W52" s="142">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="54"/>
     </row>
@@ -17856,7 +17988,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="119"/>
+      <c r="C54" s="119">
+        <v>5</v>
+      </c>
       <c r="D54" s="120"/>
       <c r="E54" s="121"/>
       <c r="F54" s="121"/>
@@ -17864,7 +17998,7 @@
       <c r="H54" s="76"/>
       <c r="I54" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J54" s="80">
         <f t="shared" si="4"/>
@@ -17896,7 +18030,7 @@
       </c>
       <c r="W54" s="138">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -18111,11 +18245,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>38692</v>
       </c>
       <c r="D60" s="57">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -18124,24 +18258,24 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="H60" s="59">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I60" s="59">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>37301</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="77">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="M60" s="77">
         <f t="shared" si="20"/>
@@ -18149,40 +18283,40 @@
       </c>
       <c r="N60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="O60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P60" s="77">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="Q60" s="78">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R60" s="91">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="S60" s="90">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>9570</v>
       </c>
       <c r="V60" s="111">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="99">
+        <v>1391</v>
+      </c>
+      <c r="W60" s="204">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>320377</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/DSSR GBDS MONTH OF MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE1CFF5-05D7-459D-8455-473AF26FD451}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FF2C39-88D0-4998-9E90-FCDBB07096F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -26,8 +26,9 @@
     <sheet name="03,11" sheetId="99" r:id="rId11"/>
     <sheet name="03,12" sheetId="100" r:id="rId12"/>
     <sheet name="03,14" sheetId="101" r:id="rId13"/>
-    <sheet name="03,15" sheetId="102" r:id="rId14"/>
-    <sheet name="03,16" sheetId="103" r:id="rId15"/>
+    <sheet name="03,16" sheetId="103" r:id="rId14"/>
+    <sheet name="03,17" sheetId="102" r:id="rId15"/>
+    <sheet name="03,18" sheetId="104" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02,05 PROMO'!$A$1:$W$61</definedName>
@@ -42,8 +43,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'03,11'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'03,12'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'03,14'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'03,15'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'03,16'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'03,16'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'03,17'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'03,18'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -411,6 +413,92 @@
     <author>User</author>
   </authors>
   <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{A29E93FB-D8E8-4DD3-90E0-2F936A44AACB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{8BB26612-BFCD-46A8-9735-F39EA4B108C4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{D471CBD0-ABFE-4D27-A880-78E662EF74B4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
     <comment ref="U5" authorId="0" shapeId="0" xr:uid="{B642556F-1505-4AB0-A3D3-B21E49888195}">
       <text>
         <r>
@@ -491,13 +579,13 @@
 </comments>
 </file>
 
-<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>User</author>
   </authors>
   <commentList>
-    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{A29E93FB-D8E8-4DD3-90E0-2F936A44AACB}">
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{3FBA208B-667A-4DFE-9BEB-9852BCB64942}">
       <text>
         <r>
           <rPr>
@@ -523,7 +611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{8BB26612-BFCD-46A8-9735-F39EA4B108C4}">
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{C8731DAC-278B-4ECB-8803-58888DD9277C}">
       <text>
         <r>
           <rPr>
@@ -548,7 +636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{D471CBD0-ABFE-4D27-A880-78E662EF74B4}">
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{E3D6CE63-E136-4BE4-890E-2BF1B8C99FD1}">
       <text>
         <r>
           <rPr>
@@ -1266,7 +1354,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2918,7 +3006,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3586,6 +3674,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4025,15 +4122,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228"/>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="P1" s="231"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -4058,62 +4155,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6364,7 +6461,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -6382,7 +6479,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -6398,7 +6495,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -6414,7 +6511,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -6432,7 +6529,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -6448,7 +6545,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -6843,17 +6940,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46091</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6878,62 +6975,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -10419,7 +10516,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -10437,7 +10534,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -10453,7 +10550,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -10469,7 +10566,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -10487,7 +10584,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -10503,7 +10600,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -10898,17 +10995,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46092</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10933,62 +11030,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="219" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14472,7 +14569,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -14490,7 +14587,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -14506,7 +14603,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -14522,7 +14619,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -14540,7 +14637,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -14556,7 +14653,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -14951,17 +15048,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46093</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14986,62 +15083,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="219" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18509,7 +18606,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -18527,7 +18624,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -18543,7 +18640,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -18559,7 +18656,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -18577,7 +18674,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -18593,7 +18690,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -18988,17 +19085,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46095</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -19023,62 +19120,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="219" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22564,7 +22661,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -22582,7 +22679,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -22598,7 +22695,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -22614,7 +22711,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -22632,7 +22729,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -22648,7 +22745,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -22994,7 +23091,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97BD689C-3A2A-47F7-8BBF-9939A9D59483}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED1BD73-A48C-4F22-A504-2935EC0BD975}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -23043,17 +23140,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
-        <v>46096</v>
-      </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="P1" s="231">
+        <v>46095</v>
+      </c>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -23078,62 +23175,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="222" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26467,7 +26564,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -26485,7 +26582,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -26501,7 +26598,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -26517,7 +26614,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -26535,7 +26632,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -26551,7 +26648,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -26897,7 +26994,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED1BD73-A48C-4F22-A504-2935EC0BD975}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97BD689C-3A2A-47F7-8BBF-9939A9D59483}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26946,17 +27043,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
-        <v>46095</v>
-      </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="P1" s="231">
+        <v>46098</v>
+      </c>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26981,62 +27078,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="222" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -27201,30 +27298,38 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
+      <c r="C8" s="119">
+        <v>62</v>
+      </c>
+      <c r="D8" s="120">
+        <v>21</v>
+      </c>
       <c r="E8" s="121"/>
       <c r="F8" s="121"/>
-      <c r="G8" s="79"/>
+      <c r="G8" s="79">
+        <v>5</v>
+      </c>
       <c r="H8" s="76"/>
       <c r="I8" s="76">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J8" s="80">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="121"/>
       <c r="M8" s="121"/>
       <c r="N8" s="121"/>
       <c r="O8" s="121"/>
-      <c r="P8" s="121"/>
+      <c r="P8" s="121">
+        <v>5</v>
+      </c>
       <c r="Q8" s="129"/>
       <c r="R8" s="92">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S8" s="133">
         <f t="shared" si="1"/>
@@ -27233,15 +27338,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="116">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V8" s="139">
         <f>U8/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8" s="138">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1389</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -27276,30 +27381,38 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="122"/>
+      <c r="C9" s="122">
+        <v>100</v>
+      </c>
       <c r="D9" s="123"/>
       <c r="E9" s="124"/>
       <c r="F9" s="124"/>
-      <c r="G9" s="81"/>
+      <c r="G9" s="81">
+        <v>5</v>
+      </c>
       <c r="H9" s="82"/>
       <c r="I9" s="81">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J9" s="103">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="53"/>
-      <c r="L9" s="130"/>
+      <c r="L9" s="130">
+        <v>3</v>
+      </c>
       <c r="M9" s="130"/>
       <c r="N9" s="130"/>
       <c r="O9" s="130"/>
-      <c r="P9" s="130"/>
+      <c r="P9" s="130">
+        <v>2</v>
+      </c>
       <c r="Q9" s="131"/>
       <c r="R9" s="107">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" s="134">
         <f t="shared" si="1"/>
@@ -27308,15 +27421,15 @@
       <c r="T9" s="53"/>
       <c r="U9" s="140">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V9" s="141">
         <f>U9/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="X9" s="54"/>
       <c r="AL9" s="12"/>
@@ -27351,30 +27464,38 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="119"/>
+      <c r="C10" s="119">
+        <v>23</v>
+      </c>
       <c r="D10" s="120"/>
       <c r="E10" s="121"/>
       <c r="F10" s="121"/>
-      <c r="G10" s="79"/>
+      <c r="G10" s="79">
+        <v>7</v>
+      </c>
       <c r="H10" s="76"/>
       <c r="I10" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="121"/>
+      <c r="L10" s="121">
+        <v>2</v>
+      </c>
       <c r="M10" s="121"/>
       <c r="N10" s="121"/>
       <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
+      <c r="P10" s="121">
+        <v>5</v>
+      </c>
       <c r="Q10" s="129"/>
       <c r="R10" s="108">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S10" s="135">
         <f t="shared" si="1"/>
@@ -27383,15 +27504,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="116">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V10" s="143">
         <f>U10/24</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -27426,11 +27547,15 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="119">
+        <v>2</v>
+      </c>
       <c r="D11" s="120"/>
       <c r="E11" s="121"/>
       <c r="F11" s="121"/>
-      <c r="G11" s="79"/>
+      <c r="G11" s="79">
+        <v>2</v>
+      </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76">
         <f t="shared" si="4"/>
@@ -27445,11 +27570,13 @@
       <c r="M11" s="121"/>
       <c r="N11" s="121"/>
       <c r="O11" s="121"/>
-      <c r="P11" s="121"/>
+      <c r="P11" s="121">
+        <v>2</v>
+      </c>
       <c r="Q11" s="129"/>
       <c r="R11" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="133">
         <f t="shared" si="1"/>
@@ -27458,11 +27585,11 @@
       <c r="T11" s="41"/>
       <c r="U11" s="116">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V11" s="139">
         <f>U11/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="138">
         <f t="shared" si="2"/>
@@ -27501,30 +27628,38 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="119">
+        <v>10</v>
+      </c>
       <c r="D12" s="120"/>
       <c r="E12" s="121"/>
       <c r="F12" s="121"/>
-      <c r="G12" s="79"/>
+      <c r="G12" s="79">
+        <v>6</v>
+      </c>
       <c r="H12" s="76"/>
       <c r="I12" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12" s="41"/>
-      <c r="L12" s="121"/>
+      <c r="L12" s="121">
+        <v>1</v>
+      </c>
       <c r="M12" s="121"/>
       <c r="N12" s="121"/>
       <c r="O12" s="121"/>
-      <c r="P12" s="121"/>
+      <c r="P12" s="121">
+        <v>5</v>
+      </c>
       <c r="Q12" s="129"/>
       <c r="R12" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S12" s="133">
         <f t="shared" si="1"/>
@@ -27533,15 +27668,15 @@
       <c r="T12" s="41"/>
       <c r="U12" s="116">
         <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V12" s="139">
         <f t="shared" ref="V12:V41" si="6">U12/24</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W12" s="138">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -27576,47 +27711,63 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
+      <c r="C13" s="122">
+        <v>3666</v>
+      </c>
+      <c r="D13" s="123">
+        <v>21</v>
+      </c>
       <c r="E13" s="124"/>
       <c r="F13" s="124"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="82"/>
+      <c r="G13" s="81">
+        <v>48</v>
+      </c>
+      <c r="H13" s="82">
+        <v>14</v>
+      </c>
       <c r="I13" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3618</v>
       </c>
       <c r="J13" s="103">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K13" s="55"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
+      <c r="L13" s="130">
+        <v>36</v>
+      </c>
+      <c r="M13" s="130">
+        <v>6</v>
+      </c>
+      <c r="N13" s="130">
+        <v>12</v>
+      </c>
+      <c r="O13" s="130">
+        <v>8</v>
+      </c>
       <c r="P13" s="130"/>
       <c r="Q13" s="131"/>
       <c r="R13" s="106">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="S13" s="134">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T13" s="55"/>
       <c r="U13" s="140">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="V13" s="144">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W13" s="142">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>86839</v>
       </c>
       <c r="X13" s="54"/>
       <c r="Y13" s="2"/>
@@ -27658,15 +27809,19 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="119">
+        <v>5</v>
+      </c>
       <c r="D14" s="120"/>
       <c r="E14" s="121"/>
       <c r="F14" s="121"/>
-      <c r="G14" s="79"/>
+      <c r="G14" s="79">
+        <v>1</v>
+      </c>
       <c r="H14" s="76"/>
       <c r="I14" s="102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="4"/>
@@ -27677,11 +27832,13 @@
       <c r="M14" s="121"/>
       <c r="N14" s="121"/>
       <c r="O14" s="121"/>
-      <c r="P14" s="121"/>
+      <c r="P14" s="121">
+        <v>1</v>
+      </c>
       <c r="Q14" s="129"/>
       <c r="R14" s="105">
         <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="135">
         <f t="shared" si="7"/>
@@ -27690,15 +27847,15 @@
       <c r="T14" s="41"/>
       <c r="U14" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V14" s="118">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="138">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -27958,7 +28115,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="119">
+        <v>4</v>
+      </c>
       <c r="D18" s="120"/>
       <c r="E18" s="121"/>
       <c r="F18" s="121"/>
@@ -27966,7 +28125,7 @@
       <c r="H18" s="76"/>
       <c r="I18" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="4"/>
@@ -27998,7 +28157,7 @@
       </c>
       <c r="W18" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -28108,7 +28267,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="119">
+        <v>4</v>
+      </c>
       <c r="D20" s="120"/>
       <c r="E20" s="121"/>
       <c r="F20" s="121"/>
@@ -28116,7 +28277,7 @@
       <c r="H20" s="76"/>
       <c r="I20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80">
         <f t="shared" si="4"/>
@@ -28148,7 +28309,7 @@
       </c>
       <c r="W20" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -28183,7 +28344,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="119"/>
+      <c r="C21" s="119">
+        <v>6</v>
+      </c>
       <c r="D21" s="120"/>
       <c r="E21" s="121"/>
       <c r="F21" s="121"/>
@@ -28191,7 +28354,7 @@
       <c r="H21" s="76"/>
       <c r="I21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="80">
         <f t="shared" si="4"/>
@@ -28223,7 +28386,7 @@
       </c>
       <c r="W21" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -28258,7 +28421,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="119">
+        <v>4</v>
+      </c>
       <c r="D22" s="120"/>
       <c r="E22" s="121"/>
       <c r="F22" s="121"/>
@@ -28266,7 +28431,7 @@
       <c r="H22" s="76"/>
       <c r="I22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="80">
         <f t="shared" si="4"/>
@@ -28298,7 +28463,7 @@
       </c>
       <c r="W22" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -28333,15 +28498,19 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="119">
+        <v>2</v>
+      </c>
       <c r="D23" s="120"/>
       <c r="E23" s="121"/>
       <c r="F23" s="121"/>
-      <c r="G23" s="79"/>
+      <c r="G23" s="79">
+        <v>1</v>
+      </c>
       <c r="H23" s="76"/>
       <c r="I23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="80">
         <f t="shared" si="4"/>
@@ -28352,11 +28521,13 @@
       <c r="M23" s="121"/>
       <c r="N23" s="121"/>
       <c r="O23" s="121"/>
-      <c r="P23" s="121"/>
+      <c r="P23" s="121">
+        <v>1</v>
+      </c>
       <c r="Q23" s="129"/>
       <c r="R23" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="133">
         <f t="shared" si="7"/>
@@ -28365,15 +28536,15 @@
       <c r="T23" s="42"/>
       <c r="U23" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V23" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -28415,19 +28586,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="120"/>
+      <c r="C24" s="119">
+        <v>38</v>
+      </c>
+      <c r="D24" s="120">
+        <v>19</v>
+      </c>
       <c r="E24" s="121"/>
       <c r="F24" s="121"/>
       <c r="G24" s="79"/>
       <c r="H24" s="76"/>
       <c r="I24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J24" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="121"/>
@@ -28455,7 +28630,7 @@
       </c>
       <c r="W24" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -28497,15 +28672,19 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="119"/>
+      <c r="C25" s="119">
+        <v>7</v>
+      </c>
       <c r="D25" s="120"/>
       <c r="E25" s="121"/>
       <c r="F25" s="121"/>
-      <c r="G25" s="79"/>
+      <c r="G25" s="79">
+        <v>1</v>
+      </c>
       <c r="H25" s="76"/>
       <c r="I25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J25" s="80">
         <f t="shared" si="4"/>
@@ -28516,11 +28695,13 @@
       <c r="M25" s="121"/>
       <c r="N25" s="121"/>
       <c r="O25" s="121"/>
-      <c r="P25" s="121"/>
+      <c r="P25" s="121">
+        <v>1</v>
+      </c>
       <c r="Q25" s="129"/>
       <c r="R25" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="133">
         <f t="shared" si="7"/>
@@ -28529,15 +28710,15 @@
       <c r="T25" s="41"/>
       <c r="U25" s="116">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V25" s="139">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="138">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -28572,6 +28753,4025 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="C26" s="119">
+        <v>119</v>
+      </c>
+      <c r="D26" s="120">
+        <v>11</v>
+      </c>
+      <c r="E26" s="121"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="79">
+        <v>20</v>
+      </c>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76">
+        <f t="shared" si="4"/>
+        <v>99</v>
+      </c>
+      <c r="J26" s="80">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="121">
+        <v>15</v>
+      </c>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="129"/>
+      <c r="R26" s="92">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="S26" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="116">
+        <f t="shared" si="5"/>
+        <v>480</v>
+      </c>
+      <c r="V26" s="139">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="W26" s="138">
+        <f t="shared" si="8"/>
+        <v>2387</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="119">
+        <v>16</v>
+      </c>
+      <c r="D27" s="120"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="79">
+        <v>3</v>
+      </c>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="J27" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="121">
+        <v>1</v>
+      </c>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="129"/>
+      <c r="R27" s="92">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S27" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="116">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="V27" s="139">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W27" s="138">
+        <f t="shared" si="8"/>
+        <v>312</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="119"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="119">
+        <v>78</v>
+      </c>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="79">
+        <v>40</v>
+      </c>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+      <c r="J29" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="121">
+        <v>10</v>
+      </c>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="121"/>
+      <c r="P29" s="121">
+        <v>30</v>
+      </c>
+      <c r="Q29" s="129"/>
+      <c r="R29" s="92">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="S29" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="116">
+        <f t="shared" si="5"/>
+        <v>960</v>
+      </c>
+      <c r="V29" s="139">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+      <c r="W29" s="138">
+        <f t="shared" si="8"/>
+        <v>912</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="119">
+        <v>6</v>
+      </c>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="79">
+        <v>6</v>
+      </c>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121">
+        <v>6</v>
+      </c>
+      <c r="Q30" s="129"/>
+      <c r="R30" s="92">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="S30" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="116">
+        <f t="shared" si="5"/>
+        <v>144</v>
+      </c>
+      <c r="V30" s="139">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="W30" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="119">
+        <v>58</v>
+      </c>
+      <c r="D31" s="120"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="79">
+        <v>2</v>
+      </c>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="J31" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="129"/>
+      <c r="R31" s="92">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S31" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="116">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V31" s="139">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W31" s="138">
+        <f t="shared" si="8"/>
+        <v>1344</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="119">
+        <v>1</v>
+      </c>
+      <c r="D32" s="120"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="79">
+        <v>1</v>
+      </c>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="121">
+        <v>1</v>
+      </c>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="92">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S32" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="116">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V32" s="139">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W32" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="129"/>
+      <c r="R33" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="119"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="121"/>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="129"/>
+      <c r="R34" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="119">
+        <v>113</v>
+      </c>
+      <c r="D35" s="120">
+        <v>5</v>
+      </c>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="79">
+        <v>20</v>
+      </c>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76">
+        <f t="shared" si="4"/>
+        <v>93</v>
+      </c>
+      <c r="J35" s="80">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="121">
+        <v>20</v>
+      </c>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="129"/>
+      <c r="R35" s="92">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="S35" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="116">
+        <f t="shared" si="5"/>
+        <v>480</v>
+      </c>
+      <c r="V35" s="139">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="W35" s="138">
+        <f t="shared" si="8"/>
+        <v>2237</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="121"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="129"/>
+      <c r="R36" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="119"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="129"/>
+      <c r="R37" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="122">
+        <v>3458</v>
+      </c>
+      <c r="D38" s="123">
+        <v>2</v>
+      </c>
+      <c r="E38" s="124"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="81">
+        <v>253</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="148">
+        <f t="shared" si="4"/>
+        <v>3205</v>
+      </c>
+      <c r="J38" s="149">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K38" s="53"/>
+      <c r="L38" s="130">
+        <v>118</v>
+      </c>
+      <c r="M38" s="130"/>
+      <c r="N38" s="130">
+        <v>30</v>
+      </c>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130">
+        <v>105</v>
+      </c>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="106">
+        <f t="shared" si="7"/>
+        <v>253</v>
+      </c>
+      <c r="S38" s="134">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="53"/>
+      <c r="U38" s="140">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>1518</v>
+      </c>
+      <c r="V38" s="144">
+        <f>U38/6</f>
+        <v>253</v>
+      </c>
+      <c r="W38" s="142">
+        <f>I38*6+J38</f>
+        <v>19232</v>
+      </c>
+      <c r="X38" s="54"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="119">
+        <v>11</v>
+      </c>
+      <c r="D39" s="120"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="79">
+        <v>2</v>
+      </c>
+      <c r="H39" s="76"/>
+      <c r="I39" s="79">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J39" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="121"/>
+      <c r="P39" s="121">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="129"/>
+      <c r="R39" s="105">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S39" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="116">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>48</v>
+      </c>
+      <c r="V39" s="118">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W39" s="138">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>216</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="129"/>
+      <c r="R40" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="145">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="146">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="101"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="155">
+        <v>504</v>
+      </c>
+      <c r="D41" s="156"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="158">
+        <v>20</v>
+      </c>
+      <c r="H41" s="159"/>
+      <c r="I41" s="160">
+        <f t="shared" si="4"/>
+        <v>484</v>
+      </c>
+      <c r="J41" s="161">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="162"/>
+      <c r="L41" s="163"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="163"/>
+      <c r="O41" s="163"/>
+      <c r="P41" s="163">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="164"/>
+      <c r="R41" s="165">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="S41" s="166">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="162"/>
+      <c r="U41" s="167">
+        <f t="shared" si="9"/>
+        <v>480</v>
+      </c>
+      <c r="V41" s="168">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="W41" s="168">
+        <f t="shared" si="10"/>
+        <v>11616</v>
+      </c>
+      <c r="X41" s="169"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="171" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="172">
+        <v>1270</v>
+      </c>
+      <c r="D42" s="173">
+        <v>9</v>
+      </c>
+      <c r="E42" s="174"/>
+      <c r="F42" s="174"/>
+      <c r="G42" s="175">
+        <v>54</v>
+      </c>
+      <c r="H42" s="176"/>
+      <c r="I42" s="175">
+        <f t="shared" si="4"/>
+        <v>1216</v>
+      </c>
+      <c r="J42" s="177">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="K42" s="178"/>
+      <c r="L42" s="174">
+        <v>3</v>
+      </c>
+      <c r="M42" s="174"/>
+      <c r="N42" s="174">
+        <v>1</v>
+      </c>
+      <c r="O42" s="174"/>
+      <c r="P42" s="174">
+        <v>50</v>
+      </c>
+      <c r="Q42" s="179"/>
+      <c r="R42" s="180">
+        <f t="shared" si="7"/>
+        <v>54</v>
+      </c>
+      <c r="S42" s="181">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="178"/>
+      <c r="U42" s="182">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>648</v>
+      </c>
+      <c r="V42" s="183">
+        <f>U42/12</f>
+        <v>54</v>
+      </c>
+      <c r="W42" s="184">
+        <f>I42*12+J42</f>
+        <v>14601</v>
+      </c>
+      <c r="X42" s="185"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="119"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="116"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="122">
+        <v>24513</v>
+      </c>
+      <c r="D44" s="123">
+        <v>3</v>
+      </c>
+      <c r="E44" s="124">
+        <v>3672</v>
+      </c>
+      <c r="F44" s="124"/>
+      <c r="G44" s="81">
+        <v>1555</v>
+      </c>
+      <c r="H44" s="82"/>
+      <c r="I44" s="76">
+        <f>C44+E44-G44</f>
+        <v>26630</v>
+      </c>
+      <c r="J44" s="186">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="53"/>
+      <c r="L44" s="130">
+        <v>840</v>
+      </c>
+      <c r="M44" s="130"/>
+      <c r="N44" s="130">
+        <v>395</v>
+      </c>
+      <c r="O44" s="130"/>
+      <c r="P44" s="130">
+        <v>320</v>
+      </c>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="187">
+        <f t="shared" si="7"/>
+        <v>1555</v>
+      </c>
+      <c r="S44" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="53"/>
+      <c r="U44" s="140">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>9330</v>
+      </c>
+      <c r="V44" s="139">
+        <f>U44/6</f>
+        <v>1555</v>
+      </c>
+      <c r="W44" s="142">
+        <f>I44*6+J44</f>
+        <v>159783</v>
+      </c>
+      <c r="X44" s="54"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="119"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="121"/>
+      <c r="F45" s="121"/>
+      <c r="G45" s="79"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="129"/>
+      <c r="R45" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="136">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="116"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="138"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="119"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="121"/>
+      <c r="F46" s="121"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="121"/>
+      <c r="P46" s="121"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="137">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="116">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="143">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="138">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="119"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="121"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="121"/>
+      <c r="P47" s="121"/>
+      <c r="Q47" s="129"/>
+      <c r="R47" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="139">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="138">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="150">
+        <v>2340</v>
+      </c>
+      <c r="D48" s="151">
+        <v>4</v>
+      </c>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="152">
+        <v>10</v>
+      </c>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148">
+        <f t="shared" si="4"/>
+        <v>2330</v>
+      </c>
+      <c r="J48" s="149">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K48" s="53"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="130"/>
+      <c r="P48" s="130">
+        <v>10</v>
+      </c>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="106">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S48" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="53"/>
+      <c r="U48" s="140">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>60</v>
+      </c>
+      <c r="V48" s="144">
+        <f>U48/6</f>
+        <v>10</v>
+      </c>
+      <c r="W48" s="142">
+        <f>I48*6+J48</f>
+        <v>13984</v>
+      </c>
+      <c r="X48" s="54"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="119">
+        <v>1</v>
+      </c>
+      <c r="D49" s="120"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="129"/>
+      <c r="R49" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="116">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="118">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="138">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="119"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="121"/>
+      <c r="G50" s="79"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="129"/>
+      <c r="R50" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="119"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="121"/>
+      <c r="F51" s="121"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="121"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="129"/>
+      <c r="R51" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="116">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="139">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="138">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="150">
+        <v>34</v>
+      </c>
+      <c r="D52" s="151"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="152"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="53"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="130"/>
+      <c r="O52" s="130"/>
+      <c r="P52" s="130"/>
+      <c r="Q52" s="131"/>
+      <c r="R52" s="106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="153">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="53"/>
+      <c r="U52" s="140">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="144">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="142">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="54"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="119"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="121"/>
+      <c r="F53" s="121"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="121"/>
+      <c r="P53" s="121"/>
+      <c r="Q53" s="129"/>
+      <c r="R53" s="105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="116">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="118">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="138">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="119">
+        <v>5</v>
+      </c>
+      <c r="D54" s="120"/>
+      <c r="E54" s="121"/>
+      <c r="F54" s="121"/>
+      <c r="G54" s="79"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J54" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="129"/>
+      <c r="R54" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="116">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="139">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="138">
+        <f t="shared" si="19"/>
+        <v>120</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="119"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="121"/>
+      <c r="M55" s="121"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="129"/>
+      <c r="R55" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="116"/>
+      <c r="V55" s="139"/>
+      <c r="W55" s="138"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="119"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="121"/>
+      <c r="F56" s="121"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="121"/>
+      <c r="M56" s="121"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="121"/>
+      <c r="P56" s="121"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="139"/>
+      <c r="W56" s="138"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="119"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="121"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="129"/>
+      <c r="R57" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="116"/>
+      <c r="V57" s="139"/>
+      <c r="W57" s="138"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="119"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="121"/>
+      <c r="F58" s="121"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="121"/>
+      <c r="M58" s="121"/>
+      <c r="N58" s="121"/>
+      <c r="O58" s="121"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="129"/>
+      <c r="R58" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="116"/>
+      <c r="V58" s="139"/>
+      <c r="W58" s="138"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="120"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="121"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="121"/>
+      <c r="M59" s="121"/>
+      <c r="N59" s="121"/>
+      <c r="O59" s="121"/>
+      <c r="P59" s="121"/>
+      <c r="Q59" s="129"/>
+      <c r="R59" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="116"/>
+      <c r="V59" s="139"/>
+      <c r="W59" s="138"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>36460</v>
+      </c>
+      <c r="D60" s="57">
+        <f>SUM(D8:D59)</f>
+        <v>95</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>3672</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>2062</v>
+      </c>
+      <c r="H60" s="59">
+        <f>SUM(H8:H59)</f>
+        <v>14</v>
+      </c>
+      <c r="I60" s="59">
+        <f>SUM(I8:I59)</f>
+        <v>38070</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>81</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="77">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>1050</v>
+      </c>
+      <c r="M60" s="77">
+        <f t="shared" si="20"/>
+        <v>6</v>
+      </c>
+      <c r="N60" s="77">
+        <f t="shared" si="20"/>
+        <v>438</v>
+      </c>
+      <c r="O60" s="77">
+        <f t="shared" si="20"/>
+        <v>8</v>
+      </c>
+      <c r="P60" s="77">
+        <f t="shared" si="20"/>
+        <v>574</v>
+      </c>
+      <c r="Q60" s="78">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="91">
+        <f t="shared" si="20"/>
+        <v>2062</v>
+      </c>
+      <c r="S60" s="90">
+        <f t="shared" si="20"/>
+        <v>14</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>16116</v>
+      </c>
+      <c r="V60" s="111">
+        <f>SUM(V8:V59)</f>
+        <v>2062</v>
+      </c>
+      <c r="W60" s="204">
+        <f>SUM(W8:W59)</f>
+        <v>319587</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="112"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="226" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="227"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="71"/>
+      <c r="R63" s="71"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="228"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="67"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="72"/>
+      <c r="R64" s="72"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="229" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="72"/>
+      <c r="R65" s="72"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="229"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="71"/>
+      <c r="R66" s="71"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="230"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="68"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="73"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="220" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="221"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="69"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="74"/>
+      <c r="R69" s="74"/>
+      <c r="S69" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="110" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FE4243-0BE5-4936-9778-A087FD7BCC5A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="231">
+        <v>46099</v>
+      </c>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="234" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="235" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="236" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="237" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="241" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="243" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="241" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="245" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="225" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="100" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="132"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="80">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="92">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="116">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="139">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="138">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="81">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="53"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="53"/>
+      <c r="U9" s="140">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="141">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="54"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="116">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="143">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="116">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="139">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="129"/>
+      <c r="R12" s="92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="116">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="139">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="103">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="55"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="106">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="134">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="55"/>
+      <c r="U13" s="140">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="144">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="142">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="105">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="135">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="138">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="129"/>
+      <c r="R15" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="129"/>
+      <c r="R16" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="119"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="129"/>
+      <c r="R18" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="119"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="129"/>
+      <c r="R19" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="119"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="129"/>
+      <c r="R22" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="119"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="129"/>
+      <c r="R24" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="92">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="133">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="139">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="C26" s="119"/>
       <c r="D26" s="120"/>
       <c r="E26" s="121"/>
@@ -30370,7 +34570,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -30388,7 +34588,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -30404,7 +34604,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -30420,7 +34620,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -30438,7 +34638,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -30454,7 +34654,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -30474,10 +34674,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="220" t="s">
+      <c r="C69" s="223" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="221"/>
+      <c r="D69" s="224"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -30847,15 +35047,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46058</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="233"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30878,60 +35078,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="248"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -33740,7 +37940,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -33758,7 +37958,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -33774,7 +37974,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -33790,7 +37990,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -33808,7 +38008,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -33824,7 +38024,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -34218,17 +38418,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46083</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -34253,62 +38453,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -37815,7 +42015,7 @@
       <c r="V62" s="203"/>
     </row>
     <row r="63" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G63" s="223" t="s">
+      <c r="G63" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H63" s="60"/>
@@ -37833,7 +42033,7 @@
       <c r="S63" s="32"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="224"/>
+      <c r="G64" s="227"/>
       <c r="H64" s="61"/>
       <c r="I64" s="61"/>
       <c r="J64" s="24" t="s">
@@ -37849,7 +42049,7 @@
       <c r="S64" s="35"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="225"/>
+      <c r="G65" s="228"/>
       <c r="H65" s="62"/>
       <c r="I65" s="62"/>
       <c r="J65" s="24" t="s">
@@ -37865,7 +42065,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226" t="s">
+      <c r="G66" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H66" s="63"/>
@@ -37883,7 +42083,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G67" s="226"/>
+      <c r="G67" s="229"/>
       <c r="H67" s="63"/>
       <c r="I67" s="63"/>
       <c r="J67" s="24" t="s">
@@ -37899,7 +42099,7 @@
       <c r="S67" s="35"/>
     </row>
     <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="227"/>
+      <c r="G68" s="230"/>
       <c r="H68" s="64"/>
       <c r="I68" s="64"/>
       <c r="J68" s="25" t="s">
@@ -38294,17 +42494,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46084</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -38329,62 +42529,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -41864,7 +46064,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -41882,7 +46082,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -41898,7 +46098,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -41914,7 +46114,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -41932,7 +46132,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -41948,7 +46148,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -42343,17 +46543,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46085</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -42378,62 +46578,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -45907,7 +50107,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -45925,7 +50125,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -45941,7 +50141,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -45957,7 +50157,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -45975,7 +50175,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -45991,7 +50191,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -46386,17 +50586,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46086</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -46421,62 +50621,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -49956,7 +54156,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -49974,7 +54174,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -49990,7 +54190,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -50006,7 +54206,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -50024,7 +54224,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -50040,7 +54240,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -50435,17 +54635,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46087</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -50470,62 +54670,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="210" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -53954,7 +58154,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -53972,7 +58172,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -53988,7 +58188,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -54004,7 +58204,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -54022,7 +58222,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -54038,7 +58238,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -54433,17 +58633,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46088</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -54468,62 +58668,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -58005,7 +62205,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -58023,7 +62223,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -58039,7 +62239,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -58055,7 +62255,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -58073,7 +62273,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -58089,7 +62289,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
@@ -58484,17 +62684,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="228">
+      <c r="P1" s="231">
         <v>46090</v>
       </c>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="230"/>
+      <c r="Q1" s="232"/>
+      <c r="R1" s="232"/>
+      <c r="S1" s="232"/>
+      <c r="T1" s="232"/>
+      <c r="U1" s="232"/>
+      <c r="V1" s="232"/>
+      <c r="W1" s="232"/>
+      <c r="X1" s="233"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -58519,62 +62719,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="235" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="234" t="s">
+      <c r="E4" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="236" t="s">
+      <c r="F4" s="238"/>
+      <c r="G4" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="238" t="s">
+      <c r="H4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="J4" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="243"/>
-      <c r="N4" s="243"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="245"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="248"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="237"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="239"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="242"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -62050,7 +66250,7 @@
       <c r="V61" s="112"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="226" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="60"/>
@@ -62068,7 +66268,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="224"/>
+      <c r="G63" s="227"/>
       <c r="H63" s="61"/>
       <c r="I63" s="61"/>
       <c r="J63" s="24" t="s">
@@ -62084,7 +66284,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="225"/>
+      <c r="G64" s="228"/>
       <c r="H64" s="62"/>
       <c r="I64" s="62"/>
       <c r="J64" s="24" t="s">
@@ -62100,7 +66300,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="226" t="s">
+      <c r="G65" s="229" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="63"/>
@@ -62118,7 +66318,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="226"/>
+      <c r="G66" s="229"/>
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
       <c r="J66" s="24" t="s">
@@ -62134,7 +66334,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="227"/>
+      <c r="G67" s="230"/>
       <c r="H67" s="64"/>
       <c r="I67" s="64"/>
       <c r="J67" s="25" t="s">
